--- a/waveprocessed/PROCESSED-20251113-tett6roof-loosepaneltaped/meta.xlsx
+++ b/waveprocessed/PROCESSED-20251113-tett6roof-loosepaneltaped/meta.xlsx
@@ -1027,47 +1027,47 @@
         <v>267.07</v>
       </c>
       <c r="P2" t="n">
-        <v>4700</v>
+        <v>4726</v>
       </c>
       <c r="Q2" t="n">
-        <v>9315.384615384615</v>
+        <v>9347</v>
       </c>
       <c r="R2" t="n">
         <v>22.69500000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>21.66437318610491</v>
+        <v>21.66610763072226</v>
       </c>
       <c r="T2" t="n">
-        <v>21.69776746080844</v>
+        <v>21.70427644422269</v>
       </c>
       <c r="U2" t="n">
-        <v>30.72355598967293</v>
+        <v>30.7361656458237</v>
       </c>
       <c r="V2" t="n">
-        <v>2.169348845171449</v>
+        <v>2.18493297482779</v>
       </c>
       <c r="W2" t="n">
-        <v>30.80004816656322</v>
+        <v>30.81372763415688</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7703333333333333</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.80664920385966</v>
+        <v>6.789092731771489</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9254823222218832</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>0.154476903681595</v>
+        <v>0.154078459547554</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992402949658459</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.199863797070839</v>
+        <v>1.20140500504788</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
@@ -1078,47 +1078,47 @@
         <v>269.75</v>
       </c>
       <c r="AI2" t="n">
-        <v>4800</v>
+        <v>4849</v>
       </c>
       <c r="AJ2" t="n">
-        <v>9415.384615384615</v>
+        <v>9469</v>
       </c>
       <c r="AK2" t="n">
         <v>23.42500000000001</v>
       </c>
       <c r="AL2" t="n">
-        <v>21.96692118890059</v>
+        <v>21.99818639435928</v>
       </c>
       <c r="AM2" t="n">
-        <v>21.91492923301928</v>
+        <v>21.92284351952297</v>
       </c>
       <c r="AN2" t="n">
-        <v>31.0248320537837</v>
+        <v>31.03793141981719</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.996793821643256</v>
+        <v>2.009574747518093</v>
       </c>
       <c r="AP2" t="n">
-        <v>31.08902361817812</v>
+        <v>31.10291911520746</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7701666666666668</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.80664920385966</v>
+        <v>6.792013952800097</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9250842755688481</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>0.1594457576004126</v>
+        <v>0.1591029268443424</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992428639850438</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201148161309909</v>
       </c>
       <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
@@ -1129,47 +1129,47 @@
         <v>270.24</v>
       </c>
       <c r="BB2" t="n">
-        <v>6500</v>
+        <v>6406</v>
       </c>
       <c r="BC2" t="n">
-        <v>11115.38461538462</v>
+        <v>11050</v>
       </c>
       <c r="BD2" t="n">
         <v>24.54000000000001</v>
       </c>
       <c r="BE2" t="n">
-        <v>21.81069136530499</v>
+        <v>22.06701717594625</v>
       </c>
       <c r="BF2" t="n">
-        <v>22.27442998257279</v>
+        <v>22.26493165805666</v>
       </c>
       <c r="BG2" t="n">
-        <v>31.54803046701923</v>
+        <v>31.53895676678999</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.554697011720335</v>
+        <v>2.489419667112058</v>
       </c>
       <c r="BI2" t="n">
-        <v>31.65129860163191</v>
+        <v>31.63705113022471</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.7740000000000001</v>
       </c>
       <c r="BK2" t="n">
-        <v>6.809582094531432</v>
+        <v>6.72531368984731</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.9342590690847371</v>
       </c>
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="n">
-        <v>0.1671071445998014</v>
+        <v>0.165039197948853</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.9991819816529883</v>
       </c>
       <c r="BP2" t="n">
-        <v>1.199606895264513</v>
+        <v>1.207053060832994</v>
       </c>
       <c r="BQ2" t="inlineStr"/>
       <c r="BR2" t="inlineStr"/>
@@ -1180,47 +1180,47 @@
         <v>270.91</v>
       </c>
       <c r="BU2" t="n">
-        <v>6500</v>
+        <v>6409</v>
       </c>
       <c r="BV2" t="n">
-        <v>11115.38461538462</v>
+        <v>11046</v>
       </c>
       <c r="BW2" t="n">
-        <v>23.97405000000004</v>
+        <v>23.96469999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>21.32145622202539</v>
+        <v>21.5619394014733</v>
       </c>
       <c r="BY2" t="n">
-        <v>21.45953814546604</v>
+        <v>21.41562177559604</v>
       </c>
       <c r="BZ2" t="n">
-        <v>30.42749013865112</v>
+        <v>30.35862539279942</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.454308027600661</v>
+        <v>3.320700988948679</v>
       </c>
       <c r="CB2" t="n">
-        <v>30.62293911575532</v>
+        <v>30.5396986035935</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.7728333333333333</v>
       </c>
       <c r="CD2" t="n">
-        <v>6.809582094531432</v>
+        <v>6.745506238654865</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.9314623817518741</v>
       </c>
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="n">
-        <v>0.1632532616134016</v>
+        <v>0.1616540333574922</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.9992009121593767</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.199606895264513</v>
+        <v>1.205256478436758</v>
       </c>
       <c r="CJ2" t="inlineStr"/>
       <c r="CK2" t="inlineStr"/>
@@ -1252,13 +1252,13 @@
       </c>
       <c r="CX2" t="inlineStr"/>
       <c r="CY2" t="n">
-        <v>1.013965232236201</v>
+        <v>1.015327107632666</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.9928879508306091</v>
+        <v>1.003128929828716</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.9775690217661854</v>
+        <v>0.9771116426635361</v>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="DC2" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298139333621809</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298420255355983</v>
       </c>
       <c r="DE2" t="n">
-        <v>1.300108342361864</v>
+        <v>1.291989664082687</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.300108342361864</v>
+        <v>1.293940047444468</v>
       </c>
     </row>
     <row r="3">
@@ -1337,47 +1337,47 @@
         <v>267.07</v>
       </c>
       <c r="P3" t="n">
-        <v>4700</v>
+        <v>4754</v>
       </c>
       <c r="Q3" t="n">
-        <v>9315.384615384615</v>
+        <v>9373</v>
       </c>
       <c r="R3" t="n">
         <v>8.465000000000003</v>
       </c>
       <c r="S3" t="n">
-        <v>7.29504088288741</v>
+        <v>7.312293439123334</v>
       </c>
       <c r="T3" t="n">
-        <v>7.305780796052079</v>
+        <v>7.298133464730054</v>
       </c>
       <c r="U3" t="n">
-        <v>10.3576649322452</v>
+        <v>10.3480240293999</v>
       </c>
       <c r="V3" t="n">
-        <v>1.22861057883512</v>
+        <v>1.241748073845101</v>
       </c>
       <c r="W3" t="n">
-        <v>10.43027836651963</v>
+        <v>10.42226173111844</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.80664920385966</v>
+        <v>6.794937114744855</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9246863070366348</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>0.05761828551067204</v>
+        <v>0.05751914267631522</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992454260183794</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200891307839786</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
@@ -1388,47 +1388,47 @@
         <v>269.75</v>
       </c>
       <c r="AI3" t="n">
-        <v>4800</v>
+        <v>4870</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9415.384615384615</v>
+        <v>9495</v>
       </c>
       <c r="AK3" t="n">
         <v>8.85499999999999</v>
       </c>
       <c r="AL3" t="n">
-        <v>7.335393511952222</v>
+        <v>7.323668210312621</v>
       </c>
       <c r="AM3" t="n">
-        <v>7.327232737028217</v>
+        <v>7.3247118141223</v>
       </c>
       <c r="AN3" t="n">
-        <v>10.38695013090273</v>
+        <v>10.38301529710768</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.389912554792356</v>
+        <v>1.392727417895053</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.47953195194469</v>
+        <v>10.47600574267353</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7710000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.80664920385966</v>
+        <v>6.777427224732707</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9270752896099725</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>0.06027287870017722</v>
+        <v>0.06001411807500805</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992299487600118</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.199863797070839</v>
+        <v>1.202432282243803</v>
       </c>
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
@@ -1439,47 +1439,47 @@
         <v>270.24</v>
       </c>
       <c r="BB3" t="n">
-        <v>6500</v>
+        <v>6434</v>
       </c>
       <c r="BC3" t="n">
-        <v>11115.38461538462</v>
+        <v>11055</v>
       </c>
       <c r="BD3" t="n">
         <v>9.669999999999987</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.129275563371093</v>
+        <v>7.109973943497785</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.059186592808203</v>
+        <v>7.046836117560455</v>
       </c>
       <c r="BG3" t="n">
-        <v>10.02058068485746</v>
+        <v>9.999334945914326</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.214082514384851</v>
+        <v>2.174047352566385</v>
       </c>
       <c r="BI3" t="n">
-        <v>10.2622706377411</v>
+        <v>10.23294587358813</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7703333333333333</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.80664920385966</v>
+        <v>6.789092731771489</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9254823222218832</v>
       </c>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="n">
-        <v>0.06582029780132283</v>
+        <v>0.06565052671623021</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992402949658459</v>
       </c>
       <c r="BP3" t="n">
-        <v>1.199863797070839</v>
+        <v>1.20140500504788</v>
       </c>
       <c r="BQ3" t="inlineStr"/>
       <c r="BR3" t="inlineStr"/>
@@ -1490,47 +1490,47 @@
         <v>270.91</v>
       </c>
       <c r="BU3" t="n">
-        <v>6500</v>
+        <v>6450</v>
       </c>
       <c r="BV3" t="n">
-        <v>11115.38461538462</v>
+        <v>11061</v>
       </c>
       <c r="BW3" t="n">
         <v>10.49000000000001</v>
       </c>
       <c r="BX3" t="n">
-        <v>7.60794013549617</v>
+        <v>7.611407732493742</v>
       </c>
       <c r="BY3" t="n">
-        <v>7.648707359103457</v>
+        <v>7.655437672256938</v>
       </c>
       <c r="BZ3" t="n">
-        <v>10.869603814833</v>
+        <v>10.88314938183021</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.936456606373792</v>
+        <v>2.98949035809491</v>
       </c>
       <c r="CB3" t="n">
-        <v>11.25926571729029</v>
+        <v>11.2862745433723</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7686666666666667</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.80664920385966</v>
+        <v>6.818392476543425</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9215053737072112</v>
       </c>
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="n">
-        <v>0.0714017501484879</v>
+        <v>0.0715249370789406</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992656724117859</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.199863797070839</v>
+        <v>1.198836132316406</v>
       </c>
       <c r="CJ3" t="inlineStr"/>
       <c r="CK3" t="inlineStr"/>
@@ -1562,13 +1562,13 @@
       </c>
       <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="n">
-        <v>1.005531515136464</v>
+        <v>1.001555568206334</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.9719009009884361</v>
+        <v>0.9708214161703927</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.067140702848459</v>
+        <v>1.070525404590903</v>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
@@ -1576,16 +1576,16 @@
         </is>
       </c>
       <c r="DC3" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298701298701299</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297016861219196</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298139333621809</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.299826689774697</v>
+        <v>1.300954032957502</v>
       </c>
     </row>
     <row r="4">
@@ -1647,47 +1647,47 @@
         <v>267.07</v>
       </c>
       <c r="P4" t="n">
-        <v>3950</v>
+        <v>5047</v>
       </c>
       <c r="Q4" t="n">
-        <v>13180.76923076923</v>
+        <v>14278</v>
       </c>
       <c r="R4" t="n">
-        <v>10.35499999999996</v>
+        <v>9.850000000000023</v>
       </c>
       <c r="S4" t="n">
-        <v>8.833401780976683</v>
+        <v>8.70390005396469</v>
       </c>
       <c r="T4" t="n">
-        <v>8.870781849323546</v>
+        <v>8.712695344757016</v>
       </c>
       <c r="U4" t="n">
-        <v>12.56589780829133</v>
+        <v>12.34307179927763</v>
       </c>
       <c r="V4" t="n">
-        <v>1.101367624740606</v>
+        <v>1.056166605050153</v>
       </c>
       <c r="W4" t="n">
-        <v>12.61407144316408</v>
+        <v>12.38817619101964</v>
       </c>
       <c r="X4" t="n">
-        <v>1.5385</v>
+        <v>1.538666666666666</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.048927717267306</v>
+        <v>2.048620597885807</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.066572458475788</v>
+        <v>3.067032184321433</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>0.02121664651230287</v>
+        <v>0.02017891288917524</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8300197669922392</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993305145789493</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -1698,47 +1698,47 @@
         <v>269.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>4000</v>
+        <v>5125</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13230.76923076923</v>
+        <v>14361</v>
       </c>
       <c r="AK4" t="n">
-        <v>10.57350000000002</v>
+        <v>10.31500000000003</v>
       </c>
       <c r="AL4" t="n">
-        <v>9.12522099848578</v>
+        <v>9.034536217378546</v>
       </c>
       <c r="AM4" t="n">
-        <v>9.17515114192911</v>
+        <v>9.059894222503816</v>
       </c>
       <c r="AN4" t="n">
-        <v>13.00739125560925</v>
+        <v>12.82916417250165</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.500388427970632</v>
+        <v>1.41964223348959</v>
       </c>
       <c r="AP4" t="n">
-        <v>13.09363939900929</v>
+        <v>12.90747215515521</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.5385</v>
+        <v>1.5395</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.048927717267306</v>
+        <v>2.047086490905204</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.066572458475788</v>
+        <v>3.069330648751053</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>0.02166433721852589</v>
+        <v>0.02111569715368723</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8297427805022363</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993719161254338</v>
       </c>
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
@@ -1749,47 +1749,47 @@
         <v>270.24</v>
       </c>
       <c r="BB4" t="n">
-        <v>4500</v>
+        <v>5503</v>
       </c>
       <c r="BC4" t="n">
-        <v>13730.76923076923</v>
+        <v>14741</v>
       </c>
       <c r="BD4" t="n">
-        <v>11.59975000000002</v>
+        <v>11.52405000000001</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.905897832747089</v>
+        <v>8.838447214302617</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.937052842960648</v>
+        <v>8.888700500091803</v>
       </c>
       <c r="BG4" t="n">
-        <v>12.67483775239758</v>
+        <v>12.60401691406808</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.348463808255846</v>
+        <v>3.391848096452517</v>
       </c>
       <c r="BI4" t="n">
-        <v>13.10968046615944</v>
+        <v>13.05242796875443</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.5385</v>
+        <v>1.539833333333333</v>
       </c>
       <c r="BK4" t="n">
-        <v>2.048927717267306</v>
+        <v>2.046473542498564</v>
       </c>
       <c r="BL4" t="n">
-        <v>3.066572458475788</v>
+        <v>3.070249957645859</v>
       </c>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="n">
-        <v>0.02376704928837147</v>
+        <v>0.02358366342743059</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8296319968694142</v>
       </c>
       <c r="BP4" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993884592041904</v>
       </c>
       <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="inlineStr"/>
@@ -1800,47 +1800,47 @@
         <v>270.91</v>
       </c>
       <c r="BU4" t="n">
-        <v>4500</v>
+        <v>5523</v>
       </c>
       <c r="BV4" t="n">
-        <v>13730.76923076923</v>
+        <v>14735</v>
       </c>
       <c r="BW4" t="n">
-        <v>12.10924999999999</v>
+        <v>11.97969999999999</v>
       </c>
       <c r="BX4" t="n">
-        <v>9.029152703691704</v>
+        <v>8.939038218911186</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.08544046595736</v>
+        <v>9.005338772384688</v>
       </c>
       <c r="BZ4" t="n">
-        <v>12.88375532199908</v>
+        <v>12.77136875744178</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.339078914949418</v>
+        <v>3.350585572596296</v>
       </c>
       <c r="CB4" t="n">
-        <v>13.30941768814096</v>
+        <v>13.20357086616535</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.5385</v>
+        <v>1.5355</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.048927717267306</v>
+        <v>2.054472918535711</v>
       </c>
       <c r="CE4" t="n">
-        <v>3.066572458475788</v>
+        <v>3.058295512436258</v>
       </c>
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="n">
-        <v>0.02481097796031909</v>
+        <v>0.02461196922218224</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8310726661901815</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.993222267452576</v>
+        <v>1.99172615593374</v>
       </c>
       <c r="CJ4" t="inlineStr"/>
       <c r="CK4" t="inlineStr"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="CO4" t="inlineStr"/>
       <c r="CP4" t="n">
-        <v>0.02166508675092972</v>
+        <v>0.02113542061151372</v>
       </c>
       <c r="CQ4" t="n">
         <v>1.18841919095278</v>
@@ -1872,13 +1872,13 @@
       </c>
       <c r="CX4" t="inlineStr"/>
       <c r="CY4" t="n">
-        <v>1.033035881843114</v>
+        <v>1.037987127766161</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.9759651666765018</v>
+        <v>0.9782956204549007</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.01383969064763</v>
+        <v>1.011381072055936</v>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="DC4" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6499133448873484</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6495615459564794</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.649420933001407</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.651253663301856</v>
       </c>
     </row>
     <row r="5">
@@ -1957,49 +1957,49 @@
         <v>267.07</v>
       </c>
       <c r="P5" t="n">
-        <v>4700</v>
+        <v>4765</v>
       </c>
       <c r="Q5" t="n">
-        <v>9315.384615384615</v>
+        <v>9381</v>
       </c>
       <c r="R5" t="n">
-        <v>16.232</v>
+        <v>16.2318</v>
       </c>
       <c r="S5" t="n">
-        <v>14.93848718834333</v>
+        <v>14.95053809013714</v>
       </c>
       <c r="T5" t="n">
-        <v>14.87989366823428</v>
+        <v>14.87017653257821</v>
       </c>
       <c r="U5" t="n">
-        <v>21.07516181476149</v>
+        <v>21.05854745678721</v>
       </c>
       <c r="V5" t="n">
-        <v>1.259289881865472</v>
+        <v>1.225874127277932</v>
       </c>
       <c r="W5" t="n">
-        <v>21.11275104113506</v>
+        <v>21.09419797872601</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7695000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.80664920385966</v>
+        <v>6.803718262158717</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9234928703802656</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.83342091411231</v>
+        <v>17.82574184685584</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.11048552987705</v>
+        <v>0.1104365940877079</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992530703381666</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200120689253106</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
@@ -2010,49 +2010,49 @@
         <v>269.75</v>
       </c>
       <c r="AI5" t="n">
-        <v>4800</v>
+        <v>4885</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9415.384615384615</v>
+        <v>9505</v>
       </c>
       <c r="AK5" t="n">
         <v>16.64000000000003</v>
       </c>
       <c r="AL5" t="n">
-        <v>15.43070322561409</v>
+        <v>15.457097609847</v>
       </c>
       <c r="AM5" t="n">
-        <v>15.62140163037432</v>
+        <v>15.60093383802386</v>
       </c>
       <c r="AN5" t="n">
-        <v>22.11641015149418</v>
+        <v>22.08852598549575</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.335886588688501</v>
+        <v>1.321853257396178</v>
       </c>
       <c r="AP5" t="n">
-        <v>22.15671886735382</v>
+        <v>22.12804275678285</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7701666666666668</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.80664920385966</v>
+        <v>6.792013952800097</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9250842755688481</v>
       </c>
       <c r="AT5" t="n">
-        <v>17.83342091411231</v>
+        <v>17.79507655633626</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1132626427522249</v>
+        <v>0.1130191121745938</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992428639850438</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201148161309909</v>
       </c>
       <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr"/>
@@ -2063,49 +2063,49 @@
         <v>270.24</v>
       </c>
       <c r="BB5" t="n">
-        <v>6500</v>
+        <v>6476</v>
       </c>
       <c r="BC5" t="n">
-        <v>11115.38461538462</v>
+        <v>11095</v>
       </c>
       <c r="BD5" t="n">
         <v>12.25999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>11.3242054539211</v>
+        <v>11.30933064864345</v>
       </c>
       <c r="BF5" t="n">
-        <v>11.34459379110191</v>
+        <v>11.33788328766953</v>
       </c>
       <c r="BG5" t="n">
-        <v>16.07554097549919</v>
+        <v>16.06501288357717</v>
       </c>
       <c r="BH5" t="n">
-        <v>1.081733975483817</v>
+        <v>1.082539039003651</v>
       </c>
       <c r="BI5" t="n">
-        <v>16.11189517247023</v>
+        <v>16.10144495753308</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.77</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.80664920385966</v>
+        <v>6.794937114744855</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9246863070366348</v>
       </c>
       <c r="BM5" t="n">
-        <v>17.83342091411231</v>
+        <v>17.80273524063152</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.08344951923931937</v>
+        <v>0.08330592902677186</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992454260183794</v>
       </c>
       <c r="BP5" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200891307839786</v>
       </c>
       <c r="BQ5" t="inlineStr"/>
       <c r="BR5" t="inlineStr"/>
@@ -2116,49 +2116,49 @@
         <v>270.91</v>
       </c>
       <c r="BU5" t="n">
-        <v>6500</v>
+        <v>6480</v>
       </c>
       <c r="BV5" t="n">
-        <v>11115.38461538462</v>
+        <v>11097</v>
       </c>
       <c r="BW5" t="n">
         <v>12.625</v>
       </c>
       <c r="BX5" t="n">
-        <v>11.59843712566669</v>
+        <v>11.59165825605624</v>
       </c>
       <c r="BY5" t="n">
-        <v>11.64692217830147</v>
+        <v>11.63832068209671</v>
       </c>
       <c r="BZ5" t="n">
-        <v>16.50507687566569</v>
+        <v>16.49214389560816</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.398923635252876</v>
+        <v>1.40601724404486</v>
       </c>
       <c r="CB5" t="n">
-        <v>16.5642551902856</v>
+        <v>16.55196951314245</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7696666666666667</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.80664920385966</v>
+        <v>6.800789267814117</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9238906044208459</v>
       </c>
       <c r="CF5" t="n">
-        <v>17.83342091411231</v>
+        <v>17.81806788167299</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.08593394619872821</v>
+        <v>0.08585996450615323</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992505291814564</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200377571789752</v>
       </c>
       <c r="CJ5" t="inlineStr"/>
       <c r="CK5" t="inlineStr"/>
@@ -2192,13 +2192,13 @@
       </c>
       <c r="CX5" t="inlineStr"/>
       <c r="CY5" t="n">
-        <v>1.032949523674314</v>
+        <v>1.033882360397719</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.7338748784386938</v>
+        <v>0.731659392604133</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.02421641614164</v>
+        <v>1.024964130608973</v>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="DC5" t="n">
-        <v>1.299826689774697</v>
+        <v>1.299545159194282</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298420255355983</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298701298701299</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29926375054136</v>
       </c>
     </row>
     <row r="6">
@@ -2277,47 +2277,47 @@
         <v>267.07</v>
       </c>
       <c r="P6" t="n">
-        <v>3950</v>
+        <v>5053</v>
       </c>
       <c r="Q6" t="n">
-        <v>13180.76923076923</v>
+        <v>14285</v>
       </c>
       <c r="R6" t="n">
-        <v>5.33499999999998</v>
+        <v>5.324999999999989</v>
       </c>
       <c r="S6" t="n">
-        <v>4.363224094282709</v>
+        <v>4.276163348784116</v>
       </c>
       <c r="T6" t="n">
-        <v>4.392178050545418</v>
+        <v>4.319436079192302</v>
       </c>
       <c r="U6" t="n">
-        <v>6.23147673286624</v>
+        <v>6.127021726029091</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8879002365829737</v>
+        <v>0.8726378786485016</v>
       </c>
       <c r="W6" t="n">
-        <v>6.294415707782369</v>
+        <v>6.188852244033998</v>
       </c>
       <c r="X6" t="n">
-        <v>1.5385</v>
+        <v>1.538833333333333</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.048927717267306</v>
+        <v>2.048313577898088</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.066572458475788</v>
+        <v>3.067491899178437</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>0.01093102937162103</v>
+        <v>0.01090726980230729</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8299643665751059</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993387999032885</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -2328,47 +2328,47 @@
         <v>269.75</v>
       </c>
       <c r="AI6" t="n">
-        <v>4000</v>
+        <v>5121</v>
       </c>
       <c r="AJ6" t="n">
-        <v>13230.76923076923</v>
+        <v>14366</v>
       </c>
       <c r="AK6" t="n">
-        <v>5.879749999999996</v>
+        <v>5.888875000000009</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.596043415348079</v>
+        <v>4.542932006854592</v>
       </c>
       <c r="AM6" t="n">
-        <v>4.602574559605379</v>
+        <v>4.558359371553752</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.535464984887695</v>
+        <v>6.470636433382194</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.147082060906366</v>
+        <v>1.18020831889283</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.635367346511142</v>
+        <v>6.577387591513585</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.5385</v>
+        <v>1.541</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.048927717267306</v>
+        <v>2.044331340633068</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.066572458475788</v>
+        <v>3.073467193059748</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
-        <v>0.01204718274560243</v>
+        <v>0.01203881172357057</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8292443039727651</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.993222267452576</v>
+        <v>1.994462811849285</v>
       </c>
       <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="inlineStr"/>
@@ -2379,47 +2379,47 @@
         <v>270.24</v>
       </c>
       <c r="BB6" t="n">
-        <v>4500</v>
+        <v>5517</v>
       </c>
       <c r="BC6" t="n">
-        <v>13730.76923076923</v>
+        <v>14744</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.794249999999988</v>
+        <v>6.839324999999976</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.549836279334752</v>
+        <v>4.549605236901022</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.620921187757665</v>
+        <v>4.595242842112601</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.566138204207187</v>
+        <v>6.530560134178906</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.492162646369344</v>
+        <v>2.540564572743309</v>
       </c>
       <c r="BI6" t="n">
-        <v>7.023179164218141</v>
+        <v>7.007330733910395</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.5385</v>
+        <v>1.538</v>
       </c>
       <c r="BK6" t="n">
-        <v>2.048927717267306</v>
+        <v>2.049849672265102</v>
       </c>
       <c r="BL6" t="n">
-        <v>3.066572458475788</v>
+        <v>3.065193214991523</v>
       </c>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="n">
-        <v>0.01392092714304337</v>
+        <v>0.01401958810976447</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8302413841571755</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.993222267452576</v>
+        <v>1.992973481789027</v>
       </c>
       <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="inlineStr"/>
@@ -2430,47 +2430,47 @@
         <v>270.91</v>
       </c>
       <c r="BU6" t="n">
-        <v>4500</v>
+        <v>5518</v>
       </c>
       <c r="BV6" t="n">
-        <v>13730.76923076923</v>
+        <v>14736</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.53000000000003</v>
+        <v>7.569999999999993</v>
       </c>
       <c r="BX6" t="n">
-        <v>4.518733632716027</v>
+        <v>4.45279367146318</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.548903020302045</v>
+        <v>4.504158528675601</v>
       </c>
       <c r="BZ6" t="n">
-        <v>6.462736505121563</v>
+        <v>6.397566907971834</v>
       </c>
       <c r="CA6" t="n">
-        <v>2.963263150452776</v>
+        <v>2.976077363288172</v>
       </c>
       <c r="CB6" t="n">
-        <v>7.109704046826576</v>
+        <v>7.055912330397295</v>
       </c>
       <c r="CC6" t="n">
-        <v>1.5385</v>
+        <v>1.5365</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.048927717267306</v>
+        <v>2.052620920444372</v>
       </c>
       <c r="CE6" t="n">
-        <v>3.066572458475788</v>
+        <v>3.061054890651382</v>
       </c>
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="n">
-        <v>0.01542842571102288</v>
+        <v>0.01553834036776388</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8307401125255206</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.993222267452576</v>
+        <v>1.992225766776038</v>
       </c>
       <c r="CJ6" t="inlineStr"/>
       <c r="CK6" t="inlineStr"/>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="CO6" t="inlineStr"/>
       <c r="CP6" t="n">
-        <v>0.0120475995482838</v>
+        <v>0.01206629666055528</v>
       </c>
       <c r="CQ6" t="n">
         <v>1.18841919095278</v>
@@ -2502,13 +2502,13 @@
       </c>
       <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
-        <v>1.053359469061065</v>
+        <v>1.062385048538038</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.9899463229918536</v>
+        <v>1.001468925803063</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.9931640075138545</v>
+        <v>0.978720886671085</v>
       </c>
       <c r="DB6" t="inlineStr">
         <is>
@@ -2516,16 +2516,16 @@
         </is>
       </c>
       <c r="DC6" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6498429546193003</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6489292667099286</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6501950585175553</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6508298080052066</v>
       </c>
     </row>
     <row r="7">
@@ -2587,49 +2587,49 @@
         <v>267.07</v>
       </c>
       <c r="P7" t="n">
-        <v>4700</v>
+        <v>4770</v>
       </c>
       <c r="Q7" t="n">
-        <v>9315.384615384615</v>
+        <v>9392</v>
       </c>
       <c r="R7" t="n">
         <v>8.159999999999997</v>
       </c>
       <c r="S7" t="n">
-        <v>7.339747246578904</v>
+        <v>7.307874954477423</v>
       </c>
       <c r="T7" t="n">
-        <v>7.316185202975977</v>
+        <v>7.307283268250005</v>
       </c>
       <c r="U7" t="n">
-        <v>10.36324982099588</v>
+        <v>10.35023178620757</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7991103392193708</v>
+        <v>0.7953106088172969</v>
       </c>
       <c r="W7" t="n">
-        <v>10.3940138631146</v>
+        <v>10.38074260314352</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7705000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.80664920385966</v>
+        <v>6.786173450053408</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9258804469741541</v>
       </c>
       <c r="AA7" t="n">
-        <v>17.83342091411231</v>
+        <v>17.77977443913993</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.05554225750349481</v>
+        <v>0.05537517535243579</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992377189472729</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201661839031998</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -2640,49 +2640,49 @@
         <v>269.75</v>
       </c>
       <c r="AI7" t="n">
-        <v>4800</v>
+        <v>4710</v>
       </c>
       <c r="AJ7" t="n">
-        <v>9415.384615384615</v>
+        <v>9326</v>
       </c>
       <c r="AK7" t="n">
-        <v>8.254999999999967</v>
+        <v>8.416799999999988</v>
       </c>
       <c r="AL7" t="n">
-        <v>7.60281264149442</v>
+        <v>7.608383648386557</v>
       </c>
       <c r="AM7" t="n">
-        <v>7.625314926233843</v>
+        <v>7.62465810481525</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.8093326787666</v>
+        <v>10.81195462793271</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.096343246592233</v>
+        <v>1.114393335703101</v>
       </c>
       <c r="AP7" t="n">
-        <v>10.86478906719316</v>
+        <v>10.86923343125609</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7695000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.80664920385966</v>
+        <v>6.803718262158717</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9234928703802656</v>
       </c>
       <c r="AT7" t="n">
-        <v>17.83342091411231</v>
+        <v>17.82574184685584</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.05618888917786127</v>
+        <v>0.05726553586893741</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992530703381666</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200120689253106</v>
       </c>
       <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr"/>
@@ -2693,49 +2693,49 @@
         <v>270.24</v>
       </c>
       <c r="BB7" t="n">
-        <v>6500</v>
+        <v>6486</v>
       </c>
       <c r="BC7" t="n">
-        <v>11115.38461538462</v>
+        <v>11107</v>
       </c>
       <c r="BD7" t="n">
         <v>5.115000000000009</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.688751939504018</v>
+        <v>4.67834670868055</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.689153081699652</v>
+        <v>4.689232654108475</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.655881727850312</v>
+        <v>6.655553234218701</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.7955391388496366</v>
+        <v>0.7954558296462528</v>
       </c>
       <c r="BI7" t="n">
-        <v>6.703256230860736</v>
+        <v>6.70292017186817</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7703333333333333</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.80664920385966</v>
+        <v>6.789092731771489</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9254823222218832</v>
       </c>
       <c r="BM7" t="n">
-        <v>17.83342091411231</v>
+        <v>17.7874229572413</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.03481601067774222</v>
+        <v>0.03472620932301123</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992402949658459</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.199863797070839</v>
+        <v>1.20140500504788</v>
       </c>
       <c r="BQ7" t="inlineStr"/>
       <c r="BR7" t="inlineStr"/>
@@ -2746,49 +2746,49 @@
         <v>270.91</v>
       </c>
       <c r="BU7" t="n">
-        <v>6500</v>
+        <v>6490</v>
       </c>
       <c r="BV7" t="n">
-        <v>11115.38461538462</v>
+        <v>11107</v>
       </c>
       <c r="BW7" t="n">
         <v>5.534999999999997</v>
       </c>
       <c r="BX7" t="n">
-        <v>4.901609559649972</v>
+        <v>4.898224150009402</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.889209570661445</v>
+        <v>4.889202155093885</v>
       </c>
       <c r="BZ7" t="n">
-        <v>6.928973105497077</v>
+        <v>6.928841457771155</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.6253613134539956</v>
+        <v>0.6255666017009848</v>
       </c>
       <c r="CB7" t="n">
-        <v>6.957136269260989</v>
+        <v>6.957023610718307</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7696666666666667</v>
       </c>
       <c r="CD7" t="n">
-        <v>6.80664920385966</v>
+        <v>6.800789267814117</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9238906044208459</v>
       </c>
       <c r="CF7" t="n">
-        <v>17.83342091411231</v>
+        <v>17.81806788167299</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.03767480334336319</v>
+        <v>0.03764236859735111</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992505291814564</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200377571789752</v>
       </c>
       <c r="CJ7" t="inlineStr"/>
       <c r="CK7" t="inlineStr"/>
@@ -2803,7 +2803,7 @@
         <v>17.83814903173707</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.05620378635762937</v>
+        <v>0.05730539418714671</v>
       </c>
       <c r="CQ7" t="n">
         <v>3.948903220766222</v>
@@ -2822,13 +2822,13 @@
       </c>
       <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="n">
-        <v>1.035841206253816</v>
+        <v>1.041121214550205</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.6167128088773197</v>
+        <v>0.6148936390283954</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.045397500847202</v>
+        <v>1.046998962458442</v>
       </c>
       <c r="DB7" t="inlineStr">
         <is>
@@ -2836,16 +2836,16 @@
         </is>
       </c>
       <c r="DC7" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297858533419857</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.299826689774697</v>
+        <v>1.299545159194282</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298139333621809</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29926375054136</v>
       </c>
     </row>
     <row r="8">
@@ -2907,47 +2907,47 @@
         <v>267.07</v>
       </c>
       <c r="P8" t="n">
-        <v>4700</v>
+        <v>4747</v>
       </c>
       <c r="Q8" t="n">
-        <v>9315.384615384615</v>
+        <v>9364</v>
       </c>
       <c r="R8" t="n">
         <v>15.72999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>14.71438080975368</v>
+        <v>14.71656320450866</v>
       </c>
       <c r="T8" t="n">
-        <v>14.85015015005686</v>
+        <v>14.85289063415684</v>
       </c>
       <c r="U8" t="n">
-        <v>21.01989008409203</v>
+        <v>21.02682335055099</v>
       </c>
       <c r="V8" t="n">
-        <v>1.239465363255359</v>
+        <v>1.249147598106461</v>
       </c>
       <c r="W8" t="n">
-        <v>21.05640172332444</v>
+        <v>21.06389493747848</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7696666666666667</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.80664920385966</v>
+        <v>6.800789267814117</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9238906044208459</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="n">
-        <v>0.1070685919767124</v>
+        <v>0.106976415182716</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992505291814564</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200377571789752</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
@@ -2958,47 +2958,47 @@
         <v>269.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>4800</v>
+        <v>4861</v>
       </c>
       <c r="AJ8" t="n">
-        <v>9415.384615384615</v>
+        <v>9486</v>
       </c>
       <c r="AK8" t="n">
         <v>15.86000000000003</v>
       </c>
       <c r="AL8" t="n">
-        <v>14.66020333941477</v>
+        <v>14.63379638313236</v>
       </c>
       <c r="AM8" t="n">
-        <v>14.7308625449969</v>
+        <v>14.73854153887669</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.86297179818516</v>
+        <v>20.87097800667832</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.648429611045485</v>
+        <v>1.665489877040305</v>
       </c>
       <c r="AP8" t="n">
-        <v>20.92799351190747</v>
+        <v>20.93732503176502</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7710000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.80664920385966</v>
+        <v>6.777427224732707</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9270752896099725</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="n">
-        <v>0.1079534563732144</v>
+        <v>0.1074899957842609</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992299487600118</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.199863797070839</v>
+        <v>1.202432282243803</v>
       </c>
       <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="inlineStr"/>
@@ -3009,47 +3009,47 @@
         <v>270.24</v>
       </c>
       <c r="BB8" t="n">
-        <v>6500</v>
+        <v>6421</v>
       </c>
       <c r="BC8" t="n">
-        <v>11115.38461538462</v>
+        <v>11054</v>
       </c>
       <c r="BD8" t="n">
         <v>17.06</v>
       </c>
       <c r="BE8" t="n">
-        <v>14.85719336291679</v>
+        <v>14.93631719232617</v>
       </c>
       <c r="BF8" t="n">
-        <v>15.02426508508258</v>
+        <v>15.01316519307722</v>
       </c>
       <c r="BG8" t="n">
-        <v>21.29502744064956</v>
+        <v>21.27615477308687</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.71475987265172</v>
+        <v>2.688536212705569</v>
       </c>
       <c r="BI8" t="n">
-        <v>21.46737326419275</v>
+        <v>21.44534888723837</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7723333333333334</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.80664920385966</v>
+        <v>6.754188888208766</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.930264967589011</v>
       </c>
       <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="n">
-        <v>0.1161214354178458</v>
+        <v>0.1152264624328416</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992089169084887</v>
       </c>
       <c r="BP8" t="n">
-        <v>1.199863797070839</v>
+        <v>1.20448636286881</v>
       </c>
       <c r="BQ8" t="inlineStr"/>
       <c r="BR8" t="inlineStr"/>
@@ -3060,47 +3060,47 @@
         <v>270.91</v>
       </c>
       <c r="BU8" t="n">
-        <v>6500</v>
+        <v>6428</v>
       </c>
       <c r="BV8" t="n">
-        <v>11115.38461538462</v>
+        <v>11059</v>
       </c>
       <c r="BW8" t="n">
-        <v>16.72000000000003</v>
+        <v>16.80500000000001</v>
       </c>
       <c r="BX8" t="n">
-        <v>14.86226428457837</v>
+        <v>14.94301024345509</v>
       </c>
       <c r="BY8" t="n">
-        <v>14.98543110176182</v>
+        <v>14.98470275799842</v>
       </c>
       <c r="BZ8" t="n">
-        <v>21.23287617746405</v>
+        <v>21.23187246879726</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.388736426312654</v>
+        <v>2.315954320893213</v>
       </c>
       <c r="CB8" t="n">
-        <v>21.3668222363999</v>
+        <v>21.35781011592095</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7719999999999999</v>
       </c>
       <c r="CD8" t="n">
-        <v>6.80664920385966</v>
+        <v>6.759986919511434</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9294670806306371</v>
       </c>
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="n">
-        <v>0.1138071746885337</v>
+        <v>0.1136015801823897</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992142175731586</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.199863797070839</v>
+        <v>1.203972902371292</v>
       </c>
       <c r="CJ8" t="inlineStr"/>
       <c r="CK8" t="inlineStr"/>
@@ -3132,13 +3132,13 @@
       </c>
       <c r="CX8" t="inlineStr"/>
       <c r="CY8" t="n">
-        <v>0.9963180597920237</v>
+        <v>0.9943759408887703</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.013437059428255</v>
+        <v>1.02067274965931</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.000341310874653</v>
+        <v>1.000448105851177</v>
       </c>
       <c r="DB8" t="inlineStr">
         <is>
@@ -3146,16 +3146,16 @@
         </is>
       </c>
       <c r="DC8" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29926375054136</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297016861219196</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.299826689774697</v>
+        <v>1.294777729823047</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.299826689774697</v>
+        <v>1.295336787564767</v>
       </c>
     </row>
     <row r="9">
@@ -3217,47 +3217,47 @@
         <v>267.07</v>
       </c>
       <c r="P9" t="n">
-        <v>3950</v>
+        <v>5047</v>
       </c>
       <c r="Q9" t="n">
-        <v>13180.76923076923</v>
+        <v>14279</v>
       </c>
       <c r="R9" t="n">
-        <v>15.17000000000003</v>
+        <v>14.95920000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>13.34236128071041</v>
+        <v>13.17393745093398</v>
       </c>
       <c r="T9" t="n">
-        <v>13.39399482130035</v>
+        <v>13.23642807719242</v>
       </c>
       <c r="U9" t="n">
-        <v>18.98196010947251</v>
+        <v>18.74440317326648</v>
       </c>
       <c r="V9" t="n">
-        <v>1.321698376143289</v>
+        <v>1.310841329466313</v>
       </c>
       <c r="W9" t="n">
-        <v>19.02791886137592</v>
+        <v>18.79018241830024</v>
       </c>
       <c r="X9" t="n">
-        <v>1.5385</v>
+        <v>1.538833333333333</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.048927717267306</v>
+        <v>2.048313577898088</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.066572458475788</v>
+        <v>3.067491899178437</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
-        <v>0.03108223347094509</v>
+        <v>0.0306411324744931</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8299643665751059</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993387999032885</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
@@ -3268,47 +3268,47 @@
         <v>269.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>4000</v>
+        <v>5129</v>
       </c>
       <c r="AJ9" t="n">
-        <v>13230.76923076923</v>
+        <v>14365</v>
       </c>
       <c r="AK9" t="n">
-        <v>15.12925</v>
+        <v>14.91500000000001</v>
       </c>
       <c r="AL9" t="n">
-        <v>13.58274509962429</v>
+        <v>13.47105059287713</v>
       </c>
       <c r="AM9" t="n">
-        <v>13.63678546553545</v>
+        <v>13.50021916523973</v>
       </c>
       <c r="AN9" t="n">
-        <v>19.32112978206084</v>
+        <v>19.12027678627677</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.575196165260816</v>
+        <v>1.553034428994947</v>
       </c>
       <c r="AP9" t="n">
-        <v>19.38523404589923</v>
+        <v>19.1832453021244</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.5385</v>
+        <v>1.5395</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.048927717267306</v>
+        <v>2.047086490905204</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.066572458475788</v>
+        <v>3.069330648751053</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AU9" t="n">
-        <v>0.03099873966646639</v>
+        <v>0.03053229501185113</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8297427805022363</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993719161254338</v>
       </c>
       <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
@@ -3319,47 +3319,47 @@
         <v>270.24</v>
       </c>
       <c r="BB9" t="n">
-        <v>4500</v>
+        <v>5501</v>
       </c>
       <c r="BC9" t="n">
-        <v>13730.76923076923</v>
+        <v>14730</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.719275</v>
+        <v>16.7193</v>
       </c>
       <c r="BE9" t="n">
-        <v>13.41008538350529</v>
+        <v>13.32765962201304</v>
       </c>
       <c r="BF9" t="n">
-        <v>13.45912521292168</v>
+        <v>13.30182454363211</v>
       </c>
       <c r="BG9" t="n">
-        <v>19.06802552325554</v>
+        <v>18.84422575600894</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.569359263258281</v>
+        <v>3.572415255348489</v>
       </c>
       <c r="BI9" t="n">
-        <v>19.3992248016701</v>
+        <v>19.17985910011012</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.538333333333333</v>
+        <v>1.538166666666667</v>
       </c>
       <c r="BK9" t="n">
-        <v>2.049234936091632</v>
+        <v>2.04954225440786</v>
       </c>
       <c r="BL9" t="n">
-        <v>3.066112721639952</v>
+        <v>3.065652973812381</v>
       </c>
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="n">
-        <v>0.03426172243612341</v>
+        <v>0.03426691181412134</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.8301305724820542</v>
+        <v>0.8301859775481096</v>
       </c>
       <c r="BP9" t="n">
-        <v>1.99313936401297</v>
+        <v>1.993056435461511</v>
       </c>
       <c r="BQ9" t="inlineStr"/>
       <c r="BR9" t="inlineStr"/>
@@ -3370,47 +3370,47 @@
         <v>270.91</v>
       </c>
       <c r="BU9" t="n">
-        <v>4500</v>
+        <v>5502</v>
       </c>
       <c r="BV9" t="n">
-        <v>13730.76923076923</v>
+        <v>14737</v>
       </c>
       <c r="BW9" t="n">
-        <v>16.064925</v>
+        <v>16.10904999999999</v>
       </c>
       <c r="BX9" t="n">
-        <v>13.44412625445492</v>
+        <v>13.32661336949928</v>
       </c>
       <c r="BY9" t="n">
-        <v>13.46053141068109</v>
+        <v>13.31286858551258</v>
       </c>
       <c r="BZ9" t="n">
-        <v>19.07416042829668</v>
+        <v>18.86318916814841</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.628731464360361</v>
+        <v>2.717945901979148</v>
       </c>
       <c r="CB9" t="n">
-        <v>19.25444948982227</v>
+        <v>19.05799400565119</v>
       </c>
       <c r="CC9" t="n">
-        <v>1.538333333333333</v>
+        <v>1.539166666666667</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.049234936091632</v>
+        <v>2.047699835907966</v>
       </c>
       <c r="CE9" t="n">
-        <v>3.066112721639952</v>
+        <v>3.068411295932723</v>
       </c>
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="n">
-        <v>0.03292080555569186</v>
+        <v>0.03298649904163319</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.8301305724820542</v>
+        <v>0.8298535704129305</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.99313936401297</v>
+        <v>1.993553630275727</v>
       </c>
       <c r="CJ9" t="inlineStr"/>
       <c r="CK9" t="inlineStr"/>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="CO9" t="inlineStr"/>
       <c r="CP9" t="n">
-        <v>0.03099981214607301</v>
+        <v>0.03056081419493228</v>
       </c>
       <c r="CQ9" t="n">
         <v>1.18841919095278</v>
@@ -3442,13 +3442,13 @@
       </c>
       <c r="CX9" t="inlineStr"/>
       <c r="CY9" t="n">
-        <v>1.018016587458279</v>
+        <v>1.022553101003382</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.9872883047681009</v>
+        <v>0.989355620790267</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.002538452961045</v>
+        <v>0.9999214976564949</v>
       </c>
       <c r="DB9" t="inlineStr">
         <is>
@@ -3456,16 +3456,16 @@
         </is>
       </c>
       <c r="DC9" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6498429546193003</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6495615459564794</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.6500541711809318</v>
+        <v>0.6501246072163831</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.6500541711809318</v>
+        <v>0.6497022198159177</v>
       </c>
     </row>
     <row r="10">
@@ -3527,49 +3527,49 @@
         <v>267.07</v>
       </c>
       <c r="P10" t="n">
-        <v>4700</v>
+        <v>4741</v>
       </c>
       <c r="Q10" t="n">
-        <v>9315.384615384615</v>
+        <v>9364</v>
       </c>
       <c r="R10" t="n">
-        <v>25.244375</v>
+        <v>25.21137499999999</v>
       </c>
       <c r="S10" t="n">
-        <v>22.6482402209212</v>
+        <v>22.50103671947776</v>
       </c>
       <c r="T10" t="n">
-        <v>22.67554175709782</v>
+        <v>22.66566481051209</v>
       </c>
       <c r="U10" t="n">
-        <v>32.18540846511858</v>
+        <v>32.15487022691579</v>
       </c>
       <c r="V10" t="n">
-        <v>4.4378719425192</v>
+        <v>4.406762862592141</v>
       </c>
       <c r="W10" t="n">
-        <v>32.48992498367341</v>
+        <v>32.45543464871357</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7706666666666666</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.80664920385966</v>
+        <v>6.783256106042011</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9262786498040373</v>
       </c>
       <c r="AA10" t="n">
-        <v>17.83342091411231</v>
+        <v>17.77213099783007</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.1718296049956847</v>
+        <v>0.1710152134104648</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992351359158013</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201918663240533</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
@@ -3580,49 +3580,49 @@
         <v>269.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>4800</v>
+        <v>4871</v>
       </c>
       <c r="AJ10" t="n">
-        <v>9415.384615384615</v>
+        <v>9487</v>
       </c>
       <c r="AK10" t="n">
-        <v>24.39625000000003</v>
+        <v>24.39600000000002</v>
       </c>
       <c r="AL10" t="n">
-        <v>22.68834636195292</v>
+        <v>22.68709127985836</v>
       </c>
       <c r="AM10" t="n">
-        <v>22.6737892847746</v>
+        <v>22.6827281347699</v>
       </c>
       <c r="AN10" t="n">
-        <v>32.13009974038984</v>
+        <v>32.13697649325827</v>
       </c>
       <c r="AO10" t="n">
-        <v>2.347779565915675</v>
+        <v>2.362610761264061</v>
       </c>
       <c r="AP10" t="n">
-        <v>32.21576288430139</v>
+        <v>32.22370536945551</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7695000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.80664920385966</v>
+        <v>6.803718262158717</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9234928703802656</v>
       </c>
       <c r="AT10" t="n">
-        <v>17.83342091411231</v>
+        <v>17.82574184685584</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1660567156396614</v>
+        <v>0.1659835107236242</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992530703381666</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200120689253106</v>
       </c>
       <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
@@ -3633,49 +3633,49 @@
         <v>270.24</v>
       </c>
       <c r="BB10" t="n">
-        <v>6500</v>
+        <v>6457</v>
       </c>
       <c r="BC10" t="n">
-        <v>11115.38461538462</v>
+        <v>11076</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.36774999999999</v>
+        <v>18.36714999999998</v>
       </c>
       <c r="BE10" t="n">
-        <v>16.89847724403939</v>
+        <v>16.91665190573246</v>
       </c>
       <c r="BF10" t="n">
-        <v>16.97109999832063</v>
+        <v>16.96552682144387</v>
       </c>
       <c r="BG10" t="n">
-        <v>24.04124881107238</v>
+        <v>24.03607099260673</v>
       </c>
       <c r="BH10" t="n">
-        <v>1.797604702785872</v>
+        <v>1.78746691384603</v>
       </c>
       <c r="BI10" t="n">
-        <v>24.10836010730235</v>
+        <v>24.10244275441236</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.77</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.80664920385966</v>
+        <v>6.794937114744855</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9246863070366348</v>
       </c>
       <c r="BM10" t="n">
-        <v>17.83342091411231</v>
+        <v>17.80273524063152</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.1250228309141933</v>
+        <v>0.1248036292270858</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992454260183794</v>
       </c>
       <c r="BP10" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200891307839786</v>
       </c>
       <c r="BQ10" t="inlineStr"/>
       <c r="BR10" t="inlineStr"/>
@@ -3686,49 +3686,49 @@
         <v>270.91</v>
       </c>
       <c r="BU10" t="n">
-        <v>6500</v>
+        <v>6458</v>
       </c>
       <c r="BV10" t="n">
-        <v>11115.38461538462</v>
+        <v>11079</v>
       </c>
       <c r="BW10" t="n">
         <v>18.38999999999999</v>
       </c>
       <c r="BX10" t="n">
-        <v>16.88695209138847</v>
+        <v>16.90001960058247</v>
       </c>
       <c r="BY10" t="n">
-        <v>17.01501697347112</v>
+        <v>17.02152864722367</v>
       </c>
       <c r="BZ10" t="n">
-        <v>24.11694553739132</v>
+        <v>24.12921766722367</v>
       </c>
       <c r="CA10" t="n">
-        <v>2.435433754881125</v>
+        <v>2.453783984273847</v>
       </c>
       <c r="CB10" t="n">
-        <v>24.23960394948551</v>
+        <v>24.25366366291364</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7703333333333333</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.80664920385966</v>
+        <v>6.789092731771489</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9254823222218832</v>
       </c>
       <c r="CF10" t="n">
-        <v>17.83342091411231</v>
+        <v>17.7874229572413</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.1251742788589791</v>
+        <v>0.1248514153372776</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992402949658459</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.199863797070839</v>
+        <v>1.20140500504788</v>
       </c>
       <c r="CJ10" t="inlineStr"/>
       <c r="CK10" t="inlineStr"/>
@@ -3743,7 +3743,7 @@
         <v>17.83814903173707</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.1661007417234794</v>
+        <v>0.1660990396100221</v>
       </c>
       <c r="CQ10" t="n">
         <v>3.948903220766222</v>
@@ -3762,13 +3762,13 @@
       </c>
       <c r="CX10" t="inlineStr"/>
       <c r="CY10" t="n">
-        <v>1.001770828136779</v>
+        <v>1.008268710579879</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.7448086773030396</v>
+        <v>0.7456509826251326</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.999317976851732</v>
+        <v>0.9990168086898832</v>
       </c>
       <c r="DB10" t="inlineStr">
         <is>
@@ -3776,16 +3776,16 @@
         </is>
       </c>
       <c r="DC10" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29757785467128</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.299826689774697</v>
+        <v>1.299545159194282</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298701298701299</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298139333621809</v>
       </c>
     </row>
     <row r="11">
@@ -3847,47 +3847,47 @@
         <v>267.07</v>
       </c>
       <c r="P11" t="n">
-        <v>3950</v>
+        <v>5064</v>
       </c>
       <c r="Q11" t="n">
-        <v>13180.76923076923</v>
+        <v>14294</v>
       </c>
       <c r="R11" t="n">
-        <v>14.74</v>
+        <v>14.2696</v>
       </c>
       <c r="S11" t="n">
-        <v>8.949520001553489</v>
+        <v>8.80558353251822</v>
       </c>
       <c r="T11" t="n">
-        <v>9.056370404375429</v>
+        <v>8.843752625390998</v>
       </c>
       <c r="U11" t="n">
-        <v>12.86679951932784</v>
+        <v>12.57274111697775</v>
       </c>
       <c r="V11" t="n">
-        <v>6.207920835161549</v>
+        <v>5.809959189289969</v>
       </c>
       <c r="W11" t="n">
-        <v>14.28610552131714</v>
+        <v>13.85025071887718</v>
       </c>
       <c r="X11" t="n">
-        <v>1.537666666666667</v>
+        <v>1.5375</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.050464806799213</v>
+        <v>2.050772523574458</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.064273664363776</v>
+        <v>3.063813872553798</v>
       </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="n">
-        <v>0.0302238512522204</v>
+        <v>0.0292637036023981</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.8303522019910555</v>
+        <v>0.8304076132092216</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.992807499044294</v>
+        <v>1.99272446995369</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
@@ -3898,47 +3898,47 @@
         <v>269.75</v>
       </c>
       <c r="AI11" t="n">
-        <v>4000</v>
+        <v>5151</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13230.76923076923</v>
+        <v>14369</v>
       </c>
       <c r="AK11" t="n">
-        <v>16.98</v>
+        <v>17.2378</v>
       </c>
       <c r="AL11" t="n">
-        <v>8.985991629870817</v>
+        <v>8.817411570393162</v>
       </c>
       <c r="AM11" t="n">
-        <v>9.064947755661191</v>
+        <v>8.832133088633983</v>
       </c>
       <c r="AN11" t="n">
-        <v>12.94613938230397</v>
+        <v>12.58194247812296</v>
       </c>
       <c r="AO11" t="n">
-        <v>8.023044825219912</v>
+        <v>7.832492633534812</v>
       </c>
       <c r="AP11" t="n">
-        <v>15.23061959256845</v>
+        <v>14.82070232401866</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.537666666666667</v>
+        <v>1.535333333333333</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.050464806799213</v>
+        <v>2.054781935753712</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.064273664363776</v>
+        <v>3.057835577513416</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AU11" t="n">
-        <v>0.03481689241945064</v>
+        <v>0.03541992005213533</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.8303522019910555</v>
+        <v>0.8311280970339954</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.992807499044294</v>
+        <v>1.991642799075173</v>
       </c>
       <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
@@ -3949,47 +3949,47 @@
         <v>270.24</v>
       </c>
       <c r="BB11" t="n">
-        <v>4500</v>
+        <v>5779</v>
       </c>
       <c r="BC11" t="n">
-        <v>13730.76923076923</v>
+        <v>15046</v>
       </c>
       <c r="BD11" t="n">
-        <v>20.32784999999998</v>
+        <v>19.55999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.677282735004802</v>
+        <v>8.468706341183472</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.935431188847973</v>
+        <v>8.746571759509946</v>
       </c>
       <c r="BG11" t="n">
-        <v>13.2267547045151</v>
+        <v>12.87451180301145</v>
       </c>
       <c r="BH11" t="n">
-        <v>12.1497646666926</v>
+        <v>11.60223562844283</v>
       </c>
       <c r="BI11" t="n">
-        <v>17.96006184481068</v>
+        <v>17.33103937286478</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.538</v>
+        <v>1.544333333333333</v>
       </c>
       <c r="BK11" t="n">
-        <v>2.049849672265102</v>
+        <v>2.038237359052525</v>
       </c>
       <c r="BL11" t="n">
-        <v>3.065193214991523</v>
+        <v>3.082656335030737</v>
       </c>
       <c r="BM11" t="inlineStr"/>
       <c r="BN11" t="n">
-        <v>0.04166903666035412</v>
+        <v>0.03986792274306736</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.8302413841571755</v>
+        <v>0.828137045526201</v>
       </c>
       <c r="BP11" t="n">
-        <v>1.992973481789027</v>
+        <v>1.996108138375181</v>
       </c>
       <c r="BQ11" t="inlineStr"/>
       <c r="BR11" t="inlineStr"/>
@@ -4000,47 +4000,47 @@
         <v>270.91</v>
       </c>
       <c r="BU11" t="n">
-        <v>4500</v>
+        <v>5710</v>
       </c>
       <c r="BV11" t="n">
-        <v>13730.76923076923</v>
+        <v>14796</v>
       </c>
       <c r="BW11" t="n">
-        <v>23.47392499999999</v>
+        <v>25.90819999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>8.997452548869104</v>
+        <v>6.925214803601146</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.160826529836175</v>
+        <v>9.101527748822935</v>
       </c>
       <c r="BZ11" t="n">
-        <v>13.64121728142971</v>
+        <v>13.72712335736595</v>
       </c>
       <c r="CA11" t="n">
-        <v>12.25864561536327</v>
+        <v>13.32856273149075</v>
       </c>
       <c r="CB11" t="n">
-        <v>18.34004365431668</v>
+        <v>19.13333478920039</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.538</v>
+        <v>1.514166666666667</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.049849672265102</v>
+        <v>2.094860323398477</v>
       </c>
       <c r="CE11" t="n">
-        <v>3.065193214991523</v>
+        <v>2.999333767984311</v>
       </c>
       <c r="CF11" t="inlineStr"/>
       <c r="CG11" t="n">
-        <v>0.04811801746802558</v>
+        <v>0.05427406023067239</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.8302413841571755</v>
+        <v>0.8381787136343422</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.992973481789027</v>
+        <v>1.980847837964322</v>
       </c>
       <c r="CJ11" t="inlineStr"/>
       <c r="CK11" t="inlineStr"/>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="CO11" t="inlineStr"/>
       <c r="CP11" t="n">
-        <v>0.03479199631444519</v>
+        <v>0.03532022815483764</v>
       </c>
       <c r="CQ11" t="n">
         <v>1.18841919095278</v>
@@ -4072,13 +4072,13 @@
       </c>
       <c r="CX11" t="inlineStr"/>
       <c r="CY11" t="n">
-        <v>1.00407526083086</v>
+        <v>1.001343242935719</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.9656455394594605</v>
+        <v>0.9604526536585224</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.036897473972205</v>
+        <v>0.8177417570761312</v>
       </c>
       <c r="DB11" t="inlineStr">
         <is>
@@ -4086,16 +4086,16 @@
         </is>
       </c>
       <c r="DC11" t="n">
-        <v>0.6503360069369173</v>
+        <v>0.6504065040650406</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.6503360069369173</v>
+        <v>0.6513243595310465</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.6501950585175553</v>
+        <v>0.6475285991797971</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.6501950585175553</v>
+        <v>0.6604292790313704</v>
       </c>
     </row>
     <row r="12">
@@ -4157,49 +4157,49 @@
         <v>267.07</v>
       </c>
       <c r="P12" t="n">
-        <v>4700</v>
+        <v>4719</v>
       </c>
       <c r="Q12" t="n">
-        <v>9315.384615384615</v>
+        <v>9343</v>
       </c>
       <c r="R12" t="n">
-        <v>23.511625</v>
+        <v>23.5096</v>
       </c>
       <c r="S12" t="n">
-        <v>21.62726161096047</v>
+        <v>21.51671037162325</v>
       </c>
       <c r="T12" t="n">
-        <v>21.60616729994833</v>
+        <v>21.60761383440697</v>
       </c>
       <c r="U12" t="n">
-        <v>30.6109041819793</v>
+        <v>30.61451744834389</v>
       </c>
       <c r="V12" t="n">
-        <v>2.64934773785407</v>
+        <v>2.662584264318246</v>
       </c>
       <c r="W12" t="n">
-        <v>30.72533967711977</v>
+        <v>30.73008352672586</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7708333333333333</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.80664920385966</v>
+        <v>6.780340698135218</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9266769306898748</v>
       </c>
       <c r="AA12" t="n">
-        <v>17.83342091411231</v>
+        <v>17.76449262911427</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.1600353835876969</v>
+        <v>0.1594030976768797</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992325458578962</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.199863797070839</v>
+        <v>1.202175477651729</v>
       </c>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
@@ -4210,49 +4210,49 @@
         <v>269.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>4800</v>
+        <v>4839</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9415.384615384615</v>
+        <v>9461</v>
       </c>
       <c r="AK12" t="n">
-        <v>24.32662500000001</v>
+        <v>24.32505000000002</v>
       </c>
       <c r="AL12" t="n">
-        <v>21.73698970217838</v>
+        <v>21.74624224480129</v>
       </c>
       <c r="AM12" t="n">
-        <v>21.67705767475349</v>
+        <v>21.71565975374388</v>
       </c>
       <c r="AN12" t="n">
-        <v>30.72351589564856</v>
+        <v>30.78613627013437</v>
       </c>
       <c r="AO12" t="n">
-        <v>2.802584576050716</v>
+        <v>2.818175421857043</v>
       </c>
       <c r="AP12" t="n">
-        <v>30.85107630693113</v>
+        <v>30.91485563853796</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7705000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.80664920385966</v>
+        <v>6.786173450053408</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9258804469741541</v>
       </c>
       <c r="AT12" t="n">
-        <v>17.83342091411231</v>
+        <v>17.77977443913993</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1655828026888426</v>
+        <v>0.1650740084812218</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992377189472729</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201661839031998</v>
       </c>
       <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="inlineStr"/>
@@ -4263,49 +4263,49 @@
         <v>270.24</v>
       </c>
       <c r="BB12" t="n">
-        <v>6500</v>
+        <v>6424</v>
       </c>
       <c r="BC12" t="n">
-        <v>11115.38461538462</v>
+        <v>11054</v>
       </c>
       <c r="BD12" t="n">
         <v>18.05500000000001</v>
       </c>
       <c r="BE12" t="n">
-        <v>16.46844497352365</v>
+        <v>16.4818129152392</v>
       </c>
       <c r="BF12" t="n">
-        <v>16.54812443571277</v>
+        <v>16.50852342198739</v>
       </c>
       <c r="BG12" t="n">
-        <v>23.43632427230977</v>
+        <v>23.38344005303008</v>
       </c>
       <c r="BH12" t="n">
-        <v>1.078808720365104</v>
+        <v>1.076637041080579</v>
       </c>
       <c r="BI12" t="n">
-        <v>23.46114071506311</v>
+        <v>23.40821257661247</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7718333333333335</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.80664920385966</v>
+        <v>6.762888819396453</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9290682539625607</v>
       </c>
       <c r="BM12" t="n">
-        <v>17.83342091411231</v>
+        <v>17.71876870681871</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.1228940513756862</v>
+        <v>0.122103957634203</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992168571960084</v>
       </c>
       <c r="BP12" t="n">
-        <v>1.199863797070839</v>
+        <v>1.203716157152961</v>
       </c>
       <c r="BQ12" t="inlineStr"/>
       <c r="BR12" t="inlineStr"/>
@@ -4316,49 +4316,49 @@
         <v>270.91</v>
       </c>
       <c r="BU12" t="n">
-        <v>6500</v>
+        <v>6426</v>
       </c>
       <c r="BV12" t="n">
-        <v>11115.38461538462</v>
+        <v>11058</v>
       </c>
       <c r="BW12" t="n">
         <v>17.88500000000002</v>
       </c>
       <c r="BX12" t="n">
-        <v>16.22077318945988</v>
+        <v>16.18302381602922</v>
       </c>
       <c r="BY12" t="n">
-        <v>16.26361159357308</v>
+        <v>16.24005111450129</v>
       </c>
       <c r="BZ12" t="n">
-        <v>23.03461230032809</v>
+        <v>23.00156480122491</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.253046707961946</v>
+        <v>1.254472113255822</v>
       </c>
       <c r="CB12" t="n">
-        <v>23.06866900969278</v>
+        <v>23.0357479493913</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7721666666666667</v>
       </c>
       <c r="CD12" t="n">
-        <v>6.80664920385966</v>
+        <v>6.757086942977636</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9298659851801143</v>
       </c>
       <c r="CF12" t="n">
-        <v>17.83342091411231</v>
+        <v>17.70356779060141</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.1217369210110301</v>
+        <v>0.1208504999751551</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.999211570815197</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.199863797070839</v>
+        <v>1.204229637617243</v>
       </c>
       <c r="CJ12" t="inlineStr"/>
       <c r="CK12" t="inlineStr"/>
@@ -4373,7 +4373,7 @@
         <v>17.83814903173707</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.1656267031256416</v>
+        <v>0.1656159798108611</v>
       </c>
       <c r="CQ12" t="n">
         <v>3.948903220766222</v>
@@ -4392,13 +4392,13 @@
       </c>
       <c r="CX12" t="inlineStr"/>
       <c r="CY12" t="n">
-        <v>1.005073600772568</v>
+        <v>1.010667609927991</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.7576230747293065</v>
+        <v>0.7579154471701606</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.9849608275424936</v>
+        <v>0.9818715877466537</v>
       </c>
       <c r="DB12" t="inlineStr">
         <is>
@@ -4406,16 +4406,16 @@
         </is>
       </c>
       <c r="DC12" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297297297297297</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297858533419857</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.299826689774697</v>
+        <v>1.295616497516735</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.299826689774697</v>
+        <v>1.295057198359594</v>
       </c>
     </row>
     <row r="13">
@@ -4477,49 +4477,49 @@
         <v>267.07</v>
       </c>
       <c r="P13" t="n">
-        <v>3950</v>
+        <v>5098</v>
       </c>
       <c r="Q13" t="n">
-        <v>13180.76923076923</v>
+        <v>14320</v>
       </c>
       <c r="R13" t="n">
-        <v>12.25930000000002</v>
+        <v>12.29952500000001</v>
       </c>
       <c r="S13" t="n">
-        <v>4.261073917698683</v>
+        <v>4.219332674425106</v>
       </c>
       <c r="T13" t="n">
-        <v>4.411084372039525</v>
+        <v>4.271921166353996</v>
       </c>
       <c r="U13" t="n">
-        <v>6.375032499974193</v>
+        <v>6.171069340336396</v>
       </c>
       <c r="V13" t="n">
-        <v>7.731190903664412</v>
+        <v>7.975758317970523</v>
       </c>
       <c r="W13" t="n">
-        <v>10.02059639765172</v>
+        <v>10.08438483745617</v>
       </c>
       <c r="X13" t="n">
-        <v>1.538166666666667</v>
+        <v>1.536666666666667</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.04954225440786</v>
+        <v>2.052312604502923</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.065652973812381</v>
+        <v>3.061514748481212</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.369800706548593</v>
+        <v>5.377059023797657</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.02512595335946232</v>
+        <v>0.02524247018689883</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.8301859775481096</v>
+        <v>0.8306846921790945</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.993056435461511</v>
+        <v>1.992308946950897</v>
       </c>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
@@ -4530,49 +4530,49 @@
         <v>269.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>4000</v>
+        <v>5179</v>
       </c>
       <c r="AJ13" t="n">
-        <v>13230.76923076923</v>
+        <v>14449</v>
       </c>
       <c r="AK13" t="n">
-        <v>15.32980000000027</v>
+        <v>13.41332499999999</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.293759711557178</v>
+        <v>4.291489326050145</v>
       </c>
       <c r="AM13" t="n">
-        <v>4.541198352360786</v>
+        <v>4.467453041308216</v>
       </c>
       <c r="AN13" t="n">
-        <v>6.92103455656352</v>
+        <v>6.774943545463522</v>
       </c>
       <c r="AO13" t="n">
-        <v>8.95637559956911</v>
+        <v>9.206629465256761</v>
       </c>
       <c r="AP13" t="n">
-        <v>11.31889496433744</v>
+        <v>11.43074302723807</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.538166666666667</v>
+        <v>1.544666666666667</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.04954225440786</v>
+        <v>2.037630117632625</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.065652973812381</v>
+        <v>3.083575008441455</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.369800706548593</v>
+        <v>5.338590908197479</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.03141907285162217</v>
+        <v>0.02733139499759462</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.8301859775481096</v>
+        <v>0.8280263558608252</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.993056435461511</v>
+        <v>1.996272124584455</v>
       </c>
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
@@ -4583,28 +4583,28 @@
         <v>270.24</v>
       </c>
       <c r="BB13" t="n">
-        <v>4500</v>
+        <v>5518</v>
       </c>
       <c r="BC13" t="n">
-        <v>13730.76923076923</v>
+        <v>14748</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.844750000000007</v>
+        <v>4.775000000000006</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.251186981047182</v>
+        <v>4.207510904285438</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.266561156867178</v>
+        <v>4.218248421129818</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.067995164570938</v>
+        <v>5.996216266165737</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.5296876785975138</v>
+        <v>0.5258219450962408</v>
       </c>
       <c r="BI13" t="n">
-        <v>6.091070050008809</v>
+        <v>6.019227378042416</v>
       </c>
       <c r="BJ13" t="n">
         <v>1.5385</v>
@@ -4619,7 +4619,7 @@
         <v>5.368190619240342</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.009926542558230797</v>
+        <v>0.009783629849951398</v>
       </c>
       <c r="BO13" t="n">
         <v>0.8300751689623258</v>
@@ -4636,49 +4636,49 @@
         <v>270.91</v>
       </c>
       <c r="BU13" t="n">
-        <v>4500</v>
+        <v>5515</v>
       </c>
       <c r="BV13" t="n">
-        <v>13730.76923076923</v>
+        <v>14751</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.114999999999981</v>
+        <v>5.034999999999997</v>
       </c>
       <c r="BX13" t="n">
-        <v>4.241434286160534</v>
+        <v>4.196311850391721</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.256654602010928</v>
+        <v>4.20282599796499</v>
       </c>
       <c r="BZ13" t="n">
-        <v>6.048498216437993</v>
+        <v>5.970285477587423</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.6722502683128709</v>
+        <v>0.6698233068513603</v>
       </c>
       <c r="CB13" t="n">
-        <v>6.08574162263732</v>
+        <v>6.007742666450734</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.5385</v>
+        <v>1.5395</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.048927717267306</v>
+        <v>2.047086490905204</v>
       </c>
       <c r="CE13" t="n">
-        <v>3.066572458475788</v>
+        <v>3.069330648751053</v>
       </c>
       <c r="CF13" t="n">
-        <v>5.368190619240342</v>
+        <v>5.363366606171634</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.01048026527382223</v>
+        <v>0.01030708048170769</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8297427805022363</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993719161254338</v>
       </c>
       <c r="CJ13" t="inlineStr"/>
       <c r="CK13" t="inlineStr"/>
@@ -4693,7 +4693,7 @@
         <v>5.368376345338421</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.03141073881632457</v>
+        <v>0.02748388421463223</v>
       </c>
       <c r="CQ13" t="n">
         <v>1.18841919095278</v>
@@ -4712,13 +4712,13 @@
       </c>
       <c r="CX13" t="inlineStr"/>
       <c r="CY13" t="n">
-        <v>1.007670787808381</v>
+        <v>1.017101436931581</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.9900849760187077</v>
+        <v>0.9804314037891363</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.9977058889834469</v>
+        <v>0.9973383185098083</v>
       </c>
       <c r="DB13" t="inlineStr">
         <is>
@@ -4726,16 +4726,16 @@
         </is>
       </c>
       <c r="DC13" t="n">
-        <v>0.6501246072163831</v>
+        <v>0.6507592190889371</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.6501246072163831</v>
+        <v>0.6473888649115235</v>
       </c>
       <c r="DE13" t="n">
         <v>0.6499837504062399</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6495615459564794</v>
       </c>
     </row>
     <row r="14">
@@ -4797,47 +4797,47 @@
         <v>267.07</v>
       </c>
       <c r="P14" t="n">
-        <v>4700</v>
+        <v>4738</v>
       </c>
       <c r="Q14" t="n">
-        <v>9315.384615384615</v>
+        <v>9352</v>
       </c>
       <c r="R14" t="n">
-        <v>23.242</v>
+        <v>23.2422</v>
       </c>
       <c r="S14" t="n">
-        <v>22.1122891230417</v>
+        <v>22.09735270549447</v>
       </c>
       <c r="T14" t="n">
-        <v>22.09637764759881</v>
+        <v>22.0955379574271</v>
       </c>
       <c r="U14" t="n">
-        <v>31.28109203716476</v>
+        <v>31.27913044424479</v>
       </c>
       <c r="V14" t="n">
-        <v>1.686114846005677</v>
+        <v>1.684796536419902</v>
       </c>
       <c r="W14" t="n">
-        <v>31.32650159707422</v>
+        <v>31.32447191441882</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7691666666666667</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.80664920385966</v>
+        <v>6.809582094531432</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9226976369409542</v>
       </c>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="n">
-        <v>0.1582001407961063</v>
+        <v>0.1582696689575185</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992581318692667</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.199863797070839</v>
+        <v>1.199606895264513</v>
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
@@ -4848,28 +4848,28 @@
         <v>269.75</v>
       </c>
       <c r="AI14" t="n">
-        <v>4800</v>
+        <v>4861</v>
       </c>
       <c r="AJ14" t="n">
-        <v>9415.384615384615</v>
+        <v>9476</v>
       </c>
       <c r="AK14" t="n">
         <v>23.33462500000001</v>
       </c>
       <c r="AL14" t="n">
-        <v>22.09538369415444</v>
+        <v>22.10703735414898</v>
       </c>
       <c r="AM14" t="n">
-        <v>22.05957554436484</v>
+        <v>22.06685483396075</v>
       </c>
       <c r="AN14" t="n">
-        <v>31.23955534988487</v>
+        <v>31.24474449700218</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.719209878158818</v>
+        <v>1.687908746419012</v>
       </c>
       <c r="AP14" t="n">
-        <v>31.28682631817551</v>
+        <v>31.29030352392233</v>
       </c>
       <c r="AQ14" t="n">
         <v>0.7693333333333332</v>
@@ -4899,47 +4899,47 @@
         <v>270.24</v>
       </c>
       <c r="BB14" t="n">
-        <v>6500</v>
+        <v>6434</v>
       </c>
       <c r="BC14" t="n">
-        <v>11115.38461538462</v>
+        <v>11055</v>
       </c>
       <c r="BD14" t="n">
-        <v>23.06720000000001</v>
+        <v>23.06600000000001</v>
       </c>
       <c r="BE14" t="n">
-        <v>21.79539959322593</v>
+        <v>21.77183803770708</v>
       </c>
       <c r="BF14" t="n">
-        <v>21.8684372430595</v>
+        <v>21.86993166331974</v>
       </c>
       <c r="BG14" t="n">
-        <v>30.96553943047279</v>
+        <v>30.97538031305208</v>
       </c>
       <c r="BH14" t="n">
-        <v>1.806977928917386</v>
+        <v>1.815541872331563</v>
       </c>
       <c r="BI14" t="n">
-        <v>31.01821725141147</v>
+        <v>31.02854134226106</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.7701666666666668</v>
       </c>
       <c r="BK14" t="n">
-        <v>6.809582094531432</v>
+        <v>6.792013952800097</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.9250842755688481</v>
       </c>
       <c r="BM14" t="inlineStr"/>
       <c r="BN14" t="n">
-        <v>0.1570779920909755</v>
+        <v>0.1566645938352871</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.9992428639850438</v>
       </c>
       <c r="BP14" t="n">
-        <v>1.199606895264513</v>
+        <v>1.201148161309909</v>
       </c>
       <c r="BQ14" t="inlineStr"/>
       <c r="BR14" t="inlineStr"/>
@@ -4950,47 +4950,47 @@
         <v>270.91</v>
       </c>
       <c r="BU14" t="n">
-        <v>6500</v>
+        <v>6438</v>
       </c>
       <c r="BV14" t="n">
-        <v>11115.38461538462</v>
+        <v>11060</v>
       </c>
       <c r="BW14" t="n">
-        <v>42.75235000000056</v>
+        <v>42.68602499999914</v>
       </c>
       <c r="BX14" t="n">
-        <v>21.4194360626002</v>
+        <v>21.36139496597642</v>
       </c>
       <c r="BY14" t="n">
-        <v>22.18808379095429</v>
+        <v>22.0743888342505</v>
       </c>
       <c r="BZ14" t="n">
-        <v>32.50291687337342</v>
+        <v>32.15638392630895</v>
       </c>
       <c r="CA14" t="n">
-        <v>10.05115313943184</v>
+        <v>9.413865902771539</v>
       </c>
       <c r="CB14" t="n">
-        <v>34.02154148050516</v>
+        <v>33.50602779279492</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.7703333333333333</v>
       </c>
       <c r="CD14" t="n">
-        <v>6.809582094531432</v>
+        <v>6.789092731771489</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.9254823222218832</v>
       </c>
       <c r="CF14" t="inlineStr"/>
       <c r="CG14" t="n">
-        <v>0.2911256370591447</v>
+        <v>0.2897993820757103</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.9992402949658459</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.199606895264513</v>
+        <v>1.20140500504788</v>
       </c>
       <c r="CJ14" t="inlineStr"/>
       <c r="CK14" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>0.9992354735960082</v>
+        <v>1.000438271895443</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.9864232228287636</v>
+        <v>0.9848374383653457</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.9827503263237907</v>
+        <v>0.9811479824983167</v>
       </c>
       <c r="DB14" t="inlineStr">
         <is>
@@ -5036,16 +5036,16 @@
         </is>
       </c>
       <c r="DC14" t="n">
-        <v>1.299826689774697</v>
+        <v>1.300108342361864</v>
       </c>
       <c r="DD14" t="n">
         <v>1.299826689774697</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.300108342361864</v>
+        <v>1.298420255355983</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.300108342361864</v>
+        <v>1.298139333621809</v>
       </c>
     </row>
     <row r="15">
@@ -5107,47 +5107,47 @@
         <v>267.07</v>
       </c>
       <c r="P15" t="n">
-        <v>4700</v>
+        <v>4757</v>
       </c>
       <c r="Q15" t="n">
-        <v>9315.384615384615</v>
+        <v>9356</v>
       </c>
       <c r="R15" t="n">
-        <v>12.299625</v>
+        <v>12.300225</v>
       </c>
       <c r="S15" t="n">
-        <v>7.761761149918128</v>
+        <v>7.769052167737289</v>
       </c>
       <c r="T15" t="n">
-        <v>7.855892829145151</v>
+        <v>7.847234781388924</v>
       </c>
       <c r="U15" t="n">
-        <v>11.15536455801334</v>
+        <v>11.15173796973871</v>
       </c>
       <c r="V15" t="n">
-        <v>5.021202587783492</v>
+        <v>5.007646262518834</v>
       </c>
       <c r="W15" t="n">
-        <v>12.23334107469189</v>
+        <v>12.22447466504107</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7666666666666668</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.80664920385966</v>
+        <v>6.853810434441637</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9167433746935054</v>
       </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="n">
-        <v>0.08371923271402236</v>
+        <v>0.08430341045097989</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992952203627681</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.199863797070839</v>
+        <v>1.195752227861094</v>
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
@@ -5158,47 +5158,47 @@
         <v>269.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>4800</v>
+        <v>4883</v>
       </c>
       <c r="AJ15" t="n">
-        <v>9415.384615384615</v>
+        <v>9500</v>
       </c>
       <c r="AK15" t="n">
-        <v>13.35737500000001</v>
+        <v>13.357025</v>
       </c>
       <c r="AL15" t="n">
-        <v>8.015388978118187</v>
+        <v>7.976161091819552</v>
       </c>
       <c r="AM15" t="n">
-        <v>7.991172991691751</v>
+        <v>7.967169440888641</v>
       </c>
       <c r="AN15" t="n">
-        <v>11.35890238313253</v>
+        <v>11.34053353272692</v>
       </c>
       <c r="AO15" t="n">
-        <v>5.704652389098189</v>
+        <v>5.722991596632061</v>
       </c>
       <c r="AP15" t="n">
-        <v>12.71092924337075</v>
+        <v>12.70276873842962</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7696666666666667</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.80664920385966</v>
+        <v>6.800789267814117</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9238906044208459</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AU15" t="n">
-        <v>0.09091896590940497</v>
+        <v>0.09083831226992484</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992505291814564</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200377571789752</v>
       </c>
       <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="inlineStr"/>
@@ -5209,47 +5209,47 @@
         <v>270.24</v>
       </c>
       <c r="BB15" t="n">
-        <v>6500</v>
+        <v>6466</v>
       </c>
       <c r="BC15" t="n">
-        <v>11115.38461538462</v>
+        <v>11062</v>
       </c>
       <c r="BD15" t="n">
-        <v>16.88899999999999</v>
+        <v>16.90289999999996</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.10094130269877</v>
+        <v>7.877565270709157</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.365758839410089</v>
+        <v>8.36962875337559</v>
       </c>
       <c r="BG15" t="n">
-        <v>12.19041201358914</v>
+        <v>12.19954130514084</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.775572833906914</v>
+        <v>9.682427079698948</v>
       </c>
       <c r="BI15" t="n">
-        <v>15.62587499284687</v>
+        <v>15.5749222216204</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7661666666666667</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.80664920385966</v>
+        <v>6.862709251881989</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9155546412601587</v>
       </c>
       <c r="BM15" t="inlineStr"/>
       <c r="BN15" t="n">
-        <v>0.1149574984039857</v>
+        <v>0.1159996882136358</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9993024555960097</v>
       </c>
       <c r="BP15" t="n">
-        <v>1.199863797070839</v>
+        <v>1.194981041453329</v>
       </c>
       <c r="BQ15" t="inlineStr"/>
       <c r="BR15" t="inlineStr"/>
@@ -5260,47 +5260,47 @@
         <v>270.91</v>
       </c>
       <c r="BU15" t="n">
-        <v>6500</v>
+        <v>6457</v>
       </c>
       <c r="BV15" t="n">
-        <v>11115.38461538462</v>
+        <v>11063</v>
       </c>
       <c r="BW15" t="n">
-        <v>21.27025000000001</v>
+        <v>21.27610000000001</v>
       </c>
       <c r="BX15" t="n">
-        <v>8.937259407844577</v>
+        <v>8.893125306091168</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.036135744522666</v>
+        <v>9.027128430671004</v>
       </c>
       <c r="BZ15" t="n">
-        <v>13.00489980056927</v>
+        <v>13.01259859926421</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.19054677551302</v>
+        <v>9.26803322584961</v>
       </c>
       <c r="CB15" t="n">
-        <v>15.924621466639</v>
+        <v>15.97573667099659</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7678333333333333</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.80664920385966</v>
+        <v>6.833115577184387</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9195198348699084</v>
       </c>
       <c r="CF15" t="inlineStr"/>
       <c r="CG15" t="n">
-        <v>0.144779130228396</v>
+        <v>0.1453820503317328</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992781028658503</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.199863797070839</v>
+        <v>1.197551336926297</v>
       </c>
       <c r="CJ15" t="inlineStr"/>
       <c r="CK15" t="inlineStr"/>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="CO15" t="inlineStr"/>
       <c r="CP15" t="n">
-        <v>0.09094307096290041</v>
+        <v>0.09094068800406024</v>
       </c>
       <c r="CQ15" t="n">
         <v>3.948903220766222</v>
@@ -5332,13 +5332,13 @@
       </c>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="n">
-        <v>1.03267658245355</v>
+        <v>1.026658197114743</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.010673508773453</v>
+        <v>0.9876386873365037</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.103237151572397</v>
+        <v>1.128918009623878</v>
       </c>
       <c r="DB15" t="inlineStr">
         <is>
@@ -5346,16 +5346,16 @@
         </is>
       </c>
       <c r="DC15" t="n">
-        <v>1.299826689774697</v>
+        <v>1.304347826086956</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29926375054136</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.299826689774697</v>
+        <v>1.305199042854035</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.299826689774697</v>
+        <v>1.302365964836119</v>
       </c>
     </row>
     <row r="16">
@@ -5417,49 +5417,49 @@
         <v>267.07</v>
       </c>
       <c r="P16" t="n">
-        <v>4700</v>
+        <v>4743</v>
       </c>
       <c r="Q16" t="n">
-        <v>9315.384615384615</v>
+        <v>9366</v>
       </c>
       <c r="R16" t="n">
         <v>18.39500000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>15.22788159962651</v>
+        <v>15.21750530459957</v>
       </c>
       <c r="T16" t="n">
-        <v>15.21149911679266</v>
+        <v>15.21052477591373</v>
       </c>
       <c r="U16" t="n">
-        <v>21.54978582622927</v>
+        <v>21.54417890702291</v>
       </c>
       <c r="V16" t="n">
-        <v>3.480842184243873</v>
+        <v>3.508512327603225</v>
       </c>
       <c r="W16" t="n">
-        <v>21.82909827427518</v>
+        <v>21.82799357546989</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7706666666666666</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.80664920385966</v>
+        <v>6.783256106042011</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9262786498040373</v>
       </c>
       <c r="AA16" t="n">
-        <v>17.83342091411231</v>
+        <v>17.77213099783007</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.1252083121049985</v>
+        <v>0.1247779960706429</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992351359158013</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201918663240533</v>
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
@@ -5470,49 +5470,49 @@
         <v>269.75</v>
       </c>
       <c r="AI16" t="n">
-        <v>4800</v>
+        <v>4866</v>
       </c>
       <c r="AJ16" t="n">
-        <v>9415.384615384615</v>
+        <v>9493</v>
       </c>
       <c r="AK16" t="n">
-        <v>21.786625</v>
+        <v>21.78392499999998</v>
       </c>
       <c r="AL16" t="n">
-        <v>16.01552329012716</v>
+        <v>16.06852338855956</v>
       </c>
       <c r="AM16" t="n">
-        <v>15.95575982947705</v>
+        <v>15.96380710587578</v>
       </c>
       <c r="AN16" t="n">
-        <v>22.67288361775881</v>
+        <v>22.66609829661789</v>
       </c>
       <c r="AO16" t="n">
-        <v>5.748406209746252</v>
+        <v>5.720768880043837</v>
       </c>
       <c r="AP16" t="n">
-        <v>23.39025065057417</v>
+        <v>23.37689475894569</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7713333333333333</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.80664920385966</v>
+        <v>6.771606075048078</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9278722414659917</v>
       </c>
       <c r="AT16" t="n">
-        <v>17.83342091411231</v>
+        <v>17.74160791662597</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.148293913711039</v>
+        <v>0.1475121588683916</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992247333900647</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.199863797070839</v>
+        <v>1.202945861883308</v>
       </c>
       <c r="AX16" t="inlineStr"/>
       <c r="AY16" t="inlineStr"/>
@@ -5523,49 +5523,49 @@
         <v>270.24</v>
       </c>
       <c r="BB16" t="n">
-        <v>6500</v>
+        <v>6465</v>
       </c>
       <c r="BC16" t="n">
-        <v>11115.38461538462</v>
+        <v>11089</v>
       </c>
       <c r="BD16" t="n">
-        <v>11.68700000000001</v>
+        <v>11.68520000000001</v>
       </c>
       <c r="BE16" t="n">
-        <v>10.77293285334049</v>
+        <v>10.74932533288856</v>
       </c>
       <c r="BF16" t="n">
-        <v>10.8558044965617</v>
+        <v>10.8496859957852</v>
       </c>
       <c r="BG16" t="n">
-        <v>15.37015332211904</v>
+        <v>15.36082675091604</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.8080004328579442</v>
+        <v>0.8077631034153114</v>
       </c>
       <c r="BI16" t="n">
-        <v>15.39137673650235</v>
+        <v>15.38205056885775</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7708333333333333</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.80664920385966</v>
+        <v>6.780340698135218</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9266769306898748</v>
       </c>
       <c r="BM16" t="n">
-        <v>17.83342091411231</v>
+        <v>17.76449262911427</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.0795493092455079</v>
+        <v>0.07922963712584968</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992325458578962</v>
       </c>
       <c r="BP16" t="n">
-        <v>1.199863797070839</v>
+        <v>1.202175477651729</v>
       </c>
       <c r="BQ16" t="inlineStr"/>
       <c r="BR16" t="inlineStr"/>
@@ -5576,49 +5576,49 @@
         <v>270.91</v>
       </c>
       <c r="BU16" t="n">
-        <v>6500</v>
+        <v>6471</v>
       </c>
       <c r="BV16" t="n">
-        <v>11115.38461538462</v>
+        <v>11092</v>
       </c>
       <c r="BW16" t="n">
         <v>12.38</v>
       </c>
       <c r="BX16" t="n">
-        <v>11.12745602780424</v>
+        <v>11.11949677147902</v>
       </c>
       <c r="BY16" t="n">
-        <v>11.11256991163929</v>
+        <v>11.09972333191264</v>
       </c>
       <c r="BZ16" t="n">
-        <v>15.74533015402419</v>
+        <v>15.72630245218208</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.083096421729366</v>
+        <v>1.085981856922313</v>
       </c>
       <c r="CB16" t="n">
-        <v>15.7825384370825</v>
+        <v>15.76375416615828</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7703333333333333</v>
       </c>
       <c r="CD16" t="n">
-        <v>6.80664920385966</v>
+        <v>6.789092731771489</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9254823222218832</v>
       </c>
       <c r="CF16" t="n">
-        <v>17.83342091411231</v>
+        <v>17.7874229572413</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.08426631714378256</v>
+        <v>0.084048968019331</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992402949658459</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.199863797070839</v>
+        <v>1.20140500504788</v>
       </c>
       <c r="CJ16" t="inlineStr"/>
       <c r="CK16" t="inlineStr"/>
@@ -5633,7 +5633,7 @@
         <v>17.83814903173707</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.1483332304002171</v>
+        <v>0.1483148475748789</v>
       </c>
       <c r="CQ16" t="n">
         <v>3.948903220766222</v>
@@ -5652,13 +5652,13 @@
       </c>
       <c r="CX16" t="inlineStr"/>
       <c r="CY16" t="n">
-        <v>1.051723654754445</v>
+        <v>1.055923626568592</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.6726556889952833</v>
+        <v>0.6689678368668178</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.032908696200943</v>
+        <v>1.034436713665916</v>
       </c>
       <c r="DB16" t="inlineStr">
         <is>
@@ -5666,16 +5666,16 @@
         </is>
       </c>
       <c r="DC16" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29757785467128</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.299826689774697</v>
+        <v>1.296456352636128</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297297297297297</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298139333621809</v>
       </c>
     </row>
     <row r="17">
@@ -5737,47 +5737,47 @@
         <v>267.07</v>
       </c>
       <c r="P17" t="n">
-        <v>4700</v>
+        <v>4726</v>
       </c>
       <c r="Q17" t="n">
-        <v>9315.384615384615</v>
+        <v>9350</v>
       </c>
       <c r="R17" t="n">
-        <v>27.81720000000002</v>
+        <v>27.52000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>24.27713150545992</v>
+        <v>24.28046269008109</v>
       </c>
       <c r="T17" t="n">
-        <v>24.4962075568862</v>
+        <v>24.51634530759659</v>
       </c>
       <c r="U17" t="n">
-        <v>34.69463712785483</v>
+        <v>34.73229827299512</v>
       </c>
       <c r="V17" t="n">
-        <v>3.800174759501049</v>
+        <v>3.836847218008981</v>
       </c>
       <c r="W17" t="n">
-        <v>34.90213709268061</v>
+        <v>34.94358224193167</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.7706666666666666</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.809582094531432</v>
+        <v>6.783256106042011</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.9262786498040373</v>
       </c>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="n">
-        <v>0.1894235070399999</v>
+        <v>0.1866752080382762</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.9992351359158013</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.199606895264513</v>
+        <v>1.201918663240533</v>
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
@@ -5788,47 +5788,47 @@
         <v>269.75</v>
       </c>
       <c r="AI17" t="n">
-        <v>4800</v>
+        <v>4842</v>
       </c>
       <c r="AJ17" t="n">
-        <v>9415.384615384615</v>
+        <v>9476</v>
       </c>
       <c r="AK17" t="n">
-        <v>27.12720000000001</v>
+        <v>27.12340000000001</v>
       </c>
       <c r="AL17" t="n">
-        <v>23.46343181048738</v>
+        <v>23.66091690441088</v>
       </c>
       <c r="AM17" t="n">
-        <v>23.74099395023659</v>
+        <v>23.74889649650783</v>
       </c>
       <c r="AN17" t="n">
-        <v>33.67917348837931</v>
+        <v>33.69136123099948</v>
       </c>
       <c r="AO17" t="n">
-        <v>4.486208550236003</v>
+        <v>4.514545421647359</v>
       </c>
       <c r="AP17" t="n">
-        <v>33.97665071805287</v>
+        <v>33.99248360978956</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.7723333333333334</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.809582094531432</v>
+        <v>6.754188888208766</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.930264967589011</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AU17" t="n">
-        <v>0.1847248953947731</v>
+        <v>0.1831965668904417</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.9992089169084887</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.199606895264513</v>
+        <v>1.20448636286881</v>
       </c>
       <c r="AX17" t="inlineStr"/>
       <c r="AY17" t="inlineStr"/>
@@ -5839,47 +5839,47 @@
         <v>270.24</v>
       </c>
       <c r="BB17" t="n">
-        <v>6500</v>
+        <v>6394</v>
       </c>
       <c r="BC17" t="n">
-        <v>11115.38461538462</v>
+        <v>11042</v>
       </c>
       <c r="BD17" t="n">
-        <v>27.556625</v>
+        <v>27.54920000000001</v>
       </c>
       <c r="BE17" t="n">
-        <v>22.11850797631879</v>
+        <v>22.10371972359066</v>
       </c>
       <c r="BF17" t="n">
-        <v>22.87924946670939</v>
+        <v>22.93447380870298</v>
       </c>
       <c r="BG17" t="n">
-        <v>32.5493067869264</v>
+        <v>32.63733054698385</v>
       </c>
       <c r="BH17" t="n">
-        <v>6.091155426264211</v>
+        <v>6.148872777644255</v>
       </c>
       <c r="BI17" t="n">
-        <v>33.11434049979497</v>
+        <v>33.21150375500543</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7748333333333334</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.80664920385966</v>
+        <v>6.710947605091348</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9362590317964584</v>
       </c>
       <c r="BM17" t="inlineStr"/>
       <c r="BN17" t="n">
-        <v>0.1875682796173092</v>
+        <v>0.1848812377621826</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9991682411536307</v>
       </c>
       <c r="BP17" t="n">
-        <v>1.199863797070839</v>
+        <v>1.208336027270112</v>
       </c>
       <c r="BQ17" t="inlineStr"/>
       <c r="BR17" t="inlineStr"/>
@@ -5890,47 +5890,47 @@
         <v>270.91</v>
       </c>
       <c r="BU17" t="n">
-        <v>6500</v>
+        <v>6409</v>
       </c>
       <c r="BV17" t="n">
-        <v>11115.38461538462</v>
+        <v>11045</v>
       </c>
       <c r="BW17" t="n">
-        <v>30.260625</v>
+        <v>30.24749999999996</v>
       </c>
       <c r="BX17" t="n">
-        <v>24.03741789332936</v>
+        <v>23.99582944913972</v>
       </c>
       <c r="BY17" t="n">
-        <v>23.53030938910445</v>
+        <v>23.42246728704156</v>
       </c>
       <c r="BZ17" t="n">
-        <v>33.4695742737002</v>
+        <v>33.30557737221249</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.138112826502566</v>
+        <v>6.126057895159853</v>
       </c>
       <c r="CB17" t="n">
-        <v>34.0277655912581</v>
+        <v>33.86428899934684</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7728333333333333</v>
       </c>
       <c r="CD17" t="n">
-        <v>6.80664920385966</v>
+        <v>6.745506238654865</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9314623817518741</v>
       </c>
       <c r="CF17" t="inlineStr"/>
       <c r="CG17" t="n">
-        <v>0.2059734590645457</v>
+        <v>0.2040346999537128</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992009121593767</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.199863797070839</v>
+        <v>1.205256478436758</v>
       </c>
       <c r="CJ17" t="inlineStr"/>
       <c r="CK17" t="inlineStr"/>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="CO17" t="inlineStr"/>
       <c r="CP17" t="n">
-        <v>0.1846942887075336</v>
+        <v>0.1846684165829838</v>
       </c>
       <c r="CQ17" t="n">
         <v>3.948903220766222</v>
@@ -5962,13 +5962,13 @@
       </c>
       <c r="CX17" t="inlineStr"/>
       <c r="CY17" t="n">
-        <v>0.9664828732014924</v>
+        <v>0.9744837734940156</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.9426800032905907</v>
+        <v>0.9341869468917359</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.086755848046579</v>
+        <v>1.085601416829841</v>
       </c>
       <c r="DB17" t="inlineStr">
         <is>
@@ -5976,16 +5976,16 @@
         </is>
       </c>
       <c r="DC17" t="n">
-        <v>1.300108342361864</v>
+        <v>1.29757785467128</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.300108342361864</v>
+        <v>1.294777729823047</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.299826689774697</v>
+        <v>1.290600129060013</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.299826689774697</v>
+        <v>1.293940047444468</v>
       </c>
     </row>
     <row r="18">
@@ -6047,47 +6047,47 @@
         <v>267.07</v>
       </c>
       <c r="P18" t="n">
-        <v>4700</v>
+        <v>4758</v>
       </c>
       <c r="Q18" t="n">
-        <v>9315.384615384615</v>
+        <v>9379</v>
       </c>
       <c r="R18" t="n">
         <v>8.210000000000008</v>
       </c>
       <c r="S18" t="n">
-        <v>7.551678839750839</v>
+        <v>7.555000242828524</v>
       </c>
       <c r="T18" t="n">
-        <v>7.531851371688052</v>
+        <v>7.535663736574103</v>
       </c>
       <c r="U18" t="n">
-        <v>10.67515103381216</v>
+        <v>10.67469275090859</v>
       </c>
       <c r="V18" t="n">
-        <v>0.726351004725253</v>
+        <v>0.7271529984205775</v>
       </c>
       <c r="W18" t="n">
-        <v>10.69983342752429</v>
+        <v>10.69943067688242</v>
       </c>
       <c r="X18" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7703333333333333</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.80664920385966</v>
+        <v>6.789092731771489</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9254823222218832</v>
       </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="n">
-        <v>0.05588258996368787</v>
+        <v>0.05573845132784398</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992402949658459</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.199863797070839</v>
+        <v>1.20140500504788</v>
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
@@ -6098,47 +6098,47 @@
         <v>269.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>4800</v>
+        <v>4881</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9415.384615384615</v>
+        <v>9503</v>
       </c>
       <c r="AK18" t="n">
         <v>8.164999999999964</v>
       </c>
       <c r="AL18" t="n">
-        <v>7.609347386095625</v>
+        <v>7.589288517497514</v>
       </c>
       <c r="AM18" t="n">
-        <v>7.607411329953437</v>
+        <v>7.607934248467553</v>
       </c>
       <c r="AN18" t="n">
-        <v>10.77979051703337</v>
+        <v>10.7735399666837</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.6204568875897931</v>
+        <v>0.6192805728911696</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.79763170053879</v>
+        <v>10.79132391515015</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7705000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>6.80664920385966</v>
+        <v>6.786173450053408</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9258804469741541</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AU18" t="n">
-        <v>0.05557629074951388</v>
+        <v>0.05540910621968583</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992377189472729</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201661839031998</v>
       </c>
       <c r="AX18" t="inlineStr"/>
       <c r="AY18" t="inlineStr"/>
@@ -6149,47 +6149,47 @@
         <v>270.24</v>
       </c>
       <c r="BB18" t="n">
-        <v>6500</v>
+        <v>6473</v>
       </c>
       <c r="BC18" t="n">
-        <v>11115.38461538462</v>
+        <v>11093</v>
       </c>
       <c r="BD18" t="n">
         <v>8.554999999999978</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.698499412050772</v>
+        <v>7.668339561357168</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.696868177334972</v>
+        <v>7.698368785431813</v>
       </c>
       <c r="BG18" t="n">
-        <v>10.9103697831253</v>
+        <v>10.91079099799287</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.7007111115608249</v>
+        <v>0.7018847432707319</v>
       </c>
       <c r="BI18" t="n">
-        <v>10.93284797600325</v>
+        <v>10.9333436054447</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7701666666666668</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.80664920385966</v>
+        <v>6.792013952800097</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9250842755688481</v>
       </c>
       <c r="BM18" t="inlineStr"/>
       <c r="BN18" t="n">
-        <v>0.05823088393901925</v>
+        <v>0.05810567936620469</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992428639850438</v>
       </c>
       <c r="BP18" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201148161309909</v>
       </c>
       <c r="BQ18" t="inlineStr"/>
       <c r="BR18" t="inlineStr"/>
@@ -6200,47 +6200,47 @@
         <v>270.91</v>
       </c>
       <c r="BU18" t="n">
-        <v>6500</v>
+        <v>6477</v>
       </c>
       <c r="BV18" t="n">
-        <v>11115.38461538462</v>
+        <v>11098</v>
       </c>
       <c r="BW18" t="n">
         <v>7.955000000000013</v>
       </c>
       <c r="BX18" t="n">
-        <v>7.345211461986906</v>
+        <v>7.315867258526938</v>
       </c>
       <c r="BY18" t="n">
-        <v>7.323912286181622</v>
+        <v>7.322268085218201</v>
       </c>
       <c r="BZ18" t="n">
-        <v>10.38406580322753</v>
+        <v>10.38003521247927</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.6571628220757708</v>
+        <v>0.658948364971629</v>
       </c>
       <c r="CB18" t="n">
-        <v>10.40483952689699</v>
+        <v>10.40092995649949</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7703333333333333</v>
       </c>
       <c r="CD18" t="n">
-        <v>6.80664920385966</v>
+        <v>6.789092731771489</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9254823222218832</v>
       </c>
       <c r="CF18" t="inlineStr"/>
       <c r="CG18" t="n">
-        <v>0.05414689441670368</v>
+        <v>0.05400723268124228</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992402949658459</v>
       </c>
       <c r="CI18" t="n">
-        <v>1.199863797070839</v>
+        <v>1.20140500504788</v>
       </c>
       <c r="CJ18" t="inlineStr"/>
       <c r="CK18" t="inlineStr"/>
@@ -6272,13 +6272,13 @@
       </c>
       <c r="CX18" t="inlineStr"/>
       <c r="CY18" t="n">
-        <v>1.007636519980329</v>
+        <v>1.004538487566766</v>
       </c>
       <c r="CZ18" t="n">
-        <v>1.011716119849917</v>
+        <v>1.010416133696512</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.9541095048327406</v>
+        <v>0.9540353814525333</v>
       </c>
       <c r="DB18" t="inlineStr">
         <is>
@@ -6286,16 +6286,16 @@
         </is>
       </c>
       <c r="DC18" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298139333621809</v>
       </c>
       <c r="DD18" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297858533419857</v>
       </c>
       <c r="DE18" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298420255355983</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298139333621809</v>
       </c>
     </row>
     <row r="19">
@@ -6357,49 +6357,49 @@
         <v>267.07</v>
       </c>
       <c r="P19" t="n">
-        <v>3950</v>
+        <v>5048</v>
       </c>
       <c r="Q19" t="n">
-        <v>13180.76923076923</v>
+        <v>14284</v>
       </c>
       <c r="R19" t="n">
-        <v>10.08725000000001</v>
+        <v>10.04689999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>8.812191496365029</v>
+        <v>8.710776461898638</v>
       </c>
       <c r="T19" t="n">
-        <v>8.841171667550981</v>
+        <v>8.741078863918359</v>
       </c>
       <c r="U19" t="n">
-        <v>12.5402392680147</v>
+        <v>12.39813826935689</v>
       </c>
       <c r="V19" t="n">
-        <v>1.118825791849999</v>
+        <v>1.115229045238322</v>
       </c>
       <c r="W19" t="n">
-        <v>12.59005051822933</v>
+        <v>12.44819538605636</v>
       </c>
       <c r="X19" t="n">
-        <v>1.5385</v>
+        <v>1.5395</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.048927717267306</v>
+        <v>2.047086490905204</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.066572458475788</v>
+        <v>3.069330648751053</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.368190619240342</v>
+        <v>5.363366606171634</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.02066804611600465</v>
+        <v>0.02056687326547547</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8297427805022363</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993719161254338</v>
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
@@ -6410,49 +6410,49 @@
         <v>269.75</v>
       </c>
       <c r="AI19" t="n">
-        <v>4000</v>
+        <v>5131</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13230.76923076923</v>
+        <v>14370</v>
       </c>
       <c r="AK19" t="n">
-        <v>10.60999999999999</v>
+        <v>10.56999999999999</v>
       </c>
       <c r="AL19" t="n">
-        <v>9.095132435982649</v>
+        <v>9.029223531307466</v>
       </c>
       <c r="AM19" t="n">
-        <v>9.151582569433106</v>
+        <v>9.069817230949797</v>
       </c>
       <c r="AN19" t="n">
-        <v>12.98023564984582</v>
+        <v>12.86018379438165</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.636966297160097</v>
+        <v>1.700041649426572</v>
       </c>
       <c r="AP19" t="n">
-        <v>13.0830491928895</v>
+        <v>12.97206494105937</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.5385</v>
+        <v>1.54</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.048927717267306</v>
+        <v>2.046167216896666</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.066572458475788</v>
+        <v>3.070709595625828</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.368190619240342</v>
+        <v>5.360958108269264</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.02173912308020609</v>
+        <v>0.02162798748259774</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8295766074154407</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993967269886901</v>
       </c>
       <c r="AX19" t="inlineStr"/>
       <c r="AY19" t="inlineStr"/>
@@ -6463,49 +6463,49 @@
         <v>270.24</v>
       </c>
       <c r="BB19" t="n">
-        <v>4500</v>
+        <v>5507</v>
       </c>
       <c r="BC19" t="n">
-        <v>13730.76923076923</v>
+        <v>14746</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.460000000000008</v>
+        <v>9.41500000000002</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.849660428528253</v>
+        <v>8.789580797595271</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.871616719342853</v>
+        <v>8.80597972656747</v>
       </c>
       <c r="BG19" t="n">
-        <v>12.56139678312541</v>
+        <v>12.47034319855418</v>
       </c>
       <c r="BH19" t="n">
-        <v>0.2260608553286635</v>
+        <v>0.2239277592415758</v>
       </c>
       <c r="BI19" t="n">
-        <v>12.56343076764565</v>
+        <v>12.47235355220038</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1.5385</v>
+        <v>1.54</v>
       </c>
       <c r="BK19" t="n">
-        <v>2.048927717267306</v>
+        <v>2.046167216896666</v>
       </c>
       <c r="BL19" t="n">
-        <v>3.066572458475788</v>
+        <v>3.070709595625828</v>
       </c>
       <c r="BM19" t="n">
-        <v>5.368190619240342</v>
+        <v>5.360958108269264</v>
       </c>
       <c r="BN19" t="n">
-        <v>0.01938285620534873</v>
+        <v>0.01926466434708215</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8295766074154407</v>
       </c>
       <c r="BP19" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993967269886901</v>
       </c>
       <c r="BQ19" t="inlineStr"/>
       <c r="BR19" t="inlineStr"/>
@@ -6516,49 +6516,49 @@
         <v>270.91</v>
       </c>
       <c r="BU19" t="n">
-        <v>4500</v>
+        <v>5510</v>
       </c>
       <c r="BV19" t="n">
-        <v>13730.76923076923</v>
+        <v>14747</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.449000000000009</v>
+        <v>9.277600000000021</v>
       </c>
       <c r="BX19" t="n">
-        <v>8.87956429623226</v>
+        <v>8.825091733776114</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.902348742211538</v>
+        <v>8.838161248022562</v>
       </c>
       <c r="BZ19" t="n">
-        <v>12.6045991204172</v>
+        <v>12.51462919671556</v>
       </c>
       <c r="CA19" t="n">
-        <v>0.2133504870090559</v>
+        <v>0.2135928795008081</v>
       </c>
       <c r="CB19" t="n">
-        <v>12.6064046189518</v>
+        <v>12.51645180749956</v>
       </c>
       <c r="CC19" t="n">
-        <v>1.5385</v>
+        <v>1.539666666666667</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.048927717267306</v>
+        <v>2.046779967151801</v>
       </c>
       <c r="CE19" t="n">
-        <v>3.066572458475788</v>
+        <v>3.069790308688119</v>
       </c>
       <c r="CF19" t="n">
-        <v>5.368190619240342</v>
+        <v>5.36256351393772</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.01936031800045879</v>
+        <v>0.01898920582324759</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8296873878994435</v>
       </c>
       <c r="CI19" t="n">
-        <v>1.993222267452576</v>
+        <v>1.99380188916743</v>
       </c>
       <c r="CJ19" t="inlineStr"/>
       <c r="CK19" t="inlineStr"/>
@@ -6573,7 +6573,7 @@
         <v>5.368376345338421</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.02173987520001548</v>
+        <v>0.02165791525581185</v>
       </c>
       <c r="CQ19" t="n">
         <v>1.18841919095278</v>
@@ -6592,13 +6592,13 @@
       </c>
       <c r="CX19" t="inlineStr"/>
       <c r="CY19" t="n">
-        <v>1.032107897307308</v>
+        <v>1.036557828203</v>
       </c>
       <c r="CZ19" t="n">
-        <v>0.9730106175822965</v>
+        <v>0.9734592091023918</v>
       </c>
       <c r="DA19" t="n">
-        <v>1.003379097756972</v>
+        <v>1.004040117156732</v>
       </c>
       <c r="DB19" t="inlineStr">
         <is>
@@ -6606,16 +6606,16 @@
         </is>
       </c>
       <c r="DC19" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6495615459564794</v>
       </c>
       <c r="DD19" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6493506493506493</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6493506493506493</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6494912318683699</v>
       </c>
     </row>
     <row r="20">
@@ -6677,49 +6677,49 @@
         <v>267.07</v>
       </c>
       <c r="P20" t="n">
-        <v>4700</v>
+        <v>4743</v>
       </c>
       <c r="Q20" t="n">
-        <v>9315.384615384615</v>
+        <v>9364</v>
       </c>
       <c r="R20" t="n">
         <v>8.899999999999977</v>
       </c>
       <c r="S20" t="n">
-        <v>7.455529913526702</v>
+        <v>7.471921013012451</v>
       </c>
       <c r="T20" t="n">
-        <v>7.452869947601279</v>
+        <v>7.452181347254492</v>
       </c>
       <c r="U20" t="n">
-        <v>10.56882212579766</v>
+        <v>10.56157550002987</v>
       </c>
       <c r="V20" t="n">
-        <v>1.253481746021161</v>
+        <v>1.257281774822397</v>
       </c>
       <c r="W20" t="n">
-        <v>10.64289517069291</v>
+        <v>10.63614754053984</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7703333333333333</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.80664920385966</v>
+        <v>6.789092731771489</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9254823222218832</v>
       </c>
       <c r="AA20" t="n">
-        <v>17.83342091411231</v>
+        <v>17.7874229572413</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.06057917791435082</v>
+        <v>0.0604229253127661</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992402949658459</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.199863797070839</v>
+        <v>1.20140500504788</v>
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
@@ -6730,49 +6730,49 @@
         <v>269.75</v>
       </c>
       <c r="AI20" t="n">
-        <v>4800</v>
+        <v>4866</v>
       </c>
       <c r="AJ20" t="n">
-        <v>9415.384615384615</v>
+        <v>9488</v>
       </c>
       <c r="AK20" t="n">
-        <v>8.810000000000002</v>
+        <v>8.900000000000006</v>
       </c>
       <c r="AL20" t="n">
-        <v>7.324812144965379</v>
+        <v>7.33881470617789</v>
       </c>
       <c r="AM20" t="n">
-        <v>7.336503056667386</v>
+        <v>7.326445539447213</v>
       </c>
       <c r="AN20" t="n">
-        <v>10.40902383815001</v>
+        <v>10.38523418239339</v>
       </c>
       <c r="AO20" t="n">
-        <v>1.17869778149832</v>
+        <v>1.178978224413979</v>
       </c>
       <c r="AP20" t="n">
-        <v>10.47554799155081</v>
+        <v>10.45194138314956</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7705000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.80664920385966</v>
+        <v>6.786173450053408</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9258804469741541</v>
       </c>
       <c r="AT20" t="n">
-        <v>17.83342091411231</v>
+        <v>17.77977443913993</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.05996657948600362</v>
+        <v>0.06039694370547536</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992377189472729</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201661839031998</v>
       </c>
       <c r="AX20" t="inlineStr"/>
       <c r="AY20" t="inlineStr"/>
@@ -6783,49 +6783,49 @@
         <v>270.24</v>
       </c>
       <c r="BB20" t="n">
-        <v>6500</v>
+        <v>6466</v>
       </c>
       <c r="BC20" t="n">
-        <v>11115.38461538462</v>
+        <v>11091</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.896624999999978</v>
+        <v>4.894374999999979</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.307227937470112</v>
+        <v>4.268590163673013</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.234225030360803</v>
+        <v>4.229035513733343</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.011086568265278</v>
+        <v>6.003025429351559</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.5847949403967285</v>
+        <v>0.5856220639332077</v>
       </c>
       <c r="BI20" t="n">
-        <v>6.039465775504722</v>
+        <v>6.03152281826131</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7710000000000001</v>
       </c>
       <c r="BK20" t="n">
-        <v>6.80664920385966</v>
+        <v>6.777427224732707</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9270752896099725</v>
       </c>
       <c r="BM20" t="n">
-        <v>17.83342091411231</v>
+        <v>17.75685932879969</v>
       </c>
       <c r="BN20" t="n">
-        <v>0.03332960865784916</v>
+        <v>0.033171270373051</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992299487600118</v>
       </c>
       <c r="BP20" t="n">
-        <v>1.199863797070839</v>
+        <v>1.202432282243803</v>
       </c>
       <c r="BQ20" t="inlineStr"/>
       <c r="BR20" t="inlineStr"/>
@@ -6836,49 +6836,49 @@
         <v>270.91</v>
       </c>
       <c r="BU20" t="n">
-        <v>6500</v>
+        <v>6469</v>
       </c>
       <c r="BV20" t="n">
-        <v>11115.38461538462</v>
+        <v>11095</v>
       </c>
       <c r="BW20" t="n">
         <v>4.945000000000022</v>
       </c>
       <c r="BX20" t="n">
-        <v>4.446163381088764</v>
+        <v>4.409298150503011</v>
       </c>
       <c r="BY20" t="n">
-        <v>4.457835693693051</v>
+        <v>4.457695905081012</v>
       </c>
       <c r="BZ20" t="n">
-        <v>6.322773146354652</v>
+        <v>6.322226400560989</v>
       </c>
       <c r="CA20" t="n">
-        <v>0.414499948551479</v>
+        <v>0.4145041295773492</v>
       </c>
       <c r="CB20" t="n">
-        <v>6.33634519795226</v>
+        <v>6.335799896886504</v>
       </c>
       <c r="CC20" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7711666666666667</v>
       </c>
       <c r="CD20" t="n">
-        <v>6.80664920385966</v>
+        <v>6.774515684235927</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9274737265426</v>
       </c>
       <c r="CF20" t="n">
-        <v>17.83342091411231</v>
+        <v>17.74923109269813</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.03365888031308616</v>
+        <v>0.0334999800585468</v>
       </c>
       <c r="CH20" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992273446085906</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.199863797070839</v>
+        <v>1.202689076994943</v>
       </c>
       <c r="CJ20" t="inlineStr"/>
       <c r="CK20" t="inlineStr"/>
@@ -6893,7 +6893,7 @@
         <v>17.83814903173707</v>
       </c>
       <c r="CP20" t="n">
-        <v>0.05998247823267315</v>
+        <v>0.06059523907727483</v>
       </c>
       <c r="CQ20" t="n">
         <v>3.948903220766222</v>
@@ -6912,13 +6912,13 @@
       </c>
       <c r="CX20" t="inlineStr"/>
       <c r="CY20" t="n">
-        <v>0.9824670050180928</v>
+        <v>0.9821857984576182</v>
       </c>
       <c r="CZ20" t="n">
-        <v>0.58803254639515</v>
+        <v>0.5816457199934031</v>
       </c>
       <c r="DA20" t="n">
-        <v>1.032256348081791</v>
+        <v>1.032963573787773</v>
       </c>
       <c r="DB20" t="inlineStr">
         <is>
@@ -6926,16 +6926,16 @@
         </is>
       </c>
       <c r="DC20" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298139333621809</v>
       </c>
       <c r="DD20" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297858533419857</v>
       </c>
       <c r="DE20" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297016861219196</v>
       </c>
       <c r="DF20" t="n">
-        <v>1.299826689774697</v>
+        <v>1.296736546358332</v>
       </c>
     </row>
     <row r="21">
@@ -6997,47 +6997,47 @@
         <v>267.07</v>
       </c>
       <c r="P21" t="n">
-        <v>4700</v>
+        <v>4763</v>
       </c>
       <c r="Q21" t="n">
-        <v>9315.384615384615</v>
+        <v>9382</v>
       </c>
       <c r="R21" t="n">
         <v>8.089999999999975</v>
       </c>
       <c r="S21" t="n">
-        <v>7.578699138241358</v>
+        <v>7.575806321579989</v>
       </c>
       <c r="T21" t="n">
-        <v>7.600498158064808</v>
+        <v>7.605324500387384</v>
       </c>
       <c r="U21" t="n">
-        <v>10.76213158117614</v>
+        <v>10.76947500774313</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5683090600214346</v>
+        <v>0.5641038855400952</v>
       </c>
       <c r="W21" t="n">
-        <v>10.77712630334503</v>
+        <v>10.78423873697561</v>
       </c>
       <c r="X21" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.77</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.80664920385966</v>
+        <v>6.794937114744855</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9246863070366348</v>
       </c>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="n">
-        <v>0.05506579205922448</v>
+        <v>0.05497104125828571</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992454260183794</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200891307839786</v>
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
@@ -7048,47 +7048,47 @@
         <v>269.75</v>
       </c>
       <c r="AI21" t="n">
-        <v>4800</v>
+        <v>4887</v>
       </c>
       <c r="AJ21" t="n">
-        <v>9415.384615384615</v>
+        <v>9506</v>
       </c>
       <c r="AK21" t="n">
-        <v>7.995000000000005</v>
+        <v>7.989999999999981</v>
       </c>
       <c r="AL21" t="n">
-        <v>7.537746677867001</v>
+        <v>7.518760351949568</v>
       </c>
       <c r="AM21" t="n">
-        <v>7.546086825635991</v>
+        <v>7.548396305596193</v>
       </c>
       <c r="AN21" t="n">
-        <v>10.68603361691672</v>
+        <v>10.68720265754339</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.4584619187906491</v>
+        <v>0.4502119785803351</v>
       </c>
       <c r="AP21" t="n">
-        <v>10.69586377030184</v>
+        <v>10.69668132969566</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.77</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.80664920385966</v>
+        <v>6.794937114744855</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9246863070366348</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AU21" t="n">
-        <v>0.05441916038485802</v>
+        <v>0.05429154754681126</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992454260183794</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200891307839786</v>
       </c>
       <c r="AX21" t="inlineStr"/>
       <c r="AY21" t="inlineStr"/>
@@ -7099,47 +7099,47 @@
         <v>270.24</v>
       </c>
       <c r="BB21" t="n">
-        <v>6500</v>
+        <v>6474</v>
       </c>
       <c r="BC21" t="n">
-        <v>11115.38461538462</v>
+        <v>11094</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.203874999999986</v>
+        <v>8.203499999999986</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.574742710466889</v>
+        <v>7.571190462226859</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.562314256326419</v>
+        <v>7.562356163829654</v>
       </c>
       <c r="BG21" t="n">
-        <v>10.71473152322133</v>
+        <v>10.71348563549</v>
       </c>
       <c r="BH21" t="n">
-        <v>0.6797391969807653</v>
+        <v>0.682348358986109</v>
       </c>
       <c r="BI21" t="n">
-        <v>10.73627109338363</v>
+        <v>10.73519323276771</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7701666666666668</v>
       </c>
       <c r="BK21" t="n">
-        <v>6.80664920385966</v>
+        <v>6.792013952800097</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9250842755688481</v>
       </c>
       <c r="BM21" t="inlineStr"/>
       <c r="BN21" t="n">
-        <v>0.05584089923731407</v>
+        <v>0.0557182864617955</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992428639850438</v>
       </c>
       <c r="BP21" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201148161309909</v>
       </c>
       <c r="BQ21" t="inlineStr"/>
       <c r="BR21" t="inlineStr"/>
@@ -7150,47 +7150,47 @@
         <v>270.91</v>
       </c>
       <c r="BU21" t="n">
-        <v>6500</v>
+        <v>6477</v>
       </c>
       <c r="BV21" t="n">
-        <v>11115.38461538462</v>
+        <v>11099</v>
       </c>
       <c r="BW21" t="n">
         <v>8.005000000000024</v>
       </c>
       <c r="BX21" t="n">
-        <v>7.389125255470363</v>
+        <v>7.383872774279485</v>
       </c>
       <c r="BY21" t="n">
-        <v>7.384251834616386</v>
+        <v>7.383234921211005</v>
       </c>
       <c r="BZ21" t="n">
-        <v>10.46373966675914</v>
+        <v>10.46081960438959</v>
       </c>
       <c r="CA21" t="n">
-        <v>0.6573541354480171</v>
+        <v>0.6587781138058665</v>
       </c>
       <c r="CB21" t="n">
-        <v>10.48436751898269</v>
+        <v>10.48154260587683</v>
       </c>
       <c r="CC21" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7705000000000001</v>
       </c>
       <c r="CD21" t="n">
-        <v>6.80664920385966</v>
+        <v>6.786173450053408</v>
       </c>
       <c r="CE21" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9258804469741541</v>
       </c>
       <c r="CF21" t="inlineStr"/>
       <c r="CG21" t="n">
-        <v>0.05448722687689674</v>
+        <v>0.05432331846767769</v>
       </c>
       <c r="CH21" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992377189472729</v>
       </c>
       <c r="CI21" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201661839031998</v>
       </c>
       <c r="CJ21" t="inlineStr"/>
       <c r="CK21" t="inlineStr"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="CO21" t="inlineStr"/>
       <c r="CP21" t="n">
-        <v>0.05443358836211374</v>
+        <v>0.05439954609296904</v>
       </c>
       <c r="CQ21" t="n">
         <v>3.948903220766222</v>
@@ -7222,13 +7222,13 @@
       </c>
       <c r="CX21" t="inlineStr"/>
       <c r="CY21" t="n">
-        <v>0.9945963733844883</v>
+        <v>0.9924699804603077</v>
       </c>
       <c r="CZ21" t="n">
-        <v>1.004908102405261</v>
+        <v>1.006973238648802</v>
       </c>
       <c r="DA21" t="n">
-        <v>0.9754952132248615</v>
+        <v>0.9752591499471697</v>
       </c>
       <c r="DB21" t="inlineStr">
         <is>
@@ -7236,16 +7236,16 @@
         </is>
       </c>
       <c r="DC21" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298701298701299</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298701298701299</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298420255355983</v>
       </c>
       <c r="DF21" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297858533419857</v>
       </c>
     </row>
     <row r="22">
@@ -7307,49 +7307,49 @@
         <v>267.07</v>
       </c>
       <c r="P22" t="n">
-        <v>3950</v>
+        <v>5055</v>
       </c>
       <c r="Q22" t="n">
-        <v>13180.76923076923</v>
+        <v>14300</v>
       </c>
       <c r="R22" t="n">
-        <v>18.48500000000001</v>
+        <v>18.47532500000002</v>
       </c>
       <c r="S22" t="n">
-        <v>13.36733164865085</v>
+        <v>13.22921520243466</v>
       </c>
       <c r="T22" t="n">
-        <v>13.42492022885174</v>
+        <v>13.24329447658213</v>
       </c>
       <c r="U22" t="n">
-        <v>19.05520865689439</v>
+        <v>18.78812712735168</v>
       </c>
       <c r="V22" t="n">
-        <v>6.069831682763795</v>
+        <v>6.017790718865434</v>
       </c>
       <c r="W22" t="n">
-        <v>19.99859579107658</v>
+        <v>19.72834321704666</v>
       </c>
       <c r="X22" t="n">
-        <v>1.538333333333333</v>
+        <v>1.540666666666667</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.049234936091632</v>
+        <v>2.044942904027034</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.066112721639952</v>
+        <v>3.072548037799163</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.368995532560076</v>
+        <v>5.357750408550831</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.03788010779365385</v>
+        <v>0.0377809847583433</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.8301305724820542</v>
+        <v>0.8293550654258437</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.99313936401297</v>
+        <v>1.994297731154801</v>
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
@@ -7360,49 +7360,49 @@
         <v>269.75</v>
       </c>
       <c r="AI22" t="n">
-        <v>4000</v>
+        <v>5155</v>
       </c>
       <c r="AJ22" t="n">
-        <v>13230.76923076923</v>
+        <v>14390</v>
       </c>
       <c r="AK22" t="n">
-        <v>20.32194999999997</v>
+        <v>20.32014999999996</v>
       </c>
       <c r="AL22" t="n">
-        <v>13.55393370213561</v>
+        <v>13.43387128180172</v>
       </c>
       <c r="AM22" t="n">
-        <v>13.6453109663016</v>
+        <v>13.43616538134358</v>
       </c>
       <c r="AN22" t="n">
-        <v>19.38653157565349</v>
+        <v>19.07568585887373</v>
       </c>
       <c r="AO22" t="n">
-        <v>7.845309797475522</v>
+        <v>7.893986789263694</v>
       </c>
       <c r="AP22" t="n">
-        <v>20.91378713557578</v>
+        <v>20.64453483165714</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.538333333333333</v>
+        <v>1.539</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.049234936091632</v>
+        <v>2.048006657255135</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.066112721639952</v>
+        <v>3.067951603048352</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.368995532560076</v>
+        <v>5.365777442008453</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.04164444990950729</v>
+        <v>0.04161580247642284</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.8301305724820542</v>
+        <v>0.8299089677142342</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.99313936401297</v>
+        <v>1.993470827191911</v>
       </c>
       <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="inlineStr"/>
@@ -7413,49 +7413,49 @@
         <v>270.24</v>
       </c>
       <c r="BB22" t="n">
-        <v>4500</v>
+        <v>5509</v>
       </c>
       <c r="BC22" t="n">
-        <v>13730.76923076923</v>
+        <v>14749</v>
       </c>
       <c r="BD22" t="n">
-        <v>14.39825</v>
+        <v>14.01499999999999</v>
       </c>
       <c r="BE22" t="n">
-        <v>13.01773959488541</v>
+        <v>12.87149159540273</v>
       </c>
       <c r="BF22" t="n">
-        <v>13.04266003608493</v>
+        <v>12.88004059400212</v>
       </c>
       <c r="BG22" t="n">
-        <v>18.46986905764118</v>
+        <v>18.24094474612495</v>
       </c>
       <c r="BH22" t="n">
-        <v>0.6798223846904058</v>
+        <v>0.6773753575233283</v>
       </c>
       <c r="BI22" t="n">
-        <v>18.4823759695862</v>
+        <v>18.25351754063209</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1.5385</v>
+        <v>1.540166666666667</v>
       </c>
       <c r="BK22" t="n">
-        <v>2.048927717267306</v>
+        <v>2.045860990297312</v>
       </c>
       <c r="BL22" t="n">
-        <v>3.066572458475788</v>
+        <v>3.071169222629584</v>
       </c>
       <c r="BM22" t="n">
-        <v>5.368190619240342</v>
+        <v>5.360155794578957</v>
       </c>
       <c r="BN22" t="n">
-        <v>0.029500973505144</v>
+        <v>0.0286727417790168</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8295212195408118</v>
       </c>
       <c r="BP22" t="n">
-        <v>1.993222267452576</v>
+        <v>1.994049922711558</v>
       </c>
       <c r="BQ22" t="inlineStr"/>
       <c r="BR22" t="inlineStr"/>
@@ -7466,49 +7466,49 @@
         <v>270.91</v>
       </c>
       <c r="BU22" t="n">
-        <v>4500</v>
+        <v>5509</v>
       </c>
       <c r="BV22" t="n">
-        <v>13730.76923076923</v>
+        <v>14750</v>
       </c>
       <c r="BW22" t="n">
-        <v>14.44</v>
+        <v>13.88499999999999</v>
       </c>
       <c r="BX22" t="n">
-        <v>13.03035202540158</v>
+        <v>12.89255400313572</v>
       </c>
       <c r="BY22" t="n">
-        <v>13.07391999541826</v>
+        <v>12.90155996546171</v>
       </c>
       <c r="BZ22" t="n">
-        <v>18.51375460585816</v>
+        <v>18.26821778039377</v>
       </c>
       <c r="CA22" t="n">
-        <v>0.6958206137091715</v>
+        <v>0.6848777354003371</v>
       </c>
       <c r="CB22" t="n">
-        <v>18.52682584611829</v>
+        <v>18.28105134789415</v>
       </c>
       <c r="CC22" t="n">
-        <v>1.5385</v>
+        <v>1.540333333333334</v>
       </c>
       <c r="CD22" t="n">
-        <v>2.048927717267306</v>
+        <v>2.045554862651738</v>
       </c>
       <c r="CE22" t="n">
-        <v>3.066572458475788</v>
+        <v>3.071628838658687</v>
       </c>
       <c r="CF22" t="n">
-        <v>5.368190619240342</v>
+        <v>5.359353740147553</v>
       </c>
       <c r="CG22" t="n">
-        <v>0.02958651623733989</v>
+        <v>0.02840252926791936</v>
       </c>
       <c r="CH22" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.829465833248814</v>
       </c>
       <c r="CI22" t="n">
-        <v>1.993222267452576</v>
+        <v>1.994132550525007</v>
       </c>
       <c r="CJ22" t="inlineStr"/>
       <c r="CK22" t="inlineStr"/>
@@ -7523,7 +7523,7 @@
         <v>5.368376345338421</v>
       </c>
       <c r="CP22" t="n">
-        <v>0.041639647202729</v>
+        <v>0.04163595900523979</v>
       </c>
       <c r="CQ22" t="n">
         <v>1.18841919095278</v>
@@ -7542,13 +7542,13 @@
       </c>
       <c r="CX22" t="inlineStr"/>
       <c r="CY22" t="n">
-        <v>1.013959558899968</v>
+        <v>1.015470009084847</v>
       </c>
       <c r="CZ22" t="n">
-        <v>0.9604399638485978</v>
+        <v>0.9581371836455792</v>
       </c>
       <c r="DA22" t="n">
-        <v>1.000968864865075</v>
+        <v>1.001636361067937</v>
       </c>
       <c r="DB22" t="inlineStr">
         <is>
@@ -7556,16 +7556,16 @@
         </is>
       </c>
       <c r="DC22" t="n">
-        <v>0.6500541711809318</v>
+        <v>0.6490696668109044</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.6500541711809318</v>
+        <v>0.649772579597141</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6492803809111568</v>
       </c>
       <c r="DF22" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6492101276779917</v>
       </c>
     </row>
     <row r="23">
@@ -7627,47 +7627,47 @@
         <v>267.07</v>
       </c>
       <c r="P23" t="n">
-        <v>3950</v>
+        <v>5044</v>
       </c>
       <c r="Q23" t="n">
-        <v>13180.76923076923</v>
+        <v>14276</v>
       </c>
       <c r="R23" t="n">
-        <v>18.99352500000001</v>
+        <v>18.6942</v>
       </c>
       <c r="S23" t="n">
-        <v>13.28365035157</v>
+        <v>13.08895369877559</v>
       </c>
       <c r="T23" t="n">
-        <v>13.31126113186447</v>
+        <v>13.11963625144671</v>
       </c>
       <c r="U23" t="n">
-        <v>18.88493627909372</v>
+        <v>18.61394787484141</v>
       </c>
       <c r="V23" t="n">
-        <v>6.123438888445901</v>
+        <v>6.216179682106058</v>
       </c>
       <c r="W23" t="n">
-        <v>19.8528920333024</v>
+        <v>19.62447312229149</v>
       </c>
       <c r="X23" t="n">
-        <v>1.538</v>
+        <v>1.538333333333333</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.049849672265102</v>
+        <v>2.049234936091632</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.065193214991523</v>
+        <v>3.066112721639952</v>
       </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="n">
-        <v>0.03893387099640904</v>
+        <v>0.03830880774228419</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.8302413841571755</v>
+        <v>0.8301305724820542</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.992973481789027</v>
+        <v>1.99313936401297</v>
       </c>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
@@ -7678,47 +7678,47 @@
         <v>269.75</v>
       </c>
       <c r="AI23" t="n">
-        <v>4000</v>
+        <v>5163</v>
       </c>
       <c r="AJ23" t="n">
-        <v>13230.76923076923</v>
+        <v>14401</v>
       </c>
       <c r="AK23" t="n">
-        <v>19.48</v>
+        <v>19.42689999999999</v>
       </c>
       <c r="AL23" t="n">
-        <v>13.4287059206842</v>
+        <v>13.26988717834499</v>
       </c>
       <c r="AM23" t="n">
-        <v>13.52003809041199</v>
+        <v>13.31009168066754</v>
       </c>
       <c r="AN23" t="n">
-        <v>19.18161102873614</v>
+        <v>18.88010030876679</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.874048766420479</v>
+        <v>7.203713818741833</v>
       </c>
       <c r="AP23" t="n">
-        <v>20.3761318237996</v>
+        <v>20.20771338997631</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.538166666666667</v>
+        <v>1.5395</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.04954225440786</v>
+        <v>2.047086490905204</v>
       </c>
       <c r="AS23" t="n">
-        <v>3.065652973812381</v>
+        <v>3.069330648751053</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AU23" t="n">
-        <v>0.03992508311586512</v>
+        <v>0.03976854455016628</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.8301859775481096</v>
+        <v>0.8297427805022363</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.993056435461511</v>
+        <v>1.993719161254338</v>
       </c>
       <c r="AX23" t="inlineStr"/>
       <c r="AY23" t="inlineStr"/>
@@ -7729,47 +7729,47 @@
         <v>270.24</v>
       </c>
       <c r="BB23" t="n">
-        <v>4500</v>
+        <v>5665</v>
       </c>
       <c r="BC23" t="n">
-        <v>13730.76923076923</v>
+        <v>14935</v>
       </c>
       <c r="BD23" t="n">
-        <v>23.73500000000001</v>
+        <v>23.78000000000002</v>
       </c>
       <c r="BE23" t="n">
-        <v>13.39526142584423</v>
+        <v>12.99683108540519</v>
       </c>
       <c r="BF23" t="n">
-        <v>13.51450028027071</v>
+        <v>13.35379278297684</v>
       </c>
       <c r="BG23" t="n">
-        <v>19.41259151653773</v>
+        <v>19.31373401967368</v>
       </c>
       <c r="BH23" t="n">
-        <v>10.98165168074197</v>
+        <v>11.07081408497606</v>
       </c>
       <c r="BI23" t="n">
-        <v>22.30348365222562</v>
+        <v>22.26169908804817</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1.5355</v>
+        <v>1.542166666666667</v>
       </c>
       <c r="BK23" t="n">
-        <v>2.054472918535711</v>
+        <v>2.04219397558473</v>
       </c>
       <c r="BL23" t="n">
-        <v>3.058295512436258</v>
+        <v>3.076683891098325</v>
       </c>
       <c r="BM23" t="inlineStr"/>
       <c r="BN23" t="n">
-        <v>0.04876291472144512</v>
+        <v>0.04856337273940493</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.8310726661901815</v>
+        <v>0.8288566894276258</v>
       </c>
       <c r="BP23" t="n">
-        <v>1.99172615593374</v>
+        <v>1.995039808342154</v>
       </c>
       <c r="BQ23" t="inlineStr"/>
       <c r="BR23" t="inlineStr"/>
@@ -7780,47 +7780,47 @@
         <v>270.91</v>
       </c>
       <c r="BU23" t="n">
-        <v>4500</v>
+        <v>5550</v>
       </c>
       <c r="BV23" t="n">
-        <v>13730.76923076923</v>
+        <v>14770</v>
       </c>
       <c r="BW23" t="n">
-        <v>29.62342499999999</v>
+        <v>29.380675</v>
       </c>
       <c r="BX23" t="n">
-        <v>13.18516347777833</v>
+        <v>13.09598303766512</v>
       </c>
       <c r="BY23" t="n">
-        <v>13.45986667927196</v>
+        <v>13.29774786913587</v>
       </c>
       <c r="BZ23" t="n">
-        <v>19.46692435404752</v>
+        <v>19.1924891623181</v>
       </c>
       <c r="CA23" t="n">
-        <v>11.40220173027852</v>
+        <v>10.68233139975244</v>
       </c>
       <c r="CB23" t="n">
-        <v>22.5603933499435</v>
+        <v>21.96505962613885</v>
       </c>
       <c r="CC23" t="n">
-        <v>1.538</v>
+        <v>1.536333333333333</v>
       </c>
       <c r="CD23" t="n">
-        <v>2.049849672265102</v>
+        <v>2.052929336419657</v>
       </c>
       <c r="CE23" t="n">
-        <v>3.065193214991523</v>
+        <v>3.060595021812863</v>
       </c>
       <c r="CF23" t="inlineStr"/>
       <c r="CG23" t="n">
-        <v>0.0607235680276198</v>
+        <v>0.06031644963131159</v>
       </c>
       <c r="CH23" t="n">
-        <v>0.8302413841571755</v>
+        <v>0.8307955343816316</v>
       </c>
       <c r="CI23" t="n">
-        <v>1.992973481789027</v>
+        <v>1.992142561388282</v>
       </c>
       <c r="CJ23" t="inlineStr"/>
       <c r="CK23" t="inlineStr"/>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="CO23" t="inlineStr"/>
       <c r="CP23" t="n">
-        <v>0.03991449282717269</v>
+        <v>0.03980569100124233</v>
       </c>
       <c r="CQ23" t="n">
         <v>1.18841919095278</v>
@@ -7852,13 +7852,13 @@
       </c>
       <c r="CX23" t="inlineStr"/>
       <c r="CY23" t="n">
-        <v>1.010919857514697</v>
+        <v>1.013823372267435</v>
       </c>
       <c r="CZ23" t="n">
-        <v>0.9975094774554223</v>
+        <v>0.9794228775821547</v>
       </c>
       <c r="DA23" t="n">
-        <v>0.9843155022222601</v>
+        <v>1.007628932899749</v>
       </c>
       <c r="DB23" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         </is>
       </c>
       <c r="DC23" t="n">
-        <v>0.6501950585175553</v>
+        <v>0.6500541711809318</v>
       </c>
       <c r="DD23" t="n">
-        <v>0.6501246072163831</v>
+        <v>0.6495615459564794</v>
       </c>
       <c r="DE23" t="n">
-        <v>0.651253663301856</v>
+        <v>0.6484383443207609</v>
       </c>
       <c r="DF23" t="n">
-        <v>0.6501950585175553</v>
+        <v>0.6509004122369277</v>
       </c>
     </row>
     <row r="24">
@@ -7937,49 +7937,49 @@
         <v>267.07</v>
       </c>
       <c r="P24" t="n">
-        <v>4700</v>
+        <v>4744</v>
       </c>
       <c r="Q24" t="n">
-        <v>9315.384615384615</v>
+        <v>9356</v>
       </c>
       <c r="R24" t="n">
         <v>16.98</v>
       </c>
       <c r="S24" t="n">
-        <v>15.37923650334453</v>
+        <v>15.37032781768088</v>
       </c>
       <c r="T24" t="n">
-        <v>15.4773547603595</v>
+        <v>15.47498331988662</v>
       </c>
       <c r="U24" t="n">
-        <v>21.92334843220194</v>
+        <v>21.92149231161045</v>
       </c>
       <c r="V24" t="n">
-        <v>1.988206707574576</v>
+        <v>1.978547187666409</v>
       </c>
       <c r="W24" t="n">
-        <v>22.01331806865507</v>
+        <v>22.01059913182326</v>
       </c>
       <c r="X24" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7688333333333335</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.80664920385966</v>
+        <v>6.815453729254355</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9219027164999912</v>
       </c>
       <c r="AA24" t="n">
-        <v>17.83342091411231</v>
+        <v>17.85648877064641</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.1155769034815371</v>
+        <v>0.115726404322739</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992631657802564</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.199863797070839</v>
+        <v>1.199093062865803</v>
       </c>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
@@ -7990,49 +7990,49 @@
         <v>269.75</v>
       </c>
       <c r="AI24" t="n">
-        <v>4800</v>
+        <v>4858</v>
       </c>
       <c r="AJ24" t="n">
-        <v>9415.384615384615</v>
+        <v>9481</v>
       </c>
       <c r="AK24" t="n">
-        <v>16.37200000000001</v>
+        <v>16.55000000000001</v>
       </c>
       <c r="AL24" t="n">
-        <v>14.44720047608495</v>
+        <v>14.49519771185136</v>
       </c>
       <c r="AM24" t="n">
-        <v>14.44831120518674</v>
+        <v>14.43168283891534</v>
       </c>
       <c r="AN24" t="n">
-        <v>20.48019850102281</v>
+        <v>20.4535633564835</v>
       </c>
       <c r="AO24" t="n">
-        <v>2.272969356804396</v>
+        <v>2.277164212666717</v>
       </c>
       <c r="AP24" t="n">
-        <v>20.6059438109073</v>
+        <v>20.57993515123735</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7706666666666666</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.80664920385966</v>
+        <v>6.783256106042011</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9262786498040373</v>
       </c>
       <c r="AT24" t="n">
-        <v>17.83342091411231</v>
+        <v>17.77213099783007</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.1114384607655904</v>
+        <v>0.1122628885549954</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992351359158013</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201918663240533</v>
       </c>
       <c r="AX24" t="inlineStr"/>
       <c r="AY24" t="inlineStr"/>
@@ -8043,49 +8043,49 @@
         <v>270.24</v>
       </c>
       <c r="BB24" t="n">
-        <v>6500</v>
+        <v>6455</v>
       </c>
       <c r="BC24" t="n">
-        <v>11115.38461538462</v>
+        <v>11076</v>
       </c>
       <c r="BD24" t="n">
         <v>11.18000000000001</v>
       </c>
       <c r="BE24" t="n">
-        <v>10.24913654689046</v>
+        <v>10.2908416145428</v>
       </c>
       <c r="BF24" t="n">
-        <v>10.24338921531117</v>
+        <v>10.24151607219691</v>
       </c>
       <c r="BG24" t="n">
-        <v>14.50799254987013</v>
+        <v>14.50774645786145</v>
       </c>
       <c r="BH24" t="n">
-        <v>0.6132926627004128</v>
+        <v>0.6150180407405464</v>
       </c>
       <c r="BI24" t="n">
-        <v>14.52094954599076</v>
+        <v>14.52077664851394</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7703333333333333</v>
       </c>
       <c r="BK24" t="n">
-        <v>6.80664920385966</v>
+        <v>6.789092731771489</v>
       </c>
       <c r="BL24" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9254823222218832</v>
       </c>
       <c r="BM24" t="n">
-        <v>17.83342091411231</v>
+        <v>17.7874229572413</v>
       </c>
       <c r="BN24" t="n">
-        <v>0.07609833809915105</v>
+        <v>0.0759020567412053</v>
       </c>
       <c r="BO24" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992402949658459</v>
       </c>
       <c r="BP24" t="n">
-        <v>1.199863797070839</v>
+        <v>1.20140500504788</v>
       </c>
       <c r="BQ24" t="inlineStr"/>
       <c r="BR24" t="inlineStr"/>
@@ -8096,49 +8096,49 @@
         <v>270.91</v>
       </c>
       <c r="BU24" t="n">
-        <v>6500</v>
+        <v>6455</v>
       </c>
       <c r="BV24" t="n">
-        <v>11115.38461538462</v>
+        <v>11078</v>
       </c>
       <c r="BW24" t="n">
         <v>11.30500000000001</v>
       </c>
       <c r="BX24" t="n">
-        <v>10.20640888400504</v>
+        <v>10.24736315642152</v>
       </c>
       <c r="BY24" t="n">
-        <v>10.15204897622004</v>
+        <v>10.1441642526548</v>
       </c>
       <c r="BZ24" t="n">
-        <v>14.39080605470158</v>
+        <v>14.38045949331869</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.000275910734953</v>
+        <v>1.001853197400643</v>
       </c>
       <c r="CB24" t="n">
-        <v>14.42552774776827</v>
+        <v>14.41531564233408</v>
       </c>
       <c r="CC24" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7706666666666666</v>
       </c>
       <c r="CD24" t="n">
-        <v>6.80664920385966</v>
+        <v>6.783256106042011</v>
       </c>
       <c r="CE24" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9262786498040373</v>
       </c>
       <c r="CF24" t="n">
-        <v>17.83342091411231</v>
+        <v>17.77213099783007</v>
       </c>
       <c r="CG24" t="n">
-        <v>0.07694916924963351</v>
+        <v>0.076684710278805</v>
       </c>
       <c r="CH24" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992351359158013</v>
       </c>
       <c r="CI24" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201918663240533</v>
       </c>
       <c r="CJ24" t="inlineStr"/>
       <c r="CK24" t="inlineStr"/>
@@ -8153,7 +8153,7 @@
         <v>17.83814903173707</v>
       </c>
       <c r="CP24" t="n">
-        <v>0.11146800608687</v>
+        <v>0.1126799108684156</v>
       </c>
       <c r="CQ24" t="n">
         <v>3.948903220766222</v>
@@ -8172,13 +8172,13 @@
       </c>
       <c r="CX24" t="inlineStr"/>
       <c r="CY24" t="n">
-        <v>0.9393964695804704</v>
+        <v>0.9430636668124389</v>
       </c>
       <c r="CZ24" t="n">
-        <v>0.7094202481550858</v>
+        <v>0.7099483442111969</v>
       </c>
       <c r="DA24" t="n">
-        <v>0.9958310963377318</v>
+        <v>0.9957750337873393</v>
       </c>
       <c r="DB24" t="inlineStr">
         <is>
@@ -8186,16 +8186,16 @@
         </is>
       </c>
       <c r="DC24" t="n">
-        <v>1.299826689774697</v>
+        <v>1.300672013873835</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29757785467128</v>
       </c>
       <c r="DE24" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298139333621809</v>
       </c>
       <c r="DF24" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29757785467128</v>
       </c>
     </row>
     <row r="25">
@@ -8257,47 +8257,47 @@
         <v>267.07</v>
       </c>
       <c r="P25" t="n">
-        <v>4700</v>
+        <v>4758</v>
       </c>
       <c r="Q25" t="n">
-        <v>9315.384615384615</v>
+        <v>9372</v>
       </c>
       <c r="R25" t="n">
         <v>15.63500000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>14.85083199326093</v>
+        <v>14.87732930722652</v>
       </c>
       <c r="T25" t="n">
-        <v>14.83648322013538</v>
+        <v>14.83338969516501</v>
       </c>
       <c r="U25" t="n">
-        <v>20.99995547232745</v>
+        <v>20.99809901107115</v>
       </c>
       <c r="V25" t="n">
-        <v>0.763478047313118</v>
+        <v>0.7596730463791087</v>
       </c>
       <c r="W25" t="n">
-        <v>21.01382945986915</v>
+        <v>21.01183631232983</v>
       </c>
       <c r="X25" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7691666666666667</v>
       </c>
       <c r="Y25" t="n">
-        <v>6.80664920385966</v>
+        <v>6.809582094531432</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9226976369409542</v>
       </c>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="n">
-        <v>0.1064219603023458</v>
+        <v>0.106467816047999</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992581318692667</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.199863797070839</v>
+        <v>1.199606895264513</v>
       </c>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
@@ -8308,47 +8308,47 @@
         <v>269.75</v>
       </c>
       <c r="AI25" t="n">
-        <v>4800</v>
+        <v>4876</v>
       </c>
       <c r="AJ25" t="n">
-        <v>9415.384615384615</v>
+        <v>9496</v>
       </c>
       <c r="AK25" t="n">
-        <v>15.859625</v>
+        <v>15.8595</v>
       </c>
       <c r="AL25" t="n">
-        <v>14.83308022053116</v>
+        <v>14.82989815619798</v>
       </c>
       <c r="AM25" t="n">
-        <v>14.88834124982207</v>
+        <v>14.88788229252236</v>
       </c>
       <c r="AN25" t="n">
-        <v>21.08040308150008</v>
+        <v>21.07860512632272</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.7522200293592904</v>
+        <v>0.7536112322245266</v>
       </c>
       <c r="AP25" t="n">
-        <v>21.09381968850325</v>
+        <v>21.09207253829678</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7701666666666668</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.80664920385966</v>
+        <v>6.792013952800097</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9250842755688481</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AU25" t="n">
-        <v>0.1079509038797627</v>
+        <v>0.1077179452844332</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992428639850438</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201148161309909</v>
       </c>
       <c r="AX25" t="inlineStr"/>
       <c r="AY25" t="inlineStr"/>
@@ -8359,47 +8359,47 @@
         <v>270.24</v>
       </c>
       <c r="BB25" t="n">
-        <v>6500</v>
+        <v>6466</v>
       </c>
       <c r="BC25" t="n">
-        <v>11115.38461538462</v>
+        <v>11083</v>
       </c>
       <c r="BD25" t="n">
-        <v>15.82550000000002</v>
+        <v>15.82490000000001</v>
       </c>
       <c r="BE25" t="n">
-        <v>14.81987253785154</v>
+        <v>14.8216840878555</v>
       </c>
       <c r="BF25" t="n">
-        <v>14.73253536656508</v>
+        <v>14.73304683800033</v>
       </c>
       <c r="BG25" t="n">
-        <v>20.86302832155953</v>
+        <v>20.86327309467274</v>
       </c>
       <c r="BH25" t="n">
-        <v>0.8250666255653959</v>
+        <v>0.8368225572331734</v>
       </c>
       <c r="BI25" t="n">
-        <v>20.87933633243204</v>
+        <v>20.88004875988535</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7696666666666667</v>
       </c>
       <c r="BK25" t="n">
-        <v>6.80664920385966</v>
+        <v>6.800789267814117</v>
       </c>
       <c r="BL25" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9238906044208459</v>
       </c>
       <c r="BM25" t="inlineStr"/>
       <c r="BN25" t="n">
-        <v>0.1077186269756812</v>
+        <v>0.1076218100842317</v>
       </c>
       <c r="BO25" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992505291814564</v>
       </c>
       <c r="BP25" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200377571789752</v>
       </c>
       <c r="BQ25" t="inlineStr"/>
       <c r="BR25" t="inlineStr"/>
@@ -8410,47 +8410,47 @@
         <v>270.91</v>
       </c>
       <c r="BU25" t="n">
-        <v>6500</v>
+        <v>6468</v>
       </c>
       <c r="BV25" t="n">
-        <v>11115.38461538462</v>
+        <v>11085</v>
       </c>
       <c r="BW25" t="n">
         <v>15.74499999999999</v>
       </c>
       <c r="BX25" t="n">
-        <v>14.66446951250549</v>
+        <v>14.65912035964693</v>
       </c>
       <c r="BY25" t="n">
-        <v>14.58225909570571</v>
+        <v>14.57802460742574</v>
       </c>
       <c r="BZ25" t="n">
-        <v>20.69606959143137</v>
+        <v>20.69226443832448</v>
       </c>
       <c r="CA25" t="n">
-        <v>2.369727732023138</v>
+        <v>2.475933365022705</v>
       </c>
       <c r="CB25" t="n">
-        <v>20.83129631245473</v>
+        <v>20.8398669288837</v>
       </c>
       <c r="CC25" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7696666666666667</v>
       </c>
       <c r="CD25" t="n">
-        <v>6.80664920385966</v>
+        <v>6.800789267814117</v>
       </c>
       <c r="CE25" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9238906044208459</v>
       </c>
       <c r="CF25" t="inlineStr"/>
       <c r="CG25" t="n">
-        <v>0.1071706917147703</v>
+        <v>0.1070784270217332</v>
       </c>
       <c r="CH25" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992505291814564</v>
       </c>
       <c r="CI25" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200377571789752</v>
       </c>
       <c r="CJ25" t="inlineStr"/>
       <c r="CK25" t="inlineStr"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="CO25" t="inlineStr"/>
       <c r="CP25" t="n">
-        <v>0.1079795245562836</v>
+        <v>0.107978673499555</v>
       </c>
       <c r="CQ25" t="n">
         <v>3.948903220766222</v>
@@ -8482,13 +8482,13 @@
       </c>
       <c r="CX25" t="inlineStr"/>
       <c r="CY25" t="n">
-        <v>0.9988046613995885</v>
+        <v>0.9968118504303392</v>
       </c>
       <c r="CZ25" t="n">
-        <v>0.9991095792321449</v>
+        <v>0.9994461143120494</v>
       </c>
       <c r="DA25" t="n">
-        <v>0.9895138757132271</v>
+        <v>0.9890320339277932</v>
       </c>
       <c r="DB25" t="inlineStr">
         <is>
@@ -8496,16 +8496,16 @@
         </is>
       </c>
       <c r="DC25" t="n">
-        <v>1.299826689774697</v>
+        <v>1.300108342361864</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298420255355983</v>
       </c>
       <c r="DE25" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29926375054136</v>
       </c>
       <c r="DF25" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29926375054136</v>
       </c>
     </row>
     <row r="26">
@@ -8567,49 +8567,49 @@
         <v>267.07</v>
       </c>
       <c r="P26" t="n">
-        <v>3950</v>
+        <v>5048</v>
       </c>
       <c r="Q26" t="n">
-        <v>13180.76923076923</v>
+        <v>14270</v>
       </c>
       <c r="R26" t="n">
-        <v>5.538999999999998</v>
+        <v>5.456149999999985</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3828660052782</v>
+        <v>4.325682652287033</v>
       </c>
       <c r="T26" t="n">
-        <v>4.374067193595232</v>
+        <v>4.336602910501052</v>
       </c>
       <c r="U26" t="n">
-        <v>6.210355158263141</v>
+        <v>6.15586502955299</v>
       </c>
       <c r="V26" t="n">
-        <v>1.139783456032015</v>
+        <v>1.167936587564102</v>
       </c>
       <c r="W26" t="n">
-        <v>6.314080892608986</v>
+        <v>6.265680340924225</v>
       </c>
       <c r="X26" t="n">
-        <v>1.5385</v>
+        <v>1.537166666666667</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.048927717267306</v>
+        <v>2.051388256387502</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.066572458475788</v>
+        <v>3.062894255933924</v>
       </c>
       <c r="AA26" t="n">
-        <v>5.368190619240342</v>
+        <v>5.374637231735255</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.0113490106259436</v>
+        <v>0.01119268203508864</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8305184402313639</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.993222267452576</v>
+        <v>1.992558336290094</v>
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
@@ -8620,49 +8620,49 @@
         <v>269.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>4000</v>
+        <v>5135</v>
       </c>
       <c r="AJ26" t="n">
-        <v>13230.76923076923</v>
+        <v>14358</v>
       </c>
       <c r="AK26" t="n">
-        <v>6.318500000000019</v>
+        <v>6.349999999999994</v>
       </c>
       <c r="AL26" t="n">
-        <v>4.670391633160183</v>
+        <v>4.635655725423037</v>
       </c>
       <c r="AM26" t="n">
-        <v>4.696790643330941</v>
+        <v>4.657662529238348</v>
       </c>
       <c r="AN26" t="n">
-        <v>6.686257999601991</v>
+        <v>6.619815380435662</v>
       </c>
       <c r="AO26" t="n">
-        <v>1.546882141053717</v>
+        <v>1.550980326632505</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.862863133966213</v>
+        <v>6.79908049993921</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.5385</v>
+        <v>1.537333333333333</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.048927717267306</v>
+        <v>2.051080340087466</v>
       </c>
       <c r="AS26" t="n">
-        <v>3.066572458475788</v>
+        <v>3.063354069744361</v>
       </c>
       <c r="AT26" t="n">
-        <v>5.368190619240342</v>
+        <v>5.37383049102916</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.01294614978155351</v>
+        <v>0.0130243601595554</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8304630259571014</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.993222267452576</v>
+        <v>1.992641415705352</v>
       </c>
       <c r="AX26" t="inlineStr"/>
       <c r="AY26" t="inlineStr"/>
@@ -8673,49 +8673,49 @@
         <v>270.24</v>
       </c>
       <c r="BB26" t="n">
-        <v>4500</v>
+        <v>5509</v>
       </c>
       <c r="BC26" t="n">
-        <v>13730.76923076923</v>
+        <v>14749</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.690000000000026</v>
+        <v>4.685000000000002</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.413339625280662</v>
+        <v>4.392955415668894</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.421926154139463</v>
+        <v>4.397313918885648</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.266877308330973</v>
+        <v>6.234011906454149</v>
       </c>
       <c r="BH26" t="n">
-        <v>0.1701245916646073</v>
+        <v>0.1712167974763205</v>
       </c>
       <c r="BI26" t="n">
-        <v>6.269186037625834</v>
+        <v>6.236362693233143</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1.5385</v>
+        <v>1.540166666666667</v>
       </c>
       <c r="BK26" t="n">
-        <v>2.048927717267306</v>
+        <v>2.045860990297312</v>
       </c>
       <c r="BL26" t="n">
-        <v>3.066572458475788</v>
+        <v>3.071169222629584</v>
       </c>
       <c r="BM26" t="n">
-        <v>5.368190619240342</v>
+        <v>5.360155794578957</v>
       </c>
       <c r="BN26" t="n">
-        <v>0.00960947099398372</v>
+        <v>0.009584858739542911</v>
       </c>
       <c r="BO26" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8295212195408118</v>
       </c>
       <c r="BP26" t="n">
-        <v>1.993222267452576</v>
+        <v>1.994049922711558</v>
       </c>
       <c r="BQ26" t="inlineStr"/>
       <c r="BR26" t="inlineStr"/>
@@ -8726,49 +8726,49 @@
         <v>270.91</v>
       </c>
       <c r="BU26" t="n">
-        <v>4500</v>
+        <v>5512</v>
       </c>
       <c r="BV26" t="n">
-        <v>13730.76923076923</v>
+        <v>14754</v>
       </c>
       <c r="BW26" t="n">
-        <v>4.599999999999994</v>
+        <v>4.569999999999993</v>
       </c>
       <c r="BX26" t="n">
-        <v>4.442716895355447</v>
+        <v>4.423706904916734</v>
       </c>
       <c r="BY26" t="n">
-        <v>4.454787443654467</v>
+        <v>4.433171876313553</v>
       </c>
       <c r="BZ26" t="n">
-        <v>6.309002382002539</v>
+        <v>6.279737964753293</v>
       </c>
       <c r="CA26" t="n">
-        <v>0.1843442456468619</v>
+        <v>0.1834839223816231</v>
       </c>
       <c r="CB26" t="n">
-        <v>6.311695006653667</v>
+        <v>6.282417946597981</v>
       </c>
       <c r="CC26" t="n">
-        <v>1.5385</v>
+        <v>1.5405</v>
       </c>
       <c r="CD26" t="n">
-        <v>2.048927717267306</v>
+        <v>2.045248833911213</v>
       </c>
       <c r="CE26" t="n">
-        <v>3.066572458475788</v>
+        <v>3.072088443714691</v>
       </c>
       <c r="CF26" t="n">
-        <v>5.368190619240342</v>
+        <v>5.358551944847379</v>
       </c>
       <c r="CG26" t="n">
-        <v>0.009425067499429597</v>
+        <v>0.009346787170974232</v>
       </c>
       <c r="CH26" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8294104485427312</v>
       </c>
       <c r="CI26" t="n">
-        <v>1.993222267452576</v>
+        <v>1.994215153336379</v>
       </c>
       <c r="CJ26" t="inlineStr"/>
       <c r="CK26" t="inlineStr"/>
@@ -8783,7 +8783,7 @@
         <v>5.368376345338421</v>
       </c>
       <c r="CP26" t="n">
-        <v>0.01294659768626752</v>
+        <v>0.01301114114232784</v>
       </c>
       <c r="CQ26" t="n">
         <v>1.18841919095278</v>
@@ -8802,13 +8802,13 @@
       </c>
       <c r="CX26" t="inlineStr"/>
       <c r="CY26" t="n">
-        <v>1.06560219443983</v>
+        <v>1.071658764188843</v>
       </c>
       <c r="CZ26" t="n">
-        <v>0.9449613591172032</v>
+        <v>0.9476448804377087</v>
       </c>
       <c r="DA26" t="n">
-        <v>1.006656471644853</v>
+        <v>1.007000182414362</v>
       </c>
       <c r="DB26" t="inlineStr">
         <is>
@@ -8816,16 +8816,16 @@
         </is>
       </c>
       <c r="DC26" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6505475441830206</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.650477016478751</v>
       </c>
       <c r="DE26" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6492803809111568</v>
       </c>
       <c r="DF26" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6491398896462188</v>
       </c>
     </row>
     <row r="27">
@@ -8887,49 +8887,49 @@
         <v>267.07</v>
       </c>
       <c r="P27" t="n">
-        <v>4700</v>
+        <v>4717</v>
       </c>
       <c r="Q27" t="n">
-        <v>9315.384615384615</v>
+        <v>9348</v>
       </c>
       <c r="R27" t="n">
         <v>24.66499999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>22.125537989452</v>
+        <v>22.13263736290454</v>
       </c>
       <c r="T27" t="n">
-        <v>22.20837051194607</v>
+        <v>22.20405401666093</v>
       </c>
       <c r="U27" t="n">
-        <v>31.52774994526082</v>
+        <v>31.51969712446332</v>
       </c>
       <c r="V27" t="n">
-        <v>5.503251337099718</v>
+        <v>5.466303642656205</v>
       </c>
       <c r="W27" t="n">
-        <v>32.0044495639307</v>
+        <v>31.99018259297089</v>
       </c>
       <c r="X27" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.7718333333333335</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.809582094531432</v>
+        <v>6.762888819396453</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.9290682539625607</v>
       </c>
       <c r="AA27" t="n">
-        <v>17.84110508767235</v>
+        <v>17.71876870681871</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.1679583423616177</v>
+        <v>0.1668066527304135</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.9992168571960084</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.199606895264513</v>
+        <v>1.203716157152961</v>
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
@@ -8940,49 +8940,49 @@
         <v>269.75</v>
       </c>
       <c r="AI27" t="n">
-        <v>4800</v>
+        <v>4844</v>
       </c>
       <c r="AJ27" t="n">
-        <v>9415.384615384615</v>
+        <v>9477</v>
       </c>
       <c r="AK27" t="n">
-        <v>27.50405000000003</v>
+        <v>27.49640000000002</v>
       </c>
       <c r="AL27" t="n">
-        <v>23.45261404719713</v>
+        <v>23.53823121332719</v>
       </c>
       <c r="AM27" t="n">
-        <v>23.47377190374787</v>
+        <v>23.47488045351724</v>
       </c>
       <c r="AN27" t="n">
-        <v>33.33371322553801</v>
+        <v>33.34573537547922</v>
       </c>
       <c r="AO27" t="n">
-        <v>5.879486643142969</v>
+        <v>5.83770503703299</v>
       </c>
       <c r="AP27" t="n">
-        <v>33.84826141161913</v>
+        <v>33.85287089496084</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.7721666666666667</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.809582094531432</v>
+        <v>6.757086942977636</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.9298659851801143</v>
       </c>
       <c r="AT27" t="n">
-        <v>17.84110508767235</v>
+        <v>17.70356779060141</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.1872910864070974</v>
+        <v>0.1857955654188904</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.999211570815197</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.199606895264513</v>
+        <v>1.204229637617243</v>
       </c>
       <c r="AX27" t="inlineStr"/>
       <c r="AY27" t="inlineStr"/>
@@ -8993,49 +8993,49 @@
         <v>270.24</v>
       </c>
       <c r="BB27" t="n">
-        <v>6500</v>
+        <v>6439</v>
       </c>
       <c r="BC27" t="n">
-        <v>11115.38461538462</v>
+        <v>11072</v>
       </c>
       <c r="BD27" t="n">
         <v>17.92</v>
       </c>
       <c r="BE27" t="n">
-        <v>16.05409437834656</v>
+        <v>16.11764482283102</v>
       </c>
       <c r="BF27" t="n">
-        <v>16.07528947827642</v>
+        <v>16.08463036696827</v>
       </c>
       <c r="BG27" t="n">
-        <v>22.77805663212956</v>
+        <v>22.79326371699867</v>
       </c>
       <c r="BH27" t="n">
-        <v>1.23112719123542</v>
+        <v>1.251864109982843</v>
       </c>
       <c r="BI27" t="n">
-        <v>22.81130285839676</v>
+        <v>22.82761561404325</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7723333333333334</v>
       </c>
       <c r="BK27" t="n">
-        <v>6.80664920385966</v>
+        <v>6.754188888208766</v>
       </c>
       <c r="BL27" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.930264967589011</v>
       </c>
       <c r="BM27" t="n">
-        <v>17.83342091411231</v>
+        <v>17.69597488710697</v>
       </c>
       <c r="BN27" t="n">
-        <v>0.1219751537331651</v>
+        <v>0.1210350648767011</v>
       </c>
       <c r="BO27" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992089169084887</v>
       </c>
       <c r="BP27" t="n">
-        <v>1.199863797070839</v>
+        <v>1.20448636286881</v>
       </c>
       <c r="BQ27" t="inlineStr"/>
       <c r="BR27" t="inlineStr"/>
@@ -9046,49 +9046,49 @@
         <v>270.91</v>
       </c>
       <c r="BU27" t="n">
-        <v>6500</v>
+        <v>6444</v>
       </c>
       <c r="BV27" t="n">
-        <v>11115.38461538462</v>
+        <v>11074</v>
       </c>
       <c r="BW27" t="n">
-        <v>19.55362500000001</v>
+        <v>19.54725000000002</v>
       </c>
       <c r="BX27" t="n">
-        <v>16.74477362602236</v>
+        <v>16.8161861845904</v>
       </c>
       <c r="BY27" t="n">
-        <v>16.51426310616409</v>
+        <v>16.50937006834083</v>
       </c>
       <c r="BZ27" t="n">
-        <v>23.411161368949</v>
+        <v>23.40747022458079</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.546647995407577</v>
+        <v>1.575162583480187</v>
       </c>
       <c r="CB27" t="n">
-        <v>23.46219505214012</v>
+        <v>23.46040919248921</v>
       </c>
       <c r="CC27" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7718333333333335</v>
       </c>
       <c r="CD27" t="n">
-        <v>6.80664920385966</v>
+        <v>6.762888819396453</v>
       </c>
       <c r="CE27" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9290682539625607</v>
       </c>
       <c r="CF27" t="n">
-        <v>17.83342091411231</v>
+        <v>17.71876870681871</v>
       </c>
       <c r="CG27" t="n">
-        <v>0.1330946660388204</v>
+        <v>0.1321958784749474</v>
       </c>
       <c r="CH27" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992168571960084</v>
       </c>
       <c r="CI27" t="n">
-        <v>1.199863797070839</v>
+        <v>1.203716157152961</v>
       </c>
       <c r="CJ27" t="inlineStr"/>
       <c r="CK27" t="inlineStr"/>
@@ -9103,7 +9103,7 @@
         <v>17.83814903173707</v>
       </c>
       <c r="CP27" t="n">
-        <v>0.1872600545329575</v>
+        <v>0.1872079698611662</v>
       </c>
       <c r="CQ27" t="n">
         <v>3.948903220766222</v>
@@ -9122,13 +9122,13 @@
       </c>
       <c r="CX27" t="inlineStr"/>
       <c r="CY27" t="n">
-        <v>1.059979380315082</v>
+        <v>1.063507743219906</v>
       </c>
       <c r="CZ27" t="n">
-        <v>0.6845332612406683</v>
+        <v>0.6847432450109217</v>
       </c>
       <c r="DA27" t="n">
-        <v>1.043021999958302</v>
+        <v>1.043340163493979</v>
       </c>
       <c r="DB27" t="inlineStr">
         <is>
@@ -9136,16 +9136,16 @@
         </is>
       </c>
       <c r="DC27" t="n">
-        <v>1.300108342361864</v>
+        <v>1.295616497516735</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.300108342361864</v>
+        <v>1.295057198359594</v>
       </c>
       <c r="DE27" t="n">
-        <v>1.299826689774697</v>
+        <v>1.294777729823047</v>
       </c>
       <c r="DF27" t="n">
-        <v>1.299826689774697</v>
+        <v>1.295616497516735</v>
       </c>
     </row>
     <row r="28">
@@ -9207,47 +9207,47 @@
         <v>267.07</v>
       </c>
       <c r="P28" t="n">
-        <v>4700</v>
+        <v>4746</v>
       </c>
       <c r="Q28" t="n">
-        <v>9315.384615384615</v>
+        <v>9366</v>
       </c>
       <c r="R28" t="n">
-        <v>20.54720000000001</v>
+        <v>20.54620000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>16.64672409617464</v>
+        <v>16.61641665263332</v>
       </c>
       <c r="T28" t="n">
-        <v>16.53094269368022</v>
+        <v>16.55137471838747</v>
       </c>
       <c r="U28" t="n">
-        <v>23.41625940013672</v>
+        <v>23.44210052267908</v>
       </c>
       <c r="V28" t="n">
-        <v>5.102972679497156</v>
+        <v>5.093455545855223</v>
       </c>
       <c r="W28" t="n">
-        <v>23.96584099217437</v>
+        <v>23.98906764159446</v>
       </c>
       <c r="X28" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.77</v>
       </c>
       <c r="Y28" t="n">
-        <v>6.809582094531432</v>
+        <v>6.794937114744855</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.9246863070366348</v>
       </c>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="n">
-        <v>0.1399178452127563</v>
+        <v>0.1396101369469708</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.9992454260183794</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.199606895264513</v>
+        <v>1.200891307839786</v>
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
@@ -9258,47 +9258,47 @@
         <v>269.75</v>
       </c>
       <c r="AI28" t="n">
-        <v>4800</v>
+        <v>4868</v>
       </c>
       <c r="AJ28" t="n">
-        <v>9415.384615384615</v>
+        <v>9489</v>
       </c>
       <c r="AK28" t="n">
-        <v>21.99250000000001</v>
+        <v>21.98499999999999</v>
       </c>
       <c r="AL28" t="n">
-        <v>16.11141043573169</v>
+        <v>16.15613740071997</v>
       </c>
       <c r="AM28" t="n">
-        <v>15.97984362714741</v>
+        <v>15.982653649621</v>
       </c>
       <c r="AN28" t="n">
-        <v>22.66977765109369</v>
+        <v>22.6725844736574</v>
       </c>
       <c r="AO28" t="n">
-        <v>5.929197010097242</v>
+        <v>6.019141920872565</v>
       </c>
       <c r="AP28" t="n">
-        <v>23.43233227688983</v>
+        <v>23.45796572976301</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.7701666666666668</v>
       </c>
       <c r="AR28" t="n">
-        <v>6.809582094531432</v>
+        <v>6.792013952800097</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.9250842755688481</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AU28" t="n">
-        <v>0.1497597342139826</v>
+        <v>0.1493224267523101</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.9992428639850438</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.199606895264513</v>
+        <v>1.201148161309909</v>
       </c>
       <c r="AX28" t="inlineStr"/>
       <c r="AY28" t="inlineStr"/>
@@ -9309,47 +9309,47 @@
         <v>270.24</v>
       </c>
       <c r="BB28" t="n">
-        <v>6500</v>
+        <v>6437</v>
       </c>
       <c r="BC28" t="n">
-        <v>11115.38461538462</v>
+        <v>11062</v>
       </c>
       <c r="BD28" t="n">
-        <v>20.55499999999999</v>
+        <v>21.364375</v>
       </c>
       <c r="BE28" t="n">
-        <v>15.59253084727719</v>
+        <v>15.74045061443303</v>
       </c>
       <c r="BF28" t="n">
-        <v>15.5478731658744</v>
+        <v>15.4957416366336</v>
       </c>
       <c r="BG28" t="n">
-        <v>22.10286663982946</v>
+        <v>22.03691380987483</v>
       </c>
       <c r="BH28" t="n">
-        <v>6.205123693249779</v>
+        <v>6.336964571821522</v>
       </c>
       <c r="BI28" t="n">
-        <v>22.95735772571869</v>
+        <v>22.92995181522135</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7710000000000001</v>
       </c>
       <c r="BK28" t="n">
-        <v>6.80664920385966</v>
+        <v>6.777427224732707</v>
       </c>
       <c r="BL28" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9270752896099725</v>
       </c>
       <c r="BM28" t="inlineStr"/>
       <c r="BN28" t="n">
-        <v>0.1399106743853353</v>
+        <v>0.1447954967643988</v>
       </c>
       <c r="BO28" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992299487600118</v>
       </c>
       <c r="BP28" t="n">
-        <v>1.199863797070839</v>
+        <v>1.202432282243803</v>
       </c>
       <c r="BQ28" t="inlineStr"/>
       <c r="BR28" t="inlineStr"/>
@@ -9360,47 +9360,47 @@
         <v>270.91</v>
       </c>
       <c r="BU28" t="n">
-        <v>6500</v>
+        <v>6466</v>
       </c>
       <c r="BV28" t="n">
-        <v>11115.38461538462</v>
+        <v>11058</v>
       </c>
       <c r="BW28" t="n">
-        <v>23.03662500000002</v>
+        <v>25.33040000000002</v>
       </c>
       <c r="BX28" t="n">
-        <v>16.50520195123786</v>
+        <v>16.12667573834542</v>
       </c>
       <c r="BY28" t="n">
-        <v>16.8466986112028</v>
+        <v>16.84661877201063</v>
       </c>
       <c r="BZ28" t="n">
-        <v>24.15884618788716</v>
+        <v>24.15805140291894</v>
       </c>
       <c r="CA28" t="n">
-        <v>7.96654283808458</v>
+        <v>7.976965841620425</v>
       </c>
       <c r="CB28" t="n">
-        <v>25.43846799477175</v>
+        <v>25.44097937628291</v>
       </c>
       <c r="CC28" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7655</v>
       </c>
       <c r="CD28" t="n">
-        <v>6.80664920385966</v>
+        <v>6.874602069357323</v>
       </c>
       <c r="CE28" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9139707642404638</v>
       </c>
       <c r="CF28" t="inlineStr"/>
       <c r="CG28" t="n">
-        <v>0.1568022252158637</v>
+        <v>0.1741364202576489</v>
       </c>
       <c r="CH28" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9993120093253508</v>
       </c>
       <c r="CI28" t="n">
-        <v>1.199863797070839</v>
+        <v>1.193952663932677</v>
       </c>
       <c r="CJ28" t="inlineStr"/>
       <c r="CK28" t="inlineStr"/>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="CO28" t="inlineStr"/>
       <c r="CP28" t="n">
-        <v>0.1497349208322435</v>
+        <v>0.1496838574285265</v>
       </c>
       <c r="CQ28" t="n">
         <v>3.948903220766222</v>
@@ -9432,13 +9432,13 @@
       </c>
       <c r="CX28" t="inlineStr"/>
       <c r="CY28" t="n">
-        <v>0.9678427024229971</v>
+        <v>0.9722997285434338</v>
       </c>
       <c r="CZ28" t="n">
-        <v>0.9677942790592851</v>
+        <v>0.9742706578944783</v>
       </c>
       <c r="DA28" t="n">
-        <v>1.058532582869319</v>
+        <v>1.024537107187912</v>
       </c>
       <c r="DB28" t="inlineStr">
         <is>
@@ -9446,16 +9446,16 @@
         </is>
       </c>
       <c r="DC28" t="n">
-        <v>1.300108342361864</v>
+        <v>1.298701298701299</v>
       </c>
       <c r="DD28" t="n">
-        <v>1.300108342361864</v>
+        <v>1.298420255355983</v>
       </c>
       <c r="DE28" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297016861219196</v>
       </c>
       <c r="DF28" t="n">
-        <v>1.299826689774697</v>
+        <v>1.306335728282169</v>
       </c>
     </row>
     <row r="29">
@@ -9517,49 +9517,49 @@
         <v>267.07</v>
       </c>
       <c r="P29" t="n">
-        <v>3950</v>
+        <v>5047</v>
       </c>
       <c r="Q29" t="n">
-        <v>13180.76923076923</v>
+        <v>14279</v>
       </c>
       <c r="R29" t="n">
-        <v>14.82400000000002</v>
+        <v>14.70499999999998</v>
       </c>
       <c r="S29" t="n">
-        <v>13.34460266806335</v>
+        <v>13.177433858884</v>
       </c>
       <c r="T29" t="n">
-        <v>13.4123341081417</v>
+        <v>13.21858950909688</v>
       </c>
       <c r="U29" t="n">
-        <v>19.01365477557452</v>
+        <v>18.73689929577244</v>
       </c>
       <c r="V29" t="n">
-        <v>1.322417873751833</v>
+        <v>1.296420261565107</v>
       </c>
       <c r="W29" t="n">
-        <v>19.05958700910243</v>
+        <v>18.78169589559244</v>
       </c>
       <c r="X29" t="n">
-        <v>1.5385</v>
+        <v>1.538833333333333</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.048927717267306</v>
+        <v>2.048313577898088</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.066572458475788</v>
+        <v>3.067491899178437</v>
       </c>
       <c r="AA29" t="n">
-        <v>5.368190619240342</v>
+        <v>5.36658157409299</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.03037330448077059</v>
+        <v>0.03012045116299135</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8299643665751059</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993387999032885</v>
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
@@ -9570,49 +9570,49 @@
         <v>269.75</v>
       </c>
       <c r="AI29" t="n">
-        <v>4000</v>
+        <v>5125</v>
       </c>
       <c r="AJ29" t="n">
-        <v>13230.76923076923</v>
+        <v>14362</v>
       </c>
       <c r="AK29" t="n">
-        <v>15.25900000000003</v>
+        <v>15.21167499999998</v>
       </c>
       <c r="AL29" t="n">
-        <v>13.7639255828492</v>
+        <v>13.70107008027015</v>
       </c>
       <c r="AM29" t="n">
-        <v>13.81995771010395</v>
+        <v>13.72958207318632</v>
       </c>
       <c r="AN29" t="n">
-        <v>19.58473106364923</v>
+        <v>19.45092933758457</v>
       </c>
       <c r="AO29" t="n">
-        <v>1.737366075596497</v>
+        <v>1.797627650041679</v>
       </c>
       <c r="AP29" t="n">
-        <v>19.66164112468999</v>
+        <v>19.53381983289245</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.5385</v>
+        <v>1.539666666666667</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.048927717267306</v>
+        <v>2.046779967151801</v>
       </c>
       <c r="AS29" t="n">
-        <v>3.066572458475788</v>
+        <v>3.069790308688119</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.368190619240342</v>
+        <v>5.36256351393772</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.03126458803778188</v>
+        <v>0.03113495165682384</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8296873878994435</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.993222267452576</v>
+        <v>1.99380188916743</v>
       </c>
       <c r="AX29" t="inlineStr"/>
       <c r="AY29" t="inlineStr"/>
@@ -9623,49 +9623,49 @@
         <v>270.24</v>
       </c>
       <c r="BB29" t="n">
-        <v>4500</v>
+        <v>5505</v>
       </c>
       <c r="BC29" t="n">
-        <v>13730.76923076923</v>
+        <v>14744</v>
       </c>
       <c r="BD29" t="n">
-        <v>14.14</v>
+        <v>13.88499999999999</v>
       </c>
       <c r="BE29" t="n">
-        <v>13.3409053889523</v>
+        <v>13.26369869772155</v>
       </c>
       <c r="BF29" t="n">
-        <v>13.36420241380861</v>
+        <v>13.27521540346162</v>
       </c>
       <c r="BG29" t="n">
-        <v>18.92121844237781</v>
+        <v>18.79864673628448</v>
       </c>
       <c r="BH29" t="n">
-        <v>0.3616500414355047</v>
+        <v>0.3621351483755615</v>
       </c>
       <c r="BI29" t="n">
-        <v>18.9246743194341</v>
+        <v>18.80213447939643</v>
       </c>
       <c r="BJ29" t="n">
-        <v>1.5385</v>
+        <v>1.54</v>
       </c>
       <c r="BK29" t="n">
-        <v>2.048927717267306</v>
+        <v>2.046167216896666</v>
       </c>
       <c r="BL29" t="n">
-        <v>3.066572458475788</v>
+        <v>3.070709595625828</v>
       </c>
       <c r="BM29" t="n">
-        <v>5.368190619240342</v>
+        <v>5.360958108269264</v>
       </c>
       <c r="BN29" t="n">
-        <v>0.02897183792215971</v>
+        <v>0.02841103180661018</v>
       </c>
       <c r="BO29" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8295766074154407</v>
       </c>
       <c r="BP29" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993967269886901</v>
       </c>
       <c r="BQ29" t="inlineStr"/>
       <c r="BR29" t="inlineStr"/>
@@ -9676,49 +9676,49 @@
         <v>270.91</v>
       </c>
       <c r="BU29" t="n">
-        <v>4500</v>
+        <v>5504</v>
       </c>
       <c r="BV29" t="n">
-        <v>13730.76923076923</v>
+        <v>14743</v>
       </c>
       <c r="BW29" t="n">
-        <v>14.18000000000001</v>
+        <v>13.84</v>
       </c>
       <c r="BX29" t="n">
-        <v>13.35976760326447</v>
+        <v>13.29088000418701</v>
       </c>
       <c r="BY29" t="n">
-        <v>13.38456956067358</v>
+        <v>13.29544628962278</v>
       </c>
       <c r="BZ29" t="n">
-        <v>18.94635491936656</v>
+        <v>18.82113071529742</v>
       </c>
       <c r="CA29" t="n">
-        <v>0.2795411113503943</v>
+        <v>0.2762036181917923</v>
       </c>
       <c r="CB29" t="n">
-        <v>18.94841703054745</v>
+        <v>18.82315727610579</v>
       </c>
       <c r="CC29" t="n">
-        <v>1.5385</v>
+        <v>1.54</v>
       </c>
       <c r="CD29" t="n">
-        <v>2.048927717267306</v>
+        <v>2.046167216896666</v>
       </c>
       <c r="CE29" t="n">
-        <v>3.066572458475788</v>
+        <v>3.070709595625828</v>
       </c>
       <c r="CF29" t="n">
-        <v>5.368190619240342</v>
+        <v>5.360958108269264</v>
       </c>
       <c r="CG29" t="n">
-        <v>0.02905379503085041</v>
+        <v>0.02831895428184986</v>
       </c>
       <c r="CH29" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8295766074154407</v>
       </c>
       <c r="CI29" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993967269886901</v>
       </c>
       <c r="CJ29" t="inlineStr"/>
       <c r="CK29" t="inlineStr"/>
@@ -9733,7 +9733,7 @@
         <v>5.368376345338421</v>
       </c>
       <c r="CP29" t="n">
-        <v>0.03126566971508363</v>
+        <v>0.0311687008560976</v>
       </c>
       <c r="CQ29" t="n">
         <v>1.18841919095278</v>
@@ -9752,13 +9752,13 @@
       </c>
       <c r="CX29" t="inlineStr"/>
       <c r="CY29" t="n">
-        <v>1.031422660173269</v>
+        <v>1.039737343931582</v>
       </c>
       <c r="CZ29" t="n">
-        <v>0.9692660214303966</v>
+        <v>0.9680775749641317</v>
       </c>
       <c r="DA29" t="n">
-        <v>1.001413863134641</v>
+        <v>1.002049300657752</v>
       </c>
       <c r="DB29" t="inlineStr">
         <is>
@@ -9766,16 +9766,16 @@
         </is>
       </c>
       <c r="DC29" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6498429546193003</v>
       </c>
       <c r="DD29" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6494912318683699</v>
       </c>
       <c r="DE29" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6493506493506493</v>
       </c>
       <c r="DF29" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6493506493506493</v>
       </c>
     </row>
     <row r="30">
@@ -9837,49 +9837,49 @@
         <v>267.07</v>
       </c>
       <c r="P30" t="n">
-        <v>4700</v>
+        <v>4762</v>
       </c>
       <c r="Q30" t="n">
-        <v>9315.384615384615</v>
+        <v>9364</v>
       </c>
       <c r="R30" t="n">
-        <v>12.96215</v>
+        <v>12.97872499999999</v>
       </c>
       <c r="S30" t="n">
-        <v>8.015561469688505</v>
+        <v>8.040997556714677</v>
       </c>
       <c r="T30" t="n">
-        <v>8.169590274720239</v>
+        <v>8.172367307810305</v>
       </c>
       <c r="U30" t="n">
-        <v>11.64079794286208</v>
+        <v>11.65690432279619</v>
       </c>
       <c r="V30" t="n">
-        <v>5.861416616641699</v>
+        <v>5.816854197799039</v>
       </c>
       <c r="W30" t="n">
-        <v>13.0332030407105</v>
+        <v>13.02763259956608</v>
       </c>
       <c r="X30" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.767</v>
       </c>
       <c r="Y30" t="n">
-        <v>6.809582094531432</v>
+        <v>6.847887767461161</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.9175362565133077</v>
       </c>
       <c r="AA30" t="n">
-        <v>17.84110508767235</v>
+        <v>17.94146595074824</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.08826682454663064</v>
+        <v>0.08887685216474227</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.9992903633723431</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.199606895264513</v>
+        <v>1.196266305753987</v>
       </c>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
@@ -9890,49 +9890,49 @@
         <v>269.75</v>
       </c>
       <c r="AI30" t="n">
-        <v>4800</v>
+        <v>4888</v>
       </c>
       <c r="AJ30" t="n">
-        <v>9415.384615384615</v>
+        <v>9473</v>
       </c>
       <c r="AK30" t="n">
-        <v>14.13685000000003</v>
+        <v>13.96860000000002</v>
       </c>
       <c r="AL30" t="n">
-        <v>8.041693078089617</v>
+        <v>7.766970101249409</v>
       </c>
       <c r="AM30" t="n">
-        <v>7.962994290684516</v>
+        <v>7.988916995171805</v>
       </c>
       <c r="AN30" t="n">
-        <v>11.41553718958201</v>
+        <v>11.44604243625829</v>
       </c>
       <c r="AO30" t="n">
-        <v>6.572437535822831</v>
+        <v>6.523330448008056</v>
       </c>
       <c r="AP30" t="n">
-        <v>13.17237353285363</v>
+        <v>13.17443462113401</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.7641666666666667</v>
       </c>
       <c r="AR30" t="n">
-        <v>6.809582094531432</v>
+        <v>6.898483167577155</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.9108067896302964</v>
       </c>
       <c r="AT30" t="n">
-        <v>17.84110508767235</v>
+        <v>18.07402589905215</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.09626604063307688</v>
+        <v>0.09636215197461835</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.9993308002414796</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.199606895264513</v>
+        <v>1.191895471708131</v>
       </c>
       <c r="AX30" t="inlineStr"/>
       <c r="AY30" t="inlineStr"/>
@@ -9943,49 +9943,49 @@
         <v>270.24</v>
       </c>
       <c r="BB30" t="n">
-        <v>6500</v>
+        <v>6486</v>
       </c>
       <c r="BC30" t="n">
-        <v>11115.38461538462</v>
+        <v>11106</v>
       </c>
       <c r="BD30" t="n">
         <v>6.40500000000003</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.555094231542609</v>
+        <v>5.56141867047917</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.599735294349129</v>
+        <v>5.60211547181889</v>
       </c>
       <c r="BG30" t="n">
-        <v>7.93577234184132</v>
+        <v>7.938736575180508</v>
       </c>
       <c r="BH30" t="n">
-        <v>0.6389933540078504</v>
+        <v>0.6381047435397575</v>
       </c>
       <c r="BI30" t="n">
-        <v>7.961456849597305</v>
+        <v>7.964340278631789</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7701666666666668</v>
       </c>
       <c r="BK30" t="n">
-        <v>6.80664920385966</v>
+        <v>6.792013952800097</v>
       </c>
       <c r="BL30" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9250842755688481</v>
       </c>
       <c r="BM30" t="n">
-        <v>17.83342091411231</v>
+        <v>17.79507655633626</v>
       </c>
       <c r="BN30" t="n">
-        <v>0.04359658815072132</v>
+        <v>0.04350284936768482</v>
       </c>
       <c r="BO30" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992428639850438</v>
       </c>
       <c r="BP30" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201148161309909</v>
       </c>
       <c r="BQ30" t="inlineStr"/>
       <c r="BR30" t="inlineStr"/>
@@ -9996,28 +9996,28 @@
         <v>270.91</v>
       </c>
       <c r="BU30" t="n">
-        <v>6500</v>
+        <v>6489</v>
       </c>
       <c r="BV30" t="n">
-        <v>11115.38461538462</v>
+        <v>11104</v>
       </c>
       <c r="BW30" t="n">
         <v>6.404999999999973</v>
       </c>
       <c r="BX30" t="n">
-        <v>5.520964456410366</v>
+        <v>5.521797262782315</v>
       </c>
       <c r="BY30" t="n">
-        <v>5.42773084111632</v>
+        <v>5.429677321262969</v>
       </c>
       <c r="BZ30" t="n">
-        <v>7.687371651248966</v>
+        <v>7.689941155256845</v>
       </c>
       <c r="CA30" t="n">
-        <v>0.6155728190515958</v>
+        <v>0.6146247632206095</v>
       </c>
       <c r="CB30" t="n">
-        <v>7.711978526939853</v>
+        <v>7.714464243930162</v>
       </c>
       <c r="CC30" t="n">
         <v>0.7693333333333332</v>
@@ -10053,7 +10053,7 @@
         <v>17.83814903173707</v>
       </c>
       <c r="CP30" t="n">
-        <v>0.09625009051118807</v>
+        <v>0.09510456815447434</v>
       </c>
       <c r="CQ30" t="n">
         <v>3.948903220766222</v>
@@ -10072,13 +10072,13 @@
       </c>
       <c r="CX30" t="inlineStr"/>
       <c r="CY30" t="n">
-        <v>1.003260109538169</v>
+        <v>0.9659212114501341</v>
       </c>
       <c r="CZ30" t="n">
-        <v>0.6907866512187599</v>
+        <v>0.7160345151302371</v>
       </c>
       <c r="DA30" t="n">
-        <v>0.9938561302995638</v>
+        <v>0.9928756653572638</v>
       </c>
       <c r="DB30" t="inlineStr">
         <is>
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="DC30" t="n">
-        <v>1.300108342361864</v>
+        <v>1.303780964797914</v>
       </c>
       <c r="DD30" t="n">
-        <v>1.300108342361864</v>
+        <v>1.308615049073064</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298420255355983</v>
       </c>
       <c r="DF30" t="n">
         <v>1.299826689774697</v>
@@ -10157,24 +10157,50 @@
         <v>267.07</v>
       </c>
       <c r="P31" t="n">
-        <v>4700</v>
+        <v>4642</v>
       </c>
       <c r="Q31" t="n">
-        <v>4315.384615384615</v>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
+        <v>5686</v>
+      </c>
+      <c r="R31" t="n">
+        <v>27.9775</v>
+      </c>
+      <c r="S31" t="n">
+        <v>16.24219425191112</v>
+      </c>
+      <c r="T31" t="n">
+        <v>15.71591056837968</v>
+      </c>
+      <c r="U31" t="n">
+        <v>22.62604320668175</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.506721966712721</v>
+      </c>
+      <c r="W31" t="n">
+        <v>22.76447860613174</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.8359999999999999</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>5.774277224914181</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.088133642089373</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>15.12860632927516</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.1615498410600365</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.9975366838725668</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.301595265657145</v>
+      </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="n">
@@ -10184,24 +10210,50 @@
         <v>269.75</v>
       </c>
       <c r="AI31" t="n">
-        <v>4800</v>
+        <v>4744</v>
       </c>
       <c r="AJ31" t="n">
-        <v>4415.384615384615</v>
-      </c>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr"/>
+        <v>5609</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>31.48937499999999</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>19.64873867491157</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>19.55665347329984</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>25.43573534231503</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>2.604806352025042</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>25.56876314051667</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.8660000000000001</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>5.388633958748201</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.166007072530715</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>14.11822097192029</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0.1696847154647566</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0.9961496654347264</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.346428490220225</v>
+      </c>
       <c r="AX31" t="inlineStr"/>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="n">
@@ -10211,24 +10263,50 @@
         <v>270.24</v>
       </c>
       <c r="BB31" t="n">
-        <v>6500</v>
+        <v>6406</v>
       </c>
       <c r="BC31" t="n">
-        <v>6115.384615384615</v>
-      </c>
-      <c r="BD31" t="inlineStr"/>
-      <c r="BE31" t="inlineStr"/>
-      <c r="BF31" t="inlineStr"/>
-      <c r="BG31" t="inlineStr"/>
-      <c r="BH31" t="inlineStr"/>
-      <c r="BI31" t="inlineStr"/>
-      <c r="BJ31" t="inlineStr"/>
-      <c r="BK31" t="inlineStr"/>
-      <c r="BL31" t="inlineStr"/>
-      <c r="BM31" t="inlineStr"/>
-      <c r="BN31" t="inlineStr"/>
-      <c r="BO31" t="inlineStr"/>
-      <c r="BP31" t="inlineStr"/>
+        <v>7386</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>13.62449999999998</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>8.93855637035289</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>8.474651652400761</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>11.86522782881691</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>1.094484174972689</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>11.91560015437732</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>0.7848000000000001</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>6.542749725283298</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0.96032793106839</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>17.14200428024224</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>0.08914169363212217</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0.9989891341735558</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>1.223659443257378</v>
+      </c>
       <c r="BQ31" t="inlineStr"/>
       <c r="BR31" t="inlineStr"/>
       <c r="BS31" t="n">
@@ -10238,24 +10316,50 @@
         <v>270.91</v>
       </c>
       <c r="BU31" t="n">
-        <v>6500</v>
+        <v>6407</v>
       </c>
       <c r="BV31" t="n">
-        <v>6115.384615384615</v>
-      </c>
-      <c r="BW31" t="inlineStr"/>
-      <c r="BX31" t="inlineStr"/>
-      <c r="BY31" t="inlineStr"/>
-      <c r="BZ31" t="inlineStr"/>
-      <c r="CA31" t="inlineStr"/>
-      <c r="CB31" t="inlineStr"/>
-      <c r="CC31" t="inlineStr"/>
-      <c r="CD31" t="inlineStr"/>
-      <c r="CE31" t="inlineStr"/>
-      <c r="CF31" t="inlineStr"/>
-      <c r="CG31" t="inlineStr"/>
-      <c r="CH31" t="inlineStr"/>
-      <c r="CI31" t="inlineStr"/>
+        <v>7386</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>11.86445000000002</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>6.879821007286997</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>6.618955373459638</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>9.160079962362577</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>1.19358221571972</v>
+      </c>
+      <c r="CB31" t="n">
+        <v>9.237516085104199</v>
+      </c>
+      <c r="CC31" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="CD31" t="n">
+        <v>6.55600789254555</v>
+      </c>
+      <c r="CE31" t="n">
+        <v>0.958385866851049</v>
+      </c>
+      <c r="CF31" t="n">
+        <v>17.17674067846934</v>
+      </c>
+      <c r="CG31" t="n">
+        <v>0.07778342784071215</v>
+      </c>
+      <c r="CH31" t="n">
+        <v>0.999004554140953</v>
+      </c>
+      <c r="CI31" t="n">
+        <v>1.222430952616134</v>
+      </c>
       <c r="CJ31" t="inlineStr"/>
       <c r="CK31" t="inlineStr"/>
       <c r="CL31" t="inlineStr"/>
@@ -10268,7 +10372,9 @@
       <c r="CO31" t="n">
         <v>17.83814903173707</v>
       </c>
-      <c r="CP31" t="inlineStr"/>
+      <c r="CP31" t="n">
+        <v>0.2143939557886471</v>
+      </c>
       <c r="CQ31" t="n">
         <v>3.948903220766222</v>
       </c>
@@ -10285,18 +10391,32 @@
         <v>5.8</v>
       </c>
       <c r="CX31" t="inlineStr"/>
-      <c r="CY31" t="inlineStr"/>
-      <c r="CZ31" t="inlineStr"/>
-      <c r="DA31" t="inlineStr"/>
+      <c r="CY31" t="n">
+        <v>1.209734249582665</v>
+      </c>
+      <c r="CZ31" t="n">
+        <v>0.4549175658672714</v>
+      </c>
+      <c r="DA31" t="n">
+        <v>0.7696792101804897</v>
+      </c>
       <c r="DB31" t="inlineStr">
         <is>
           <t>PROCESSED-20251113-tett6roof-loosepaneltaped</t>
         </is>
       </c>
-      <c r="DC31" t="inlineStr"/>
-      <c r="DD31" t="inlineStr"/>
-      <c r="DE31" t="inlineStr"/>
-      <c r="DF31" t="inlineStr"/>
+      <c r="DC31" t="n">
+        <v>1.196172248803828</v>
+      </c>
+      <c r="DD31" t="n">
+        <v>1.15473441108545</v>
+      </c>
+      <c r="DE31" t="n">
+        <v>1.27420998980632</v>
+      </c>
+      <c r="DF31" t="n">
+        <v>1.275510204081633</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10357,47 +10477,47 @@
         <v>267.07</v>
       </c>
       <c r="P32" t="n">
-        <v>3950</v>
+        <v>5063</v>
       </c>
       <c r="Q32" t="n">
-        <v>13180.76923076923</v>
+        <v>14296</v>
       </c>
       <c r="R32" t="n">
-        <v>12.55019999999999</v>
+        <v>12.59932500000001</v>
       </c>
       <c r="S32" t="n">
-        <v>4.4829695678267</v>
+        <v>4.447595624688176</v>
       </c>
       <c r="T32" t="n">
-        <v>4.589759436354918</v>
+        <v>4.555203010301959</v>
       </c>
       <c r="U32" t="n">
-        <v>6.632137597661694</v>
+        <v>6.580461578785396</v>
       </c>
       <c r="V32" t="n">
-        <v>7.722993705383294</v>
+        <v>7.968153518298192</v>
       </c>
       <c r="W32" t="n">
-        <v>10.17987627074651</v>
+        <v>10.3341155925913</v>
       </c>
       <c r="X32" t="n">
-        <v>1.5375</v>
+        <v>1.538</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.050772523574458</v>
+        <v>2.049849672265102</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.063813872553798</v>
+        <v>3.065193214991523</v>
       </c>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="n">
-        <v>0.02573760532536415</v>
+        <v>0.02582672222201152</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.8304076132092216</v>
+        <v>0.8302413841571755</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.99272446995369</v>
+        <v>1.992973481789027</v>
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
@@ -10408,47 +10528,47 @@
         <v>269.75</v>
       </c>
       <c r="AI32" t="n">
-        <v>4000</v>
+        <v>5147</v>
       </c>
       <c r="AJ32" t="n">
-        <v>13230.76923076923</v>
+        <v>14386</v>
       </c>
       <c r="AK32" t="n">
-        <v>13.74439999999999</v>
+        <v>13.9634</v>
       </c>
       <c r="AL32" t="n">
-        <v>4.459569602553477</v>
+        <v>4.43034679549129</v>
       </c>
       <c r="AM32" t="n">
-        <v>4.576175921664607</v>
+        <v>4.67676162838812</v>
       </c>
       <c r="AN32" t="n">
-        <v>6.689082233157181</v>
+        <v>6.850756137531426</v>
       </c>
       <c r="AO32" t="n">
-        <v>9.366730851994891</v>
+        <v>9.486063586750735</v>
       </c>
       <c r="AP32" t="n">
-        <v>11.50997254452208</v>
+        <v>11.70120771663347</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.5375</v>
+        <v>1.539</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.050772523574458</v>
+        <v>2.048006657255135</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.063813872553798</v>
+        <v>3.067951603048352</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AU32" t="n">
-        <v>0.02818663787301676</v>
+        <v>0.02859713615791635</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.8304076132092216</v>
+        <v>0.8299089677142342</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.99272446995369</v>
+        <v>1.993470827191911</v>
       </c>
       <c r="AX32" t="inlineStr"/>
       <c r="AY32" t="inlineStr"/>
@@ -10459,47 +10579,47 @@
         <v>270.24</v>
       </c>
       <c r="BB32" t="n">
-        <v>4500</v>
+        <v>5671</v>
       </c>
       <c r="BC32" t="n">
-        <v>13730.76923076923</v>
+        <v>14887</v>
       </c>
       <c r="BD32" t="n">
-        <v>17.9869</v>
+        <v>16.93800000000002</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.069932000996957</v>
+        <v>4.117339944851108</v>
       </c>
       <c r="BF32" t="n">
-        <v>4.451779144786069</v>
+        <v>4.449218198534311</v>
       </c>
       <c r="BG32" t="n">
-        <v>7.445986615416277</v>
+        <v>7.411745835903846</v>
       </c>
       <c r="BH32" t="n">
-        <v>12.37534532797078</v>
+        <v>11.38938918452667</v>
       </c>
       <c r="BI32" t="n">
-        <v>14.44271057189358</v>
+        <v>13.58867772568954</v>
       </c>
       <c r="BJ32" t="n">
-        <v>1.536333333333333</v>
+        <v>1.534333333333333</v>
       </c>
       <c r="BK32" t="n">
-        <v>2.052929336419657</v>
+        <v>2.056638148796316</v>
       </c>
       <c r="BL32" t="n">
-        <v>3.060595021812863</v>
+        <v>3.055075736515406</v>
       </c>
       <c r="BM32" t="inlineStr"/>
       <c r="BN32" t="n">
-        <v>0.03692583468124672</v>
+        <v>0.03483533696431204</v>
       </c>
       <c r="BO32" t="n">
-        <v>0.8307955343816316</v>
+        <v>0.8314607131888911</v>
       </c>
       <c r="BP32" t="n">
-        <v>1.992142561388282</v>
+        <v>1.991142126775194</v>
       </c>
       <c r="BQ32" t="inlineStr"/>
       <c r="BR32" t="inlineStr"/>
@@ -10510,47 +10630,47 @@
         <v>270.91</v>
       </c>
       <c r="BU32" t="n">
-        <v>4500</v>
+        <v>5665</v>
       </c>
       <c r="BV32" t="n">
-        <v>13730.76923076923</v>
+        <v>14879</v>
       </c>
       <c r="BW32" t="n">
-        <v>27.21890000000023</v>
+        <v>26.29767499999999</v>
       </c>
       <c r="BX32" t="n">
-        <v>4.394625080749956</v>
+        <v>4.347427515873112</v>
       </c>
       <c r="BY32" t="n">
-        <v>5.282695588952136</v>
+        <v>5.114069541297805</v>
       </c>
       <c r="BZ32" t="n">
-        <v>9.53407535337915</v>
+        <v>9.472178510270618</v>
       </c>
       <c r="CA32" t="n">
-        <v>15.14810921481032</v>
+        <v>15.28269135968512</v>
       </c>
       <c r="CB32" t="n">
-        <v>17.89870960789445</v>
+        <v>17.98006732261664</v>
       </c>
       <c r="CC32" t="n">
-        <v>1.536666666666667</v>
+        <v>1.535</v>
       </c>
       <c r="CD32" t="n">
-        <v>2.052312604502923</v>
+        <v>2.055400271381493</v>
       </c>
       <c r="CE32" t="n">
-        <v>3.061514748481212</v>
+        <v>3.056915674607982</v>
       </c>
       <c r="CF32" t="inlineStr"/>
       <c r="CG32" t="n">
-        <v>0.05586169155070508</v>
+        <v>0.05405224833170228</v>
       </c>
       <c r="CH32" t="n">
-        <v>0.8306846921790945</v>
+        <v>0.8312389631768243</v>
       </c>
       <c r="CI32" t="n">
-        <v>1.992308946950897</v>
+        <v>1.991476009516601</v>
       </c>
       <c r="CJ32" t="inlineStr"/>
       <c r="CK32" t="inlineStr"/>
@@ -10563,7 +10683,7 @@
       </c>
       <c r="CO32" t="inlineStr"/>
       <c r="CP32" t="n">
-        <v>0.02816225642781272</v>
+        <v>0.02861098712232767</v>
       </c>
       <c r="CQ32" t="n">
         <v>1.18841919095278</v>
@@ -10582,13 +10702,13 @@
       </c>
       <c r="CX32" t="inlineStr"/>
       <c r="CY32" t="n">
-        <v>0.994780253374647</v>
+        <v>0.9961217631609447</v>
       </c>
       <c r="CZ32" t="n">
-        <v>0.9126288776088572</v>
+        <v>0.929349356813619</v>
       </c>
       <c r="DA32" t="n">
-        <v>1.079778502361578</v>
+        <v>1.055882578097477</v>
       </c>
       <c r="DB32" t="inlineStr">
         <is>
@@ -10596,16 +10716,16 @@
         </is>
       </c>
       <c r="DC32" t="n">
-        <v>0.6504065040650406</v>
+        <v>0.6501950585175553</v>
       </c>
       <c r="DD32" t="n">
-        <v>0.6504065040650406</v>
+        <v>0.649772579597141</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.6509004122369277</v>
+        <v>0.651748859439496</v>
       </c>
       <c r="DF32" t="n">
-        <v>0.6507592190889371</v>
+        <v>0.6514657980456026</v>
       </c>
     </row>
     <row r="33">
@@ -10667,49 +10787,49 @@
         <v>267.07</v>
       </c>
       <c r="P33" t="n">
-        <v>4700</v>
+        <v>4770</v>
       </c>
       <c r="Q33" t="n">
-        <v>6238.461538461538</v>
+        <v>6311</v>
       </c>
       <c r="R33" t="n">
-        <v>74.71969999999996</v>
+        <v>76.93299999999998</v>
       </c>
       <c r="S33" t="n">
-        <v>51.696496041685</v>
+        <v>51.08666669194909</v>
       </c>
       <c r="T33" t="n">
-        <v>53.6304526204627</v>
+        <v>54.1191594445641</v>
       </c>
       <c r="U33" t="n">
-        <v>77.01799047223676</v>
+        <v>76.54901115712559</v>
       </c>
       <c r="V33" t="n">
-        <v>21.08332631762611</v>
+        <v>20.8728219564268</v>
       </c>
       <c r="W33" t="n">
-        <v>79.85159675921992</v>
+        <v>79.34371938319021</v>
       </c>
       <c r="X33" t="n">
-        <v>0.7635</v>
+        <v>0.7655000000000001</v>
       </c>
       <c r="Y33" t="n">
-        <v>6.910471661373164</v>
+        <v>6.874602069357319</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.909226694655321</v>
+        <v>0.9139707642404643</v>
       </c>
       <c r="AA33" t="n">
-        <v>18.10543575279769</v>
+        <v>18.01145742171618</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.5163483693963041</v>
+        <v>0.5288837610018665</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.9993400391095105</v>
+        <v>0.9993120093253508</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.190866659666432</v>
+        <v>1.193952663932677</v>
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
@@ -10720,49 +10840,49 @@
         <v>269.75</v>
       </c>
       <c r="AI33" t="n">
-        <v>4800</v>
+        <v>4876</v>
       </c>
       <c r="AJ33" t="n">
-        <v>6338.461538461538</v>
+        <v>6404</v>
       </c>
       <c r="AK33" t="n">
-        <v>59.43395</v>
+        <v>63.95659999999995</v>
       </c>
       <c r="AL33" t="n">
-        <v>45.31853843010108</v>
+        <v>45.61502917241833</v>
       </c>
       <c r="AM33" t="n">
-        <v>49.3785316424196</v>
+        <v>48.67661869969534</v>
       </c>
       <c r="AN33" t="n">
-        <v>72.26962593472186</v>
+        <v>70.40596015221247</v>
       </c>
       <c r="AO33" t="n">
-        <v>20.07364080113048</v>
+        <v>21.1236280165095</v>
       </c>
       <c r="AP33" t="n">
-        <v>75.0056657043815</v>
+        <v>73.50650913718319</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.7695</v>
+        <v>0.7645000000000001</v>
       </c>
       <c r="AR33" t="n">
-        <v>6.80371826215872</v>
+        <v>6.892500926879841</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.9234928703802652</v>
+        <v>0.9115973104444564</v>
       </c>
       <c r="AT33" t="n">
-        <v>17.82574184685585</v>
+        <v>18.05835242842518</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.4043718510072283</v>
+        <v>0.4408209247800829</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.9992530703381666</v>
+        <v>0.999326141817212</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.200120689253106</v>
+        <v>1.192409823995365</v>
       </c>
       <c r="AX33" t="inlineStr"/>
       <c r="AY33" t="inlineStr"/>
@@ -10773,49 +10893,49 @@
         <v>270.24</v>
       </c>
       <c r="BB33" t="n">
-        <v>6500</v>
+        <v>6426</v>
       </c>
       <c r="BC33" t="n">
-        <v>8038.461538461538</v>
+        <v>7849</v>
       </c>
       <c r="BD33" t="n">
-        <v>56.82874999999999</v>
+        <v>57.30312499999999</v>
       </c>
       <c r="BE33" t="n">
-        <v>23.56970114052037</v>
+        <v>29.19384706154364</v>
       </c>
       <c r="BF33" t="n">
-        <v>43.22815929434431</v>
+        <v>40.49427390574014</v>
       </c>
       <c r="BG33" t="n">
-        <v>61.68819774125984</v>
+        <v>55.52499320637862</v>
       </c>
       <c r="BH33" t="n">
-        <v>12.39819381557476</v>
+        <v>10.21259327392921</v>
       </c>
       <c r="BI33" t="n">
-        <v>62.92176849432423</v>
+        <v>56.45637193397301</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0.7655000000000001</v>
+        <v>0.8091428571428571</v>
       </c>
       <c r="BK33" t="n">
-        <v>6.874602069357319</v>
+        <v>6.158494799560341</v>
       </c>
       <c r="BL33" t="n">
-        <v>0.9139707642404643</v>
+        <v>1.020246912870357</v>
       </c>
       <c r="BM33" t="n">
-        <v>18.01145742171618</v>
+        <v>16.13525637484809</v>
       </c>
       <c r="BN33" t="n">
-        <v>0.3906750423489896</v>
+        <v>0.3529009973110561</v>
       </c>
       <c r="BO33" t="n">
-        <v>0.9993120093253508</v>
+        <v>0.998421840805628</v>
       </c>
       <c r="BP33" t="n">
-        <v>1.193952663932677</v>
+        <v>1.260898373957009</v>
       </c>
       <c r="BQ33" t="inlineStr"/>
       <c r="BR33" t="inlineStr"/>
@@ -10826,49 +10946,49 @@
         <v>270.91</v>
       </c>
       <c r="BU33" t="n">
-        <v>6500</v>
+        <v>6533</v>
       </c>
       <c r="BV33" t="n">
-        <v>8038.461538461538</v>
+        <v>8088</v>
       </c>
       <c r="BW33" t="n">
-        <v>56.70289999999999</v>
+        <v>56.69524999999998</v>
       </c>
       <c r="BX33" t="n">
-        <v>23.79625146371452</v>
+        <v>24.11429557946379</v>
       </c>
       <c r="BY33" t="n">
-        <v>42.3406537889321</v>
+        <v>42.77473584037434</v>
       </c>
       <c r="BZ33" t="n">
-        <v>60.56941472985756</v>
+        <v>61.18922949327087</v>
       </c>
       <c r="CA33" t="n">
-        <v>7.703502923725415</v>
+        <v>7.803425169563004</v>
       </c>
       <c r="CB33" t="n">
-        <v>61.05733336801839</v>
+        <v>61.68480566847188</v>
       </c>
       <c r="CC33" t="n">
-        <v>0.7695</v>
+        <v>0.778</v>
       </c>
       <c r="CD33" t="n">
-        <v>6.80371826215872</v>
+        <v>6.656787263970566</v>
       </c>
       <c r="CE33" t="n">
-        <v>0.9234928703802652</v>
+        <v>0.9438765365369153</v>
       </c>
       <c r="CF33" t="n">
-        <v>17.82574184685585</v>
+        <v>17.44078263160288</v>
       </c>
       <c r="CG33" t="n">
-        <v>0.3857905562473596</v>
+        <v>0.3774082181276271</v>
       </c>
       <c r="CH33" t="n">
-        <v>0.9992530703381666</v>
+        <v>0.9991143325155043</v>
       </c>
       <c r="CI33" t="n">
-        <v>1.200120689253106</v>
+        <v>1.213208915857218</v>
       </c>
       <c r="CJ33" t="inlineStr"/>
       <c r="CK33" t="inlineStr"/>
@@ -10883,7 +11003,7 @@
         <v>17.83814903173707</v>
       </c>
       <c r="CP33" t="n">
-        <v>0.4046533044445839</v>
+        <v>0.435445558153891</v>
       </c>
       <c r="CQ33" t="n">
         <v>3.948903220766222</v>
@@ -10902,13 +11022,13 @@
       </c>
       <c r="CX33" t="inlineStr"/>
       <c r="CY33" t="n">
-        <v>0.876626887701613</v>
+        <v>0.8928949983657272</v>
       </c>
       <c r="CZ33" t="n">
-        <v>0.5200896135887982</v>
+        <v>0.6400050069286385</v>
       </c>
       <c r="DA33" t="n">
-        <v>1.009611930242283</v>
+        <v>0.8260060939768703</v>
       </c>
       <c r="DB33" t="inlineStr">
         <is>
@@ -10916,16 +11036,16 @@
         </is>
       </c>
       <c r="DC33" t="n">
-        <v>1.309757694826457</v>
+        <v>1.306335728282168</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.299545159194282</v>
+        <v>1.308044473512099</v>
       </c>
       <c r="DE33" t="n">
-        <v>1.306335728282168</v>
+        <v>1.235875706214689</v>
       </c>
       <c r="DF33" t="n">
-        <v>1.299545159194282</v>
+        <v>1.2853470437018</v>
       </c>
     </row>
     <row r="34">
@@ -10987,49 +11107,49 @@
         <v>267.07</v>
       </c>
       <c r="P34" t="n">
-        <v>3950</v>
+        <v>5066</v>
       </c>
       <c r="Q34" t="n">
-        <v>13180.76923076923</v>
+        <v>14326</v>
       </c>
       <c r="R34" t="n">
-        <v>15.375625</v>
+        <v>15.32474999999997</v>
       </c>
       <c r="S34" t="n">
-        <v>8.978051154644859</v>
+        <v>8.7495454883514</v>
       </c>
       <c r="T34" t="n">
-        <v>9.066805716781406</v>
+        <v>8.891092861873778</v>
       </c>
       <c r="U34" t="n">
-        <v>12.93475762302974</v>
+        <v>12.65909972881109</v>
       </c>
       <c r="V34" t="n">
-        <v>7.077686371739508</v>
+        <v>6.66536068105117</v>
       </c>
       <c r="W34" t="n">
-        <v>14.74454472485445</v>
+        <v>14.30663618578763</v>
       </c>
       <c r="X34" t="n">
-        <v>1.537666666666667</v>
+        <v>1.5425</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.050464806799213</v>
+        <v>2.041584185922544</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.064273664363776</v>
+        <v>3.077602849054379</v>
       </c>
       <c r="AA34" t="n">
-        <v>5.372217793813937</v>
+        <v>5.348950567117067</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.03152717794504215</v>
+        <v>0.03128676725321644</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.8303522019910555</v>
+        <v>0.8287459569625379</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.992807499044294</v>
+        <v>1.995204440229743</v>
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
@@ -11040,49 +11160,49 @@
         <v>269.75</v>
       </c>
       <c r="AI34" t="n">
-        <v>4000</v>
+        <v>5143</v>
       </c>
       <c r="AJ34" t="n">
-        <v>13230.76923076923</v>
+        <v>14386</v>
       </c>
       <c r="AK34" t="n">
-        <v>17.19499999999999</v>
+        <v>16.98407499999999</v>
       </c>
       <c r="AL34" t="n">
-        <v>9.158970511705048</v>
+        <v>9.057339287463629</v>
       </c>
       <c r="AM34" t="n">
-        <v>9.295164322518739</v>
+        <v>9.315952997133419</v>
       </c>
       <c r="AN34" t="n">
-        <v>13.37362314581008</v>
+        <v>13.4287896470192</v>
       </c>
       <c r="AO34" t="n">
-        <v>8.732505612667582</v>
+        <v>8.551561500685326</v>
       </c>
       <c r="AP34" t="n">
-        <v>15.97217738197951</v>
+        <v>15.92047723794401</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.537666666666667</v>
+        <v>1.539666666666667</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.050464806799213</v>
+        <v>2.046779967151801</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.064273664363776</v>
+        <v>3.069790308688119</v>
       </c>
       <c r="AT34" t="n">
-        <v>5.372217793813937</v>
+        <v>5.36256351393772</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.03525774235291245</v>
+        <v>0.0347626644706037</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.8303522019910555</v>
+        <v>0.8296873878994435</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.992807499044294</v>
+        <v>1.99380188916743</v>
       </c>
       <c r="AX34" t="inlineStr"/>
       <c r="AY34" t="inlineStr"/>
@@ -11093,49 +11213,49 @@
         <v>270.24</v>
       </c>
       <c r="BB34" t="n">
-        <v>4500</v>
+        <v>5510</v>
       </c>
       <c r="BC34" t="n">
-        <v>13730.76923076923</v>
+        <v>14749</v>
       </c>
       <c r="BD34" t="n">
-        <v>9.715000000000003</v>
+        <v>9.533174999999996</v>
       </c>
       <c r="BE34" t="n">
-        <v>8.625923568834081</v>
+        <v>8.521576475271143</v>
       </c>
       <c r="BF34" t="n">
-        <v>8.648952028513895</v>
+        <v>8.53882766441548</v>
       </c>
       <c r="BG34" t="n">
-        <v>12.26975308949725</v>
+        <v>12.11594520073636</v>
       </c>
       <c r="BH34" t="n">
-        <v>0.5845188311583664</v>
+        <v>0.5922240889208399</v>
       </c>
       <c r="BI34" t="n">
-        <v>12.28366814682023</v>
+        <v>12.13041044147907</v>
       </c>
       <c r="BJ34" t="n">
-        <v>1.5385</v>
+        <v>1.54</v>
       </c>
       <c r="BK34" t="n">
-        <v>2.048927717267306</v>
+        <v>2.046167216896666</v>
       </c>
       <c r="BL34" t="n">
-        <v>3.066572458475788</v>
+        <v>3.070709595625828</v>
       </c>
       <c r="BM34" t="n">
-        <v>5.368190619240342</v>
+        <v>5.360958108269264</v>
       </c>
       <c r="BN34" t="n">
-        <v>0.01990533277325188</v>
+        <v>0.01950647015793886</v>
       </c>
       <c r="BO34" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8295766074154407</v>
       </c>
       <c r="BP34" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993967269886901</v>
       </c>
       <c r="BQ34" t="inlineStr"/>
       <c r="BR34" t="inlineStr"/>
@@ -11146,49 +11266,49 @@
         <v>270.91</v>
       </c>
       <c r="BU34" t="n">
-        <v>4500</v>
+        <v>5510</v>
       </c>
       <c r="BV34" t="n">
-        <v>13730.76923076923</v>
+        <v>14745</v>
       </c>
       <c r="BW34" t="n">
-        <v>9.75400000000003</v>
+        <v>9.455000000000013</v>
       </c>
       <c r="BX34" t="n">
-        <v>8.605737394388266</v>
+        <v>8.537754365185785</v>
       </c>
       <c r="BY34" t="n">
-        <v>8.621022427305766</v>
+        <v>8.526983032970708</v>
       </c>
       <c r="BZ34" t="n">
-        <v>12.2230826464326</v>
+        <v>12.08965680816828</v>
       </c>
       <c r="CA34" t="n">
-        <v>0.6922149426428034</v>
+        <v>0.690197593592233</v>
       </c>
       <c r="CB34" t="n">
-        <v>12.2426676385639</v>
+        <v>12.10934244529777</v>
       </c>
       <c r="CC34" t="n">
-        <v>1.5385</v>
+        <v>1.539333333333333</v>
       </c>
       <c r="CD34" t="n">
-        <v>2.048927717267306</v>
+        <v>2.047393113807629</v>
       </c>
       <c r="CE34" t="n">
-        <v>3.066572458475788</v>
+        <v>3.068870977833106</v>
       </c>
       <c r="CF34" t="n">
-        <v>5.368190619240342</v>
+        <v>5.364169958175987</v>
       </c>
       <c r="CG34" t="n">
-        <v>0.01998524095422536</v>
+        <v>0.01935810189105115</v>
       </c>
       <c r="CH34" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8297981746744977</v>
       </c>
       <c r="CI34" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993636408293486</v>
       </c>
       <c r="CJ34" t="inlineStr"/>
       <c r="CK34" t="inlineStr"/>
@@ -11203,7 +11323,7 @@
         <v>5.368376345338421</v>
       </c>
       <c r="CP34" t="n">
-        <v>0.03523253101453973</v>
+        <v>0.0348003459837609</v>
       </c>
       <c r="CQ34" t="n">
         <v>1.18841919095278</v>
@@ -11222,13 +11342,13 @@
       </c>
       <c r="CX34" t="inlineStr"/>
       <c r="CY34" t="n">
-        <v>1.020151294968573</v>
+        <v>1.035178261490498</v>
       </c>
       <c r="CZ34" t="n">
-        <v>0.9418005612978292</v>
+        <v>0.9408476600921817</v>
       </c>
       <c r="DA34" t="n">
-        <v>0.9976598245643228</v>
+        <v>1.001898462093439</v>
       </c>
       <c r="DB34" t="inlineStr">
         <is>
@@ -11236,16 +11356,16 @@
         </is>
       </c>
       <c r="DC34" t="n">
-        <v>0.6503360069369173</v>
+        <v>0.6482982171799028</v>
       </c>
       <c r="DD34" t="n">
-        <v>0.6503360069369173</v>
+        <v>0.6494912318683699</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6493506493506493</v>
       </c>
       <c r="DF34" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6496318752706799</v>
       </c>
     </row>
   </sheetData>
